--- a/data/Ascona/investment_decision/aggregated_investment_decision.xlsx
+++ b/data/Ascona/investment_decision/aggregated_investment_decision.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K216"/>
+  <dimension ref="A1:K211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,28 +499,28 @@
         <v>46023</v>
       </c>
       <c r="C2" t="n">
-        <v>6.012635090781166</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>471337.0606824432</v>
+        <v>1603792.017964014</v>
       </c>
       <c r="E2" t="n">
-        <v>6.027760775346405</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>471337.0606824432</v>
+        <v>1603792.017964014</v>
       </c>
       <c r="G2" t="n">
-        <v>6.027760775346405</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>471337.0606824432</v>
+        <v>1603792.017964014</v>
       </c>
       <c r="I2" t="n">
-        <v>6.141230981562329</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>471337.0606824432</v>
+        <v>1603792.017964014</v>
       </c>
       <c r="K2" t="n">
         <v>0.003</v>
@@ -536,28 +536,28 @@
         <v>47849</v>
       </c>
       <c r="C3" t="n">
-        <v>594.9639508018255</v>
+        <v>2107.998814484529</v>
       </c>
       <c r="D3" t="n">
-        <v>471337.0606824432</v>
+        <v>1603792.017964014</v>
       </c>
       <c r="E3" t="n">
-        <v>594.9639508018222</v>
+        <v>1928.298028259503</v>
       </c>
       <c r="F3" t="n">
-        <v>471337.0606824432</v>
+        <v>1603792.017964014</v>
       </c>
       <c r="G3" t="n">
-        <v>595.5396712652223</v>
+        <v>2107.998814484535</v>
       </c>
       <c r="H3" t="n">
-        <v>471337.0606824432</v>
+        <v>1603792.017964014</v>
       </c>
       <c r="I3" t="n">
-        <v>595.5391177803915</v>
+        <v>1928.298028259503</v>
       </c>
       <c r="J3" t="n">
-        <v>471337.0606824432</v>
+        <v>1603792.017964014</v>
       </c>
       <c r="K3" t="n">
         <v>0.003</v>
@@ -573,28 +573,28 @@
         <v>49675</v>
       </c>
       <c r="C4" t="n">
-        <v>1769.209872184992</v>
+        <v>5931.052512637291</v>
       </c>
       <c r="D4" t="n">
-        <v>471337.0606824432</v>
+        <v>1603792.017964014</v>
       </c>
       <c r="E4" t="n">
-        <v>1787.813600308598</v>
+        <v>5778.584426112904</v>
       </c>
       <c r="F4" t="n">
-        <v>471337.0606824432</v>
+        <v>1603792.017964014</v>
       </c>
       <c r="G4" t="n">
-        <v>1770.600959162138</v>
+        <v>5931.052512637296</v>
       </c>
       <c r="H4" t="n">
-        <v>471337.0606824432</v>
+        <v>1603792.017964014</v>
       </c>
       <c r="I4" t="n">
-        <v>1767.470559045316</v>
+        <v>5778.584426112898</v>
       </c>
       <c r="J4" t="n">
-        <v>471337.0606824432</v>
+        <v>1603792.017964014</v>
       </c>
       <c r="K4" t="n">
         <v>0.003</v>
@@ -610,28 +610,28 @@
         <v>51502</v>
       </c>
       <c r="C5" t="n">
-        <v>2186.016940706689</v>
+        <v>6981.790938079661</v>
       </c>
       <c r="D5" t="n">
-        <v>471337.0606824432</v>
+        <v>1603792.017964014</v>
       </c>
       <c r="E5" t="n">
-        <v>2237.274552768716</v>
+        <v>6904.609400347793</v>
       </c>
       <c r="F5" t="n">
-        <v>471337.0606824432</v>
+        <v>1603792.017964014</v>
       </c>
       <c r="G5" t="n">
-        <v>2171.391197017018</v>
+        <v>6981.790938079661</v>
       </c>
       <c r="H5" t="n">
-        <v>471337.0606824432</v>
+        <v>1603792.017964014</v>
       </c>
       <c r="I5" t="n">
-        <v>2243.626840433342</v>
+        <v>6904.609400347793</v>
       </c>
       <c r="J5" t="n">
-        <v>471337.0606824432</v>
+        <v>1603792.017964014</v>
       </c>
       <c r="K5" t="n">
         <v>0.003</v>
@@ -647,28 +647,28 @@
         <v>53328</v>
       </c>
       <c r="C6" t="n">
-        <v>2186.016940706689</v>
+        <v>6981.790938079661</v>
       </c>
       <c r="D6" t="n">
-        <v>471337.0606824432</v>
+        <v>1603792.017964014</v>
       </c>
       <c r="E6" t="n">
-        <v>2238.609507324858</v>
+        <v>6904.609400347794</v>
       </c>
       <c r="F6" t="n">
-        <v>471337.0606824432</v>
+        <v>1603792.017964014</v>
       </c>
       <c r="G6" t="n">
-        <v>2171.391197017018</v>
+        <v>6981.790938079661</v>
       </c>
       <c r="H6" t="n">
-        <v>471337.0606824432</v>
+        <v>1603792.017964014</v>
       </c>
       <c r="I6" t="n">
-        <v>2244.961794989484</v>
+        <v>6904.609400347792</v>
       </c>
       <c r="J6" t="n">
-        <v>471337.0606824432</v>
+        <v>1603792.017964014</v>
       </c>
       <c r="K6" t="n">
         <v>0.003</v>
@@ -687,25 +687,25 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>707.0055910236647</v>
+        <v>2405.688026946022</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>707.0055910236647</v>
+        <v>2405.688026946022</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>356.7829589523546</v>
+        <v>1427.050483977316</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>356.7829589523546</v>
+        <v>1427.050483977316</v>
       </c>
       <c r="K7" t="n">
         <v>2</v>
@@ -724,25 +724,25 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>707.0055910236647</v>
+        <v>2405.688026946022</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>707.0055910236647</v>
+        <v>2405.688026946022</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>494.7904561143828</v>
+        <v>1708.304501463547</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>494.7904561143828</v>
+        <v>1708.304501463547</v>
       </c>
       <c r="K8" t="n">
         <v>2</v>
@@ -761,25 +761,25 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>707.0055910236647</v>
+        <v>2405.688026946022</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>707.0055910236647</v>
+        <v>2405.688026946022</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>564.2486750564943</v>
+        <v>1823.514628913067</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>564.2486750564943</v>
+        <v>1823.514628913067</v>
       </c>
       <c r="K9" t="n">
         <v>2</v>
@@ -798,25 +798,25 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>707.0055910236647</v>
+        <v>2405.688026946022</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>707.0055910236647</v>
+        <v>2405.688026946022</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>603.5753004354622</v>
+        <v>1885.099714401069</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>603.5753004354622</v>
+        <v>1885.099714401069</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
@@ -835,25 +835,25 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>707.0055910236647</v>
+        <v>2405.688026946022</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>707.0055910236647</v>
+        <v>2405.688026946022</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>627.8476976644408</v>
+        <v>1923.582451745854</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>627.8476976644408</v>
+        <v>1923.582451745854</v>
       </c>
       <c r="K11" t="n">
         <v>2</v>
@@ -872,25 +872,25 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>11.99397521250205</v>
+        <v>38.83232050396268</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>11.99397521250205</v>
+        <v>38.83232050396268</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.607837863137207</v>
+        <v>11.85896762513558</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>3.607837863137207</v>
+        <v>11.85896762513558</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -909,25 +909,25 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>11.99397521250205</v>
+        <v>38.83232050396268</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>11.99397521250205</v>
+        <v>38.83232050396268</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>5.722747024218983</v>
+        <v>16.32257745401947</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>5.722747024218983</v>
+        <v>16.32257745401947</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -946,25 +946,25 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>11.99397521250205</v>
+        <v>38.83232050396268</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>11.99397521250205</v>
+        <v>38.83232050396268</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>7.063248398539037</v>
+        <v>18.55779820003381</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>7.063248398539037</v>
+        <v>18.55779820003381</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -983,25 +983,25 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.99397521250205</v>
+        <v>38.83232050396268</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>11.99397521250205</v>
+        <v>38.83232050396268</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>7.964919593117228</v>
+        <v>19.86937002844656</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>7.964919593117228</v>
+        <v>19.86937002844656</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1020,25 +1020,25 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>11.99397521250205</v>
+        <v>38.83232050396268</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>11.99397521250205</v>
+        <v>38.83232050396268</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>8.600938502920275</v>
+        <v>20.72475010080856</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>8.600938502920275</v>
+        <v>20.72475010080856</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1054,28 +1054,28 @@
         <v>46023</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3126818435799518</v>
+        <v>1.668885927770414</v>
       </c>
       <c r="D17" t="n">
-        <v>11.99397521250205</v>
+        <v>38.83232050396268</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3126818435799518</v>
+        <v>1.668885927770414</v>
       </c>
       <c r="F17" t="n">
-        <v>11.99397521250205</v>
+        <v>38.83232050396268</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3127014969537156</v>
+        <v>1.668885927770413</v>
       </c>
       <c r="H17" t="n">
-        <v>3.607837863137207</v>
+        <v>11.85896762513558</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3127015087558676</v>
+        <v>1.668885927770414</v>
       </c>
       <c r="J17" t="n">
-        <v>3.607837863137207</v>
+        <v>11.85896762513558</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
@@ -1091,28 +1091,28 @@
         <v>47849</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3126818435799518</v>
+        <v>1.668885927770414</v>
       </c>
       <c r="D18" t="n">
-        <v>11.99397521250205</v>
+        <v>38.83232050396268</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3126818435799518</v>
+        <v>1.668885927770414</v>
       </c>
       <c r="F18" t="n">
-        <v>11.99397521250205</v>
+        <v>38.83232050396268</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3127014969537156</v>
+        <v>1.668885927770413</v>
       </c>
       <c r="H18" t="n">
-        <v>5.722747024218983</v>
+        <v>16.32257745401947</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3127015087558676</v>
+        <v>1.668885927770414</v>
       </c>
       <c r="J18" t="n">
-        <v>5.722747024218983</v>
+        <v>16.32257745401947</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -1128,28 +1128,28 @@
         <v>49675</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3217323713003519</v>
+        <v>1.72203695031119</v>
       </c>
       <c r="D19" t="n">
-        <v>11.99397521250205</v>
+        <v>38.83232050396268</v>
       </c>
       <c r="E19" t="n">
-        <v>0.321732371300352</v>
+        <v>1.723041410039284</v>
       </c>
       <c r="F19" t="n">
-        <v>11.99397521250205</v>
+        <v>38.83232050396268</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3217323713003521</v>
+        <v>1.72203695031119</v>
       </c>
       <c r="H19" t="n">
-        <v>7.063248398539037</v>
+        <v>18.55779820003381</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3217323713003519</v>
+        <v>1.723041410039284</v>
       </c>
       <c r="J19" t="n">
-        <v>7.063248398539037</v>
+        <v>18.55779820003381</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -1165,28 +1165,28 @@
         <v>51502</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3302514618736146</v>
+        <v>1.780896937953275</v>
       </c>
       <c r="D20" t="n">
-        <v>11.99397521250205</v>
+        <v>38.83232050396268</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3302514906135793</v>
+        <v>1.781102472681083</v>
       </c>
       <c r="F20" t="n">
-        <v>11.99397521250205</v>
+        <v>38.83232050396268</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3302541766555159</v>
+        <v>1.780896937953274</v>
       </c>
       <c r="H20" t="n">
-        <v>7.964919593117228</v>
+        <v>19.86937002844656</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3302541766555159</v>
+        <v>1.781102472681083</v>
       </c>
       <c r="J20" t="n">
-        <v>7.964919593117228</v>
+        <v>19.86937002844656</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
@@ -1202,28 +1202,28 @@
         <v>53328</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3302514618736146</v>
+        <v>1.783030930674917</v>
       </c>
       <c r="D21" t="n">
-        <v>11.99397521250205</v>
+        <v>38.83232050396268</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3302514906135793</v>
+        <v>1.783030930674916</v>
       </c>
       <c r="F21" t="n">
-        <v>11.99397521250205</v>
+        <v>38.83232050396268</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3302541766555159</v>
+        <v>1.783030930674915</v>
       </c>
       <c r="H21" t="n">
-        <v>8.600938502920275</v>
+        <v>20.72475010080856</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3302541766555159</v>
+        <v>1.783030930674915</v>
       </c>
       <c r="J21" t="n">
-        <v>8.600938502920275</v>
+        <v>20.72475010080856</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -1239,25 +1239,25 @@
         <v>46023</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1108364072376471</v>
+        <v>0.5865130888845524</v>
       </c>
       <c r="D22" t="n">
         <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1108364072376471</v>
+        <v>0.5865130888845524</v>
       </c>
       <c r="F22" t="n">
         <v>6</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1108364072376471</v>
+        <v>0.5865130888845524</v>
       </c>
       <c r="H22" t="n">
         <v>6</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1108364072376471</v>
+        <v>0.5865130888845524</v>
       </c>
       <c r="J22" t="n">
         <v>6</v>
@@ -1276,25 +1276,25 @@
         <v>47849</v>
       </c>
       <c r="C23" t="n">
-        <v>0.11555538312</v>
+        <v>0.6112755175735319</v>
       </c>
       <c r="D23" t="n">
         <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>0.11555538312</v>
+        <v>0.6120610294491871</v>
       </c>
       <c r="F23" t="n">
         <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>0.11555538312</v>
+        <v>0.6112755175735309</v>
       </c>
       <c r="H23" t="n">
         <v>6</v>
       </c>
       <c r="I23" t="n">
-        <v>0.11555538312</v>
+        <v>0.6120610294491871</v>
       </c>
       <c r="J23" t="n">
         <v>6</v>
@@ -1313,25 +1313,25 @@
         <v>49675</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1219154869741177</v>
+        <v>0.6316737420741051</v>
       </c>
       <c r="D24" t="n">
         <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1219154869741177</v>
+        <v>0.6330825941800524</v>
       </c>
       <c r="F24" t="n">
         <v>6</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1219154869741177</v>
+        <v>0.6316737420741051</v>
       </c>
       <c r="H24" t="n">
         <v>6</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1219154869741177</v>
+        <v>0.6330825941800524</v>
       </c>
       <c r="J24" t="n">
         <v>6</v>
@@ -1350,25 +1350,25 @@
         <v>51502</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1348269860987721</v>
+        <v>0.6693645873036504</v>
       </c>
       <c r="D25" t="n">
         <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1348272663577288</v>
+        <v>0.6693578099306406</v>
       </c>
       <c r="F25" t="n">
         <v>6</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1348534594070588</v>
+        <v>0.6693645873036504</v>
       </c>
       <c r="H25" t="n">
         <v>6</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1348534594070588</v>
+        <v>0.6693578099306406</v>
       </c>
       <c r="J25" t="n">
         <v>6</v>
@@ -1387,25 +1387,25 @@
         <v>53328</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1348269860987721</v>
+        <v>0.6693645873036504</v>
       </c>
       <c r="D26" t="n">
         <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1348272663577291</v>
+        <v>0.6693578099306406</v>
       </c>
       <c r="F26" t="n">
         <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1348534594070588</v>
+        <v>0.6693645873036504</v>
       </c>
       <c r="H26" t="n">
         <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1348534594070588</v>
+        <v>0.6693578099306406</v>
       </c>
       <c r="J26" t="n">
         <v>6</v>
@@ -1439,13 +1439,13 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0147365431046726</v>
+        <v>0.0867453946648023</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0147365431046726</v>
+        <v>0.0867453946648023</v>
       </c>
       <c r="K27" t="n">
         <v>100</v>
@@ -1476,13 +1476,13 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0275334314020259</v>
+        <v>0.1343372936492743</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0275334314020259</v>
+        <v>0.1343372936492743</v>
       </c>
       <c r="K28" t="n">
         <v>100</v>
@@ -1513,13 +1513,13 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.03882132685350974</v>
+        <v>0.1647522628953677</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.03882132685350974</v>
+        <v>0.1647522628953677</v>
       </c>
       <c r="K29" t="n">
         <v>100</v>
@@ -1550,13 +1550,13 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.04888731824920112</v>
+        <v>0.1862401701876625</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.04888731824920112</v>
+        <v>0.1862401701876625</v>
       </c>
       <c r="K30" t="n">
         <v>100</v>
@@ -1587,13 +1587,13 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0579683588432312</v>
+        <v>0.202571092960545</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0579683588432312</v>
+        <v>0.202571092960545</v>
       </c>
       <c r="K31" t="n">
         <v>100</v>
@@ -1609,28 +1609,28 @@
         <v>46023</v>
       </c>
       <c r="C32" t="n">
-        <v>0.01310655965273057</v>
+        <v>0.06987360984846264</v>
       </c>
       <c r="D32" t="n">
-        <v>8.080063897413311</v>
+        <v>27.49357745081168</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01310655965273057</v>
+        <v>0.06987360984846264</v>
       </c>
       <c r="F32" t="n">
-        <v>8.080063897413311</v>
+        <v>27.49357745081168</v>
       </c>
       <c r="G32" t="n">
-        <v>0.01310745809267406</v>
+        <v>0.06987360984846257</v>
       </c>
       <c r="H32" t="n">
-        <v>8.080063897413311</v>
+        <v>27.49357745081168</v>
       </c>
       <c r="I32" t="n">
-        <v>0.01310745863220101</v>
+        <v>0.06987360984846264</v>
       </c>
       <c r="J32" t="n">
-        <v>8.080063897413311</v>
+        <v>27.49357745081168</v>
       </c>
       <c r="K32" t="n">
         <v>175</v>
@@ -1646,28 +1646,28 @@
         <v>47849</v>
       </c>
       <c r="C33" t="n">
-        <v>0.01319646235229359</v>
+        <v>0.06987360984846264</v>
       </c>
       <c r="D33" t="n">
-        <v>8.080063897413311</v>
+        <v>27.49357745081168</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01319646235229359</v>
+        <v>0.06987360984846264</v>
       </c>
       <c r="F33" t="n">
-        <v>8.080063897413311</v>
+        <v>27.49357745081168</v>
       </c>
       <c r="G33" t="n">
-        <v>0.01319736079223708</v>
+        <v>0.06987360984846258</v>
       </c>
       <c r="H33" t="n">
-        <v>8.080063897413311</v>
+        <v>27.49357745081168</v>
       </c>
       <c r="I33" t="n">
-        <v>0.01319736133176403</v>
+        <v>0.06987360984846264</v>
       </c>
       <c r="J33" t="n">
-        <v>8.080063897413311</v>
+        <v>27.49357745081168</v>
       </c>
       <c r="K33" t="n">
         <v>175</v>
@@ -1683,28 +1683,28 @@
         <v>49675</v>
       </c>
       <c r="C34" t="n">
-        <v>0.013520298062806</v>
+        <v>0.07230337087889811</v>
       </c>
       <c r="D34" t="n">
-        <v>8.080063897413311</v>
+        <v>27.49357745081168</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01352029806280601</v>
+        <v>0.07234928903789667</v>
       </c>
       <c r="F34" t="n">
-        <v>8.080063897413311</v>
+        <v>27.49357745081168</v>
       </c>
       <c r="G34" t="n">
-        <v>0.01352029806280601</v>
+        <v>0.07230337087889811</v>
       </c>
       <c r="H34" t="n">
-        <v>8.080063897413311</v>
+        <v>27.49357745081168</v>
       </c>
       <c r="I34" t="n">
-        <v>0.013520298062806</v>
+        <v>0.07234928903789668</v>
       </c>
       <c r="J34" t="n">
-        <v>8.080063897413311</v>
+        <v>27.49357745081168</v>
       </c>
       <c r="K34" t="n">
         <v>175</v>
@@ -1720,28 +1720,28 @@
         <v>51502</v>
       </c>
       <c r="C35" t="n">
-        <v>0.01572038713692553</v>
+        <v>0.07499411317110753</v>
       </c>
       <c r="D35" t="n">
-        <v>8.080063897413311</v>
+        <v>27.49357745081168</v>
       </c>
       <c r="E35" t="n">
-        <v>0.01572044988228867</v>
+        <v>0.07500350904437884</v>
       </c>
       <c r="F35" t="n">
-        <v>8.080063897413311</v>
+        <v>27.49357745081168</v>
       </c>
       <c r="G35" t="n">
-        <v>0.01572631407450414</v>
+        <v>0.07499411317110766</v>
       </c>
       <c r="H35" t="n">
-        <v>8.080063897413311</v>
+        <v>27.49357745081168</v>
       </c>
       <c r="I35" t="n">
-        <v>0.01572631407450415</v>
+        <v>0.07500350904437879</v>
       </c>
       <c r="J35" t="n">
-        <v>8.080063897413311</v>
+        <v>27.49357745081168</v>
       </c>
       <c r="K35" t="n">
         <v>175</v>
@@ -1757,28 +1757,28 @@
         <v>53328</v>
       </c>
       <c r="C36" t="n">
-        <v>0.01572038713692553</v>
+        <v>0.07509166712409703</v>
       </c>
       <c r="D36" t="n">
-        <v>8.080063897413311</v>
+        <v>27.49357745081168</v>
       </c>
       <c r="E36" t="n">
-        <v>0.01572044988228874</v>
+        <v>0.075091667124097</v>
       </c>
       <c r="F36" t="n">
-        <v>8.080063897413311</v>
+        <v>27.49357745081168</v>
       </c>
       <c r="G36" t="n">
-        <v>0.01572631407450415</v>
+        <v>0.07509166712409697</v>
       </c>
       <c r="H36" t="n">
-        <v>8.080063897413311</v>
+        <v>27.49357745081168</v>
       </c>
       <c r="I36" t="n">
-        <v>0.01572631407450415</v>
+        <v>0.07509166712409697</v>
       </c>
       <c r="J36" t="n">
-        <v>8.080063897413311</v>
+        <v>27.49357745081168</v>
       </c>
       <c r="K36" t="n">
         <v>175</v>
@@ -1797,25 +1797,25 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>1.135883270089286</v>
+        <v>5.878502256181318</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>1.135883270089286</v>
+        <v>5.878502256181318</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.03553253809114845</v>
+        <v>0.47079117807104</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0.03553253809114845</v>
+        <v>0.47079117807104</v>
       </c>
       <c r="K37" t="n">
         <v>8</v>
@@ -1834,25 +1834,25 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>1.135883270089286</v>
+        <v>5.878502256181318</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>1.135883270089286</v>
+        <v>5.878502256181318</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.06628992744512983</v>
+        <v>0.742930397094833</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0.06628992744512983</v>
+        <v>0.742930397094833</v>
       </c>
       <c r="K38" t="n">
         <v>8</v>
@@ -1871,25 +1871,25 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>1.135883270089286</v>
+        <v>5.878502256181318</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>1.135883270089286</v>
+        <v>5.878502256181318</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.09334953007617701</v>
+        <v>0.9247372801783194</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.09334953007617701</v>
+        <v>0.9247372801783194</v>
       </c>
       <c r="K39" t="n">
         <v>8</v>
@@ -1908,25 +1908,25 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>1.135883270089286</v>
+        <v>5.878502256181318</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>1.135883270089286</v>
+        <v>5.878502256181318</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1174813095612829</v>
+        <v>1.058489268339244</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0.1174813095612829</v>
+        <v>1.058489268339244</v>
       </c>
       <c r="K40" t="n">
         <v>8</v>
@@ -1945,25 +1945,25 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>1.135883270089286</v>
+        <v>5.878502256181318</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>1.135883270089286</v>
+        <v>5.878502256181318</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1392411358567997</v>
+        <v>1.163707434539444</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0.1392411358567997</v>
+        <v>1.163707434539444</v>
       </c>
       <c r="K41" t="n">
         <v>8</v>
@@ -1982,25 +1982,25 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>2.189654496557659</v>
+        <v>11.33205254203628</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>2.189654496557659</v>
+        <v>11.33205254203628</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.06849645897088857</v>
+        <v>0.9075492589321255</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.06849645897088857</v>
+        <v>0.9075492589321255</v>
       </c>
       <c r="K42" t="n">
         <v>4.15</v>
@@ -2019,25 +2019,25 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>2.189654496557659</v>
+        <v>11.33205254203628</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>2.189654496557659</v>
+        <v>11.33205254203628</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.127787811942419</v>
+        <v>1.432154982351485</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0.127787811942419</v>
+        <v>1.432154982351485</v>
       </c>
       <c r="K43" t="n">
         <v>4.15</v>
@@ -2056,25 +2056,25 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>2.189654496557659</v>
+        <v>11.33205254203628</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>2.189654496557659</v>
+        <v>11.33205254203628</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1799509013516665</v>
+        <v>1.782626082271459</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0.1799509013516665</v>
+        <v>1.782626082271459</v>
       </c>
       <c r="K44" t="n">
         <v>4.15</v>
@@ -2093,25 +2093,25 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>2.189654496557659</v>
+        <v>11.33205254203628</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>2.189654496557659</v>
+        <v>11.33205254203628</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2264699943350033</v>
+        <v>2.040461240172037</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0.2264699943350033</v>
+        <v>2.040461240172037</v>
       </c>
       <c r="K45" t="n">
         <v>4.15</v>
@@ -2130,25 +2130,25 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>2.189654496557659</v>
+        <v>11.33205254203628</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>2.189654496557659</v>
+        <v>11.33205254203628</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2684166474347946</v>
+        <v>2.243291440076036</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0.2684166474347946</v>
+        <v>2.243291440076036</v>
       </c>
       <c r="K46" t="n">
         <v>4.15</v>
@@ -2167,25 +2167,25 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>0.03029022053571429</v>
+        <v>0.1567600601648352</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.03029022053571429</v>
+        <v>0.1567600601648352</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0009475343490972921</v>
+        <v>0.01255443141522774</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0.0009475343490972921</v>
+        <v>0.01255443141522774</v>
       </c>
       <c r="K47" t="n">
         <v>300</v>
@@ -2204,25 +2204,25 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0.03029022053571429</v>
+        <v>0.1567600601648352</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0.03029022053571429</v>
+        <v>0.1567600601648352</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.001767731398536796</v>
+        <v>0.01981147725586221</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.001767731398536796</v>
+        <v>0.01981147725586221</v>
       </c>
       <c r="K48" t="n">
         <v>300</v>
@@ -2241,25 +2241,25 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0.03029022053571429</v>
+        <v>0.1567600601648352</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0.03029022053571429</v>
+        <v>0.1567600601648352</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.002489320802031387</v>
+        <v>0.02465966080475518</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.002489320802031387</v>
+        <v>0.02465966080475518</v>
       </c>
       <c r="K49" t="n">
         <v>300</v>
@@ -2278,25 +2278,25 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0.03029022053571429</v>
+        <v>0.1567600601648352</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.03029022053571429</v>
+        <v>0.1567600601648352</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.003132834921634212</v>
+        <v>0.02822638048904651</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0.003132834921634212</v>
+        <v>0.02822638048904651</v>
       </c>
       <c r="K50" t="n">
         <v>300</v>
@@ -2315,25 +2315,25 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0.03029022053571429</v>
+        <v>0.1567600601648352</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0.03029022053571429</v>
+        <v>0.1567600601648352</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.003713096956181325</v>
+        <v>0.03103219825438517</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0.003713096956181325</v>
+        <v>0.03103219825438517</v>
       </c>
       <c r="K51" t="n">
         <v>300</v>
@@ -2719,28 +2719,28 @@
         <v>46023</v>
       </c>
       <c r="C62" t="n">
-        <v>0.4285249050239265</v>
+        <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E62" t="n">
-        <v>0.4283831017311274</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G62" t="n">
-        <v>0.4283831017311274</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4273193185478531</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K62" t="n">
         <v>0.04</v>
@@ -2756,28 +2756,28 @@
         <v>47849</v>
       </c>
       <c r="C63" t="n">
-        <v>0.8371698919142299</v>
+        <v>0.5720909640975366</v>
       </c>
       <c r="D63" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E63" t="n">
-        <v>0.8370280886214639</v>
+        <v>0.4216803319583462</v>
       </c>
       <c r="F63" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G63" t="n">
-        <v>0.8350222907167945</v>
+        <v>0.5720909640975366</v>
       </c>
       <c r="H63" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8340471982784728</v>
+        <v>0.4216803319583462</v>
       </c>
       <c r="J63" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K63" t="n">
         <v>0.04</v>
@@ -2793,28 +2793,28 @@
         <v>49675</v>
       </c>
       <c r="C64" t="n">
-        <v>0.8371698919142299</v>
+        <v>5.465095428241168</v>
       </c>
       <c r="D64" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E64" t="n">
-        <v>0.8370280886214639</v>
+        <v>5.208964280291676</v>
       </c>
       <c r="F64" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G64" t="n">
-        <v>0.8350222907167945</v>
+        <v>5.465095428241169</v>
       </c>
       <c r="H64" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8340471982784728</v>
+        <v>5.208964280291676</v>
       </c>
       <c r="J64" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K64" t="n">
         <v>0.04</v>
@@ -2830,28 +2830,28 @@
         <v>51502</v>
       </c>
       <c r="C65" t="n">
-        <v>0.5026758658272612</v>
+        <v>12.75210305814845</v>
       </c>
       <c r="D65" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E65" t="n">
-        <v>0.5026460883131121</v>
+        <v>12.75210305814845</v>
       </c>
       <c r="F65" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G65" t="n">
-        <v>0.499863076821796</v>
+        <v>12.75210305814845</v>
       </c>
       <c r="H65" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I65" t="n">
-        <v>0.499863076821796</v>
+        <v>12.75210305814845</v>
       </c>
       <c r="J65" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K65" t="n">
         <v>0.04</v>
@@ -2867,28 +2867,28 @@
         <v>53328</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4546290519369589</v>
+        <v>12.75210305814844</v>
       </c>
       <c r="D66" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E66" t="n">
-        <v>0.4545992744227766</v>
+        <v>12.75210305814844</v>
       </c>
       <c r="F66" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G66" t="n">
-        <v>0.45382206083613</v>
+        <v>12.75210305814845</v>
       </c>
       <c r="H66" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I66" t="n">
-        <v>0.4537333700911773</v>
+        <v>12.75210305814844</v>
       </c>
       <c r="J66" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K66" t="n">
         <v>0.04</v>
@@ -2907,25 +2907,25 @@
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="K67" t="n">
         <v>0.008</v>
@@ -2944,25 +2944,25 @@
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="K68" t="n">
         <v>0.008</v>
@@ -2978,28 +2978,28 @@
         <v>49675</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>0.04332084431076671</v>
       </c>
       <c r="D69" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>0.04692132372220224</v>
       </c>
       <c r="F69" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>0.04332084431076752</v>
       </c>
       <c r="H69" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>0.04692132372220077</v>
       </c>
       <c r="J69" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="K69" t="n">
         <v>0.008</v>
@@ -3015,28 +3015,28 @@
         <v>51502</v>
       </c>
       <c r="C70" t="n">
-        <v>2.156978033315449</v>
+        <v>2.398406122036903</v>
       </c>
       <c r="D70" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="E70" t="n">
-        <v>2.156978033315449</v>
+        <v>2.402006601448339</v>
       </c>
       <c r="F70" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="G70" t="n">
-        <v>2.156978033315449</v>
+        <v>2.398406122036905</v>
       </c>
       <c r="H70" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="I70" t="n">
-        <v>2.156978033315449</v>
+        <v>2.402006601448337</v>
       </c>
       <c r="J70" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="K70" t="n">
         <v>0.008</v>
@@ -3052,28 +3052,28 @@
         <v>53328</v>
       </c>
       <c r="C71" t="n">
-        <v>2.156978033315449</v>
+        <v>2.398406122036903</v>
       </c>
       <c r="D71" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="E71" t="n">
-        <v>2.156978033315449</v>
+        <v>2.402006601448339</v>
       </c>
       <c r="F71" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="G71" t="n">
-        <v>2.156978033315449</v>
+        <v>2.398406122036905</v>
       </c>
       <c r="H71" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="I71" t="n">
-        <v>2.156978033315449</v>
+        <v>2.402006601448337</v>
       </c>
       <c r="J71" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="K71" t="n">
         <v>0.008</v>
@@ -3092,25 +3092,25 @@
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K72" t="n">
         <v>0.04</v>
@@ -3129,25 +3129,25 @@
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K73" t="n">
         <v>0.04</v>
@@ -3166,25 +3166,25 @@
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K74" t="n">
         <v>0.04</v>
@@ -3203,25 +3203,25 @@
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K75" t="n">
         <v>0.04</v>
@@ -3240,25 +3240,25 @@
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K76" t="n">
         <v>0.04</v>
@@ -3277,25 +3277,25 @@
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="K77" t="n">
         <v>0.008</v>
@@ -3314,25 +3314,25 @@
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="K78" t="n">
         <v>0.008</v>
@@ -3351,25 +3351,25 @@
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="K79" t="n">
         <v>0.008</v>
@@ -3388,25 +3388,25 @@
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="K80" t="n">
         <v>0.008</v>
@@ -3425,25 +3425,25 @@
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="K81" t="n">
         <v>0.008</v>
@@ -3462,25 +3462,25 @@
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K82" t="n">
         <v>0.04</v>
@@ -3499,25 +3499,25 @@
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K83" t="n">
         <v>0.04</v>
@@ -3536,25 +3536,25 @@
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K84" t="n">
         <v>0.04</v>
@@ -3573,25 +3573,25 @@
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K85" t="n">
         <v>0.04</v>
@@ -3610,25 +3610,25 @@
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K86" t="n">
         <v>0.04</v>
@@ -3647,25 +3647,25 @@
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="K87" t="n">
         <v>0.008</v>
@@ -3684,25 +3684,25 @@
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="K88" t="n">
         <v>0.008</v>
@@ -3721,25 +3721,25 @@
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="K89" t="n">
         <v>0.008</v>
@@ -3758,25 +3758,25 @@
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="K90" t="n">
         <v>0.008</v>
@@ -3795,25 +3795,25 @@
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="K91" t="n">
         <v>0.008</v>
@@ -3832,25 +3832,25 @@
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K92" t="n">
         <v>0.04</v>
@@ -3869,25 +3869,25 @@
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K93" t="n">
         <v>0.04</v>
@@ -3906,25 +3906,25 @@
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K94" t="n">
         <v>0.04</v>
@@ -3943,25 +3943,25 @@
         <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K95" t="n">
         <v>0.04</v>
@@ -3980,25 +3980,25 @@
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K96" t="n">
         <v>0.04</v>
@@ -4017,25 +4017,25 @@
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="K97" t="n">
         <v>0.008</v>
@@ -4054,25 +4054,25 @@
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="K98" t="n">
         <v>0.008</v>
@@ -4091,25 +4091,25 @@
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="K99" t="n">
         <v>0.008</v>
@@ -4128,25 +4128,25 @@
         <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="K100" t="n">
         <v>0.008</v>
@@ -4165,25 +4165,25 @@
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="K101" t="n">
         <v>0.008</v>
@@ -4202,25 +4202,25 @@
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K102" t="n">
         <v>0.04</v>
@@ -4239,25 +4239,25 @@
         <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I103" t="n">
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K103" t="n">
         <v>0.04</v>
@@ -4276,25 +4276,25 @@
         <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I104" t="n">
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K104" t="n">
         <v>0.04</v>
@@ -4313,25 +4313,25 @@
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E105" t="n">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K105" t="n">
         <v>0.04</v>
@@ -4350,25 +4350,25 @@
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>4.470300525600001</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K106" t="n">
         <v>0.04</v>
@@ -4387,25 +4387,25 @@
         <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="E107" t="n">
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="K107" t="n">
         <v>0.008</v>
@@ -4424,25 +4424,25 @@
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="E108" t="n">
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="I108" t="n">
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="K108" t="n">
         <v>0.008</v>
@@ -4461,25 +4461,25 @@
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="E109" t="n">
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="I109" t="n">
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="K109" t="n">
         <v>0.008</v>
@@ -4498,25 +4498,25 @@
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="E110" t="n">
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="I110" t="n">
         <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="K110" t="n">
         <v>0.008</v>
@@ -4535,25 +4535,25 @@
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="E111" t="n">
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>70.382286072</v>
+        <v>111.621575016</v>
       </c>
       <c r="K111" t="n">
         <v>0.008</v>
@@ -4572,13 +4572,13 @@
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>19.24846222160268</v>
+        <v>0.1191671853885055</v>
       </c>
       <c r="E112" t="n">
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>19.24846222160268</v>
+        <v>0.1191671853885055</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -4606,16 +4606,16 @@
         <v>47849</v>
       </c>
       <c r="C113" t="n">
-        <v>0.9518352754008268</v>
+        <v>0.1191671853885055</v>
       </c>
       <c r="D113" t="n">
-        <v>19.24846222160268</v>
+        <v>0.1191671853885055</v>
       </c>
       <c r="E113" t="n">
-        <v>0.9518352754008268</v>
+        <v>0.1191671853885055</v>
       </c>
       <c r="F113" t="n">
-        <v>19.24846222160268</v>
+        <v>0.1191671853885055</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -4643,16 +4643,16 @@
         <v>49675</v>
       </c>
       <c r="C114" t="n">
-        <v>2.457302264702742</v>
+        <v>0.1191671853885055</v>
       </c>
       <c r="D114" t="n">
-        <v>19.24846222160268</v>
+        <v>0.1191671853885055</v>
       </c>
       <c r="E114" t="n">
-        <v>2.462129022715714</v>
+        <v>0.1191671853885055</v>
       </c>
       <c r="F114" t="n">
-        <v>19.24846222160268</v>
+        <v>0.1191671853885055</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -4680,16 +4680,16 @@
         <v>51502</v>
       </c>
       <c r="C115" t="n">
-        <v>9.490291696759236</v>
+        <v>0.1191671853885055</v>
       </c>
       <c r="D115" t="n">
-        <v>19.24846222160268</v>
+        <v>0.1191671853885055</v>
       </c>
       <c r="E115" t="n">
-        <v>9.490289205800256</v>
+        <v>0.1191671853885055</v>
       </c>
       <c r="F115" t="n">
-        <v>19.24846222160268</v>
+        <v>0.1191671853885055</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -4717,16 +4717,16 @@
         <v>53328</v>
       </c>
       <c r="C116" t="n">
-        <v>9.694411338198092</v>
+        <v>0.1191671853885055</v>
       </c>
       <c r="D116" t="n">
-        <v>19.24846222160268</v>
+        <v>0.1191671853885055</v>
       </c>
       <c r="E116" t="n">
-        <v>9.694408793662921</v>
+        <v>0.1191671853885055</v>
       </c>
       <c r="F116" t="n">
-        <v>19.24846222160268</v>
+        <v>0.1191671853885055</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -4757,25 +4757,25 @@
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>265.5568819273586</v>
+        <v>408.2479934734613</v>
       </c>
       <c r="E117" t="n">
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>265.5568819273586</v>
+        <v>408.2479934734613</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>146.14775294066</v>
+        <v>245.0708881712023</v>
       </c>
       <c r="I117" t="n">
         <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>146.14775294066</v>
+        <v>245.0708881712023</v>
       </c>
       <c r="K117" t="n">
         <v>0.01</v>
@@ -4794,25 +4794,25 @@
         <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>265.5568819273586</v>
+        <v>408.2479934734613</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>265.5568819273586</v>
+        <v>408.2479934734613</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>195.9362286536411</v>
+        <v>293.6728799384529</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>195.9362286536411</v>
+        <v>293.6728799384529</v>
       </c>
       <c r="K118" t="n">
         <v>0.01</v>
@@ -4831,25 +4831,25 @@
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>265.5568819273586</v>
+        <v>408.2479934734613</v>
       </c>
       <c r="E119" t="n">
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>265.5568819273586</v>
+        <v>408.2479934734613</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>220.0614813359284</v>
+        <v>313.6885407026189</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>220.0614813359284</v>
+        <v>313.6885407026189</v>
       </c>
       <c r="K119" t="n">
         <v>0.01</v>
@@ -4868,25 +4868,25 @@
         <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>265.5568819273586</v>
+        <v>408.2479934734613</v>
       </c>
       <c r="E120" t="n">
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>265.5568819273586</v>
+        <v>408.2479934734613</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>233.3262203850576</v>
+        <v>324.5386626470429</v>
       </c>
       <c r="I120" t="n">
         <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>233.3262203850576</v>
+        <v>324.5386626470429</v>
       </c>
       <c r="K120" t="n">
         <v>0.01</v>
@@ -4905,25 +4905,25 @@
         <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>265.5568819273586</v>
+        <v>408.2479934734613</v>
       </c>
       <c r="E121" t="n">
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>265.5568819273586</v>
+        <v>408.2479934734613</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>241.3250919862749</v>
+        <v>331.4339421130536</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>241.3250919862749</v>
+        <v>331.4339421130536</v>
       </c>
       <c r="K121" t="n">
         <v>0.01</v>
@@ -4942,25 +4942,25 @@
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>12.89437269088045</v>
+        <v>172.0646688421795</v>
       </c>
       <c r="E122" t="n">
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>12.89437269088045</v>
+        <v>172.0646688421795</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>6.98212132639982</v>
+        <v>109.1637891589338</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>6.98212132639982</v>
+        <v>109.1637891589338</v>
       </c>
       <c r="K122" t="n">
         <v>0.03</v>
@@ -4979,25 +4979,25 @@
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>12.89437269088045</v>
+        <v>172.0646688421795</v>
       </c>
       <c r="E123" t="n">
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>12.89437269088045</v>
+        <v>172.0646688421795</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>9.447276092768421</v>
+        <v>127.8986970423353</v>
       </c>
       <c r="I123" t="n">
         <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>9.447276092768421</v>
+        <v>127.8986970423353</v>
       </c>
       <c r="K123" t="n">
         <v>0.03</v>
@@ -5016,25 +5016,25 @@
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>12.89437269088045</v>
+        <v>172.0646688421795</v>
       </c>
       <c r="E124" t="n">
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>12.89437269088045</v>
+        <v>172.0646688421795</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>10.64177905330155</v>
+        <v>135.6142565699748</v>
       </c>
       <c r="I124" t="n">
         <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>10.64177905330155</v>
+        <v>135.6142565699748</v>
       </c>
       <c r="K124" t="n">
         <v>0.03</v>
@@ -5053,25 +5053,25 @@
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>12.89437269088045</v>
+        <v>172.0646688421795</v>
       </c>
       <c r="E125" t="n">
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>12.89437269088045</v>
+        <v>172.0646688421795</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>11.29855020813871</v>
+        <v>139.7967196288124</v>
       </c>
       <c r="I125" t="n">
         <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>11.29855020813871</v>
+        <v>139.7967196288124</v>
       </c>
       <c r="K125" t="n">
         <v>0.03</v>
@@ -5090,25 +5090,25 @@
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>12.89437269088045</v>
+        <v>172.0646688421795</v>
       </c>
       <c r="E126" t="n">
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>12.89437269088045</v>
+        <v>172.0646688421795</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>11.69459479819572</v>
+        <v>142.4546852991219</v>
       </c>
       <c r="I126" t="n">
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>11.69459479819572</v>
+        <v>142.4546852991219</v>
       </c>
       <c r="K126" t="n">
         <v>0.03</v>
@@ -5117,7 +5117,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>RE_WT_s_3.3 MW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
@@ -5127,145 +5127,145 @@
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>0.6060606060606061</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E127" t="n">
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>0.6060606060606061</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>0</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="K127" t="n">
-        <v>3.3</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>RE_WT_s_3.3 MW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C128" t="n">
-        <v>0</v>
+        <v>3.34944850319345</v>
       </c>
       <c r="D128" t="n">
-        <v>0.6060606060606061</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E128" t="n">
-        <v>0</v>
+        <v>17.92036485449546</v>
       </c>
       <c r="F128" t="n">
-        <v>0.6060606060606061</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>3.349448503193331</v>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>17.92036485449547</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="K128" t="n">
-        <v>3.3</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>RE_WT_s_3.3 MW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B129" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>3.34944850319345</v>
       </c>
       <c r="D129" t="n">
-        <v>0.6060606060606061</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E129" t="n">
-        <v>0</v>
+        <v>18.0215590373562</v>
       </c>
       <c r="F129" t="n">
-        <v>0.6060606060606061</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>3.349448503193331</v>
       </c>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="I129" t="n">
-        <v>0</v>
+        <v>18.0215590373562</v>
       </c>
       <c r="J129" t="n">
-        <v>0</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="K129" t="n">
-        <v>3.3</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>RE_WT_s_3.3 MW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B130" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C130" t="n">
-        <v>0</v>
+        <v>3.34944850319345</v>
       </c>
       <c r="D130" t="n">
-        <v>0.6060606060606061</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E130" t="n">
-        <v>0</v>
+        <v>18.0215590373562</v>
       </c>
       <c r="F130" t="n">
-        <v>0.6060606060606061</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>3.349448503193331</v>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="I130" t="n">
-        <v>0</v>
+        <v>18.0215590373562</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="K130" t="n">
-        <v>3.3</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>RE_WT_s_3.3 MW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B131" s="2" t="n">
@@ -5275,34 +5275,34 @@
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>0.6060606060606061</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E131" t="n">
-        <v>0</v>
+        <v>0.1011941828607345</v>
       </c>
       <c r="F131" t="n">
-        <v>0.6060606060606061</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="I131" t="n">
-        <v>0</v>
+        <v>0.1011941828607345</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="K131" t="n">
-        <v>3.3</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B132" s="2" t="n">
@@ -5312,34 +5312,34 @@
         <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E132" t="n">
-        <v>0.2121776417932261</v>
+        <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="I132" t="n">
-        <v>0.2121776417932293</v>
+        <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="K132" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B133" s="2" t="n">
@@ -5349,145 +5349,145 @@
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E133" t="n">
-        <v>0.2121776417932261</v>
+        <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2121776417932293</v>
+        <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="K133" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B134" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C134" t="n">
-        <v>0</v>
+        <v>0.5081714412488159</v>
       </c>
       <c r="D134" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E134" t="n">
-        <v>0.2941538065981599</v>
+        <v>2.7343000445237</v>
       </c>
       <c r="F134" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>0.5081714412488149</v>
       </c>
       <c r="H134" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="I134" t="n">
-        <v>0.294153806598164</v>
+        <v>2.734300044523696</v>
       </c>
       <c r="J134" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="K134" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B135" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C135" t="n">
-        <v>0</v>
+        <v>0.5081714412488159</v>
       </c>
       <c r="D135" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E135" t="n">
-        <v>0.08197616480493385</v>
+        <v>2.7343000445237</v>
       </c>
       <c r="F135" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>0.5081714412488149</v>
       </c>
       <c r="H135" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="I135" t="n">
-        <v>0.08197616480493471</v>
+        <v>2.734300044523696</v>
       </c>
       <c r="J135" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="K135" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B136" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>0.5081714412488159</v>
       </c>
       <c r="D136" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E136" t="n">
-        <v>0.08197616480493385</v>
+        <v>2.7343000445237</v>
       </c>
       <c r="F136" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>0.5081714412488149</v>
       </c>
       <c r="H136" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="I136" t="n">
-        <v>0.08197616480493471</v>
+        <v>2.734300044523696</v>
       </c>
       <c r="J136" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="K136" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B137" s="2" t="n">
@@ -5497,182 +5497,182 @@
         <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E137" t="n">
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>24.58434289929532</v>
+        <v>247.4515096086553</v>
       </c>
       <c r="I137" t="n">
         <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>24.58434289929532</v>
+        <v>247.4515096086553</v>
       </c>
       <c r="K137" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B138" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C138" t="n">
-        <v>0.2261354984775276</v>
+        <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E138" t="n">
-        <v>0.2365368956604269</v>
+        <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G138" t="n">
-        <v>0.2271255434058661</v>
+        <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>24.58434289929532</v>
+        <v>318.6220023864096</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2360739630188868</v>
+        <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>24.58434289929532</v>
+        <v>318.6220023864096</v>
       </c>
       <c r="K138" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B139" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C139" t="n">
-        <v>0.3802797699120732</v>
+        <v>134.9610879995077</v>
       </c>
       <c r="D139" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E139" t="n">
-        <v>0.4825616337922581</v>
+        <v>128.3457928130431</v>
       </c>
       <c r="F139" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G139" t="n">
-        <v>0.3787847055919699</v>
+        <v>134.9610879995078</v>
       </c>
       <c r="H139" t="n">
-        <v>24.58434289929532</v>
+        <v>350.3390766016955</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4562807230230681</v>
+        <v>128.3457928130431</v>
       </c>
       <c r="J139" t="n">
-        <v>24.58434289929532</v>
+        <v>350.3390766016955</v>
       </c>
       <c r="K139" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B140" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C140" t="n">
-        <v>0.3802797699120732</v>
+        <v>167.7989381927821</v>
       </c>
       <c r="D140" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E140" t="n">
-        <v>0.4825616337922581</v>
+        <v>162.8208749881784</v>
       </c>
       <c r="F140" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G140" t="n">
-        <v>0.3787847055919699</v>
+        <v>167.7989381927822</v>
       </c>
       <c r="H140" t="n">
-        <v>24.58434289929532</v>
+        <v>367.4560928344465</v>
       </c>
       <c r="I140" t="n">
-        <v>0.4562807230230681</v>
+        <v>162.8208749881783</v>
       </c>
       <c r="J140" t="n">
-        <v>24.58434289929532</v>
+        <v>367.4560928344465</v>
       </c>
       <c r="K140" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B141" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C141" t="n">
-        <v>0.1541442714345456</v>
+        <v>182.4354965458602</v>
       </c>
       <c r="D141" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E141" t="n">
-        <v>0.2460247381318313</v>
+        <v>169.2415278060546</v>
       </c>
       <c r="F141" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G141" t="n">
-        <v>0.1516591621861038</v>
+        <v>182.4354965458602</v>
       </c>
       <c r="H141" t="n">
-        <v>24.58434289929532</v>
+        <v>378.0225365637701</v>
       </c>
       <c r="I141" t="n">
-        <v>0.2202067600041814</v>
+        <v>169.2415278060546</v>
       </c>
       <c r="J141" t="n">
-        <v>24.58434289929532</v>
+        <v>378.0225365637701</v>
       </c>
       <c r="K141" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B142" s="2" t="n">
@@ -5682,34 +5682,34 @@
         <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E142" t="n">
         <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
       </c>
       <c r="H142" t="n">
-        <v>146.7056153048075</v>
+        <v>104.3219211043365</v>
       </c>
       <c r="I142" t="n">
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>146.7056153048075</v>
+        <v>104.3219211043365</v>
       </c>
       <c r="K142" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B143" s="2" t="n">
@@ -5719,330 +5719,330 @@
         <v>0</v>
       </c>
       <c r="D143" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E143" t="n">
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>218.6411790307994</v>
+        <v>130.3840765833794</v>
       </c>
       <c r="I143" t="n">
         <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>218.6411790307994</v>
+        <v>130.3840765833794</v>
       </c>
       <c r="K143" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B144" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C144" t="n">
-        <v>83.11847781917876</v>
+        <v>49.15790618822192</v>
       </c>
       <c r="D144" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E144" t="n">
-        <v>88.25146084026098</v>
+        <v>47.56605966096768</v>
       </c>
       <c r="F144" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G144" t="n">
-        <v>83.03387907435497</v>
+        <v>49.15790618822192</v>
       </c>
       <c r="H144" t="n">
-        <v>266.8200082731564</v>
+        <v>141.9986557056627</v>
       </c>
       <c r="I144" t="n">
-        <v>88.40188282604353</v>
+        <v>47.56605966096768</v>
       </c>
       <c r="J144" t="n">
-        <v>266.8200082731564</v>
+        <v>141.9986557056627</v>
       </c>
       <c r="K144" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B145" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C145" t="n">
-        <v>137.4965700659751</v>
+        <v>63.92297824658233</v>
       </c>
       <c r="D145" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E145" t="n">
-        <v>135.0827088855115</v>
+        <v>63.28300450181493</v>
       </c>
       <c r="F145" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G145" t="n">
-        <v>137.3489528492098</v>
+        <v>63.92297824658233</v>
       </c>
       <c r="H145" t="n">
-        <v>300.7886739307696</v>
+        <v>148.2667918528765</v>
       </c>
       <c r="I145" t="n">
-        <v>135.0831563012655</v>
+        <v>63.28300450181493</v>
       </c>
       <c r="J145" t="n">
-        <v>300.7886739307696</v>
+        <v>148.2667918528765</v>
       </c>
       <c r="K145" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B146" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C146" t="n">
-        <v>137.4965700659751</v>
+        <v>65.81529390877152</v>
       </c>
       <c r="D146" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E146" t="n">
-        <v>135.0827088855115</v>
+        <v>63.76201717990671</v>
       </c>
       <c r="F146" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G146" t="n">
-        <v>137.3489528492098</v>
+        <v>65.81529390877152</v>
       </c>
       <c r="H146" t="n">
-        <v>325.7388167399461</v>
+        <v>152.1361524345734</v>
       </c>
       <c r="I146" t="n">
-        <v>135.0831563012655</v>
+        <v>63.76201717990671</v>
       </c>
       <c r="J146" t="n">
-        <v>325.7388167399461</v>
+        <v>152.1361524345734</v>
       </c>
       <c r="K146" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B147" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C147" t="n">
-        <v>0.002004806806213684</v>
+        <v>0</v>
       </c>
       <c r="D147" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E147" t="n">
-        <v>0.05013133668662601</v>
+        <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G147" t="n">
-        <v>0.02505216113119287</v>
+        <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>6.134106096981654</v>
+        <v>247.4515096086553</v>
       </c>
       <c r="I147" t="n">
-        <v>0.050131336686626</v>
+        <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>6.134106096981654</v>
+        <v>247.4515096086553</v>
       </c>
       <c r="K147" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B148" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C148" t="n">
-        <v>2.474082408075044</v>
+        <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E148" t="n">
-        <v>2.733923597836654</v>
+        <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G148" t="n">
-        <v>2.411924539313729</v>
+        <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>9.405348018312193</v>
+        <v>318.6220023864096</v>
       </c>
       <c r="I148" t="n">
-        <v>2.733969817043408</v>
+        <v>0</v>
       </c>
       <c r="J148" t="n">
-        <v>9.405348018312193</v>
+        <v>318.6220023864096</v>
       </c>
       <c r="K148" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B149" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C149" t="n">
-        <v>5.557041341382663</v>
+        <v>0</v>
       </c>
       <c r="D149" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E149" t="n">
-        <v>5.801171567977478</v>
+        <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G149" t="n">
-        <v>5.49705434242902</v>
+        <v>0</v>
       </c>
       <c r="H149" t="n">
-        <v>11.5962616328708</v>
+        <v>350.3390766016955</v>
       </c>
       <c r="I149" t="n">
-        <v>5.82001020125486</v>
+        <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>11.5962616328708</v>
+        <v>350.3390766016955</v>
       </c>
       <c r="K149" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B150" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C150" t="n">
-        <v>5.95676295216092</v>
+        <v>0</v>
       </c>
       <c r="D150" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E150" t="n">
-        <v>6.172197610429166</v>
+        <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G150" t="n">
-        <v>5.867264943458535</v>
+        <v>0</v>
       </c>
       <c r="H150" t="n">
-        <v>13.14097355775553</v>
+        <v>367.4560928344465</v>
       </c>
       <c r="I150" t="n">
-        <v>6.176309168442729</v>
+        <v>0</v>
       </c>
       <c r="J150" t="n">
-        <v>13.14097355775553</v>
+        <v>367.4560928344465</v>
       </c>
       <c r="K150" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B151" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C151" t="n">
-        <v>6.21667488103452</v>
+        <v>0</v>
       </c>
       <c r="D151" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E151" t="n">
-        <v>6.160618490564987</v>
+        <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G151" t="n">
-        <v>6.221876905855162</v>
+        <v>0</v>
       </c>
       <c r="H151" t="n">
-        <v>14.27557164628169</v>
+        <v>378.0225365637701</v>
       </c>
       <c r="I151" t="n">
-        <v>6.15589320965017</v>
+        <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>14.27557164628169</v>
+        <v>378.0225365637701</v>
       </c>
       <c r="K151" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B152" s="2" t="n">
@@ -6052,34 +6052,34 @@
         <v>0</v>
       </c>
       <c r="D152" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E152" t="n">
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>146.7056153048075</v>
+        <v>104.3219211043365</v>
       </c>
       <c r="I152" t="n">
         <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>146.7056153048075</v>
+        <v>104.3219211043365</v>
       </c>
       <c r="K152" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B153" s="2" t="n">
@@ -6089,34 +6089,34 @@
         <v>0</v>
       </c>
       <c r="D153" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E153" t="n">
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>218.6411790307994</v>
+        <v>130.3840765833794</v>
       </c>
       <c r="I153" t="n">
         <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>218.6411790307994</v>
+        <v>130.3840765833794</v>
       </c>
       <c r="K153" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B154" s="2" t="n">
@@ -6126,34 +6126,34 @@
         <v>0</v>
       </c>
       <c r="D154" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E154" t="n">
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
       </c>
       <c r="H154" t="n">
-        <v>266.8200082731564</v>
+        <v>141.9986557056627</v>
       </c>
       <c r="I154" t="n">
         <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>266.8200082731564</v>
+        <v>141.9986557056627</v>
       </c>
       <c r="K154" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B155" s="2" t="n">
@@ -6163,34 +6163,34 @@
         <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E155" t="n">
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>300.7886739307696</v>
+        <v>148.2667918528765</v>
       </c>
       <c r="I155" t="n">
         <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>300.7886739307696</v>
+        <v>148.2667918528765</v>
       </c>
       <c r="K155" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B156" s="2" t="n">
@@ -6200,34 +6200,34 @@
         <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>325.7388167399461</v>
+        <v>152.1361524345734</v>
       </c>
       <c r="I156" t="n">
         <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>325.7388167399461</v>
+        <v>152.1361524345734</v>
       </c>
       <c r="K156" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B157" s="2" t="n">
@@ -6237,34 +6237,34 @@
         <v>0</v>
       </c>
       <c r="D157" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E157" t="n">
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>6.134106096981654</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>6.134106096981654</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="K157" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B158" s="2" t="n">
@@ -6274,330 +6274,330 @@
         <v>0</v>
       </c>
       <c r="D158" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E158" t="n">
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>9.405348018312193</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="I158" t="n">
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>9.405348018312193</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="K158" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B159" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C159" t="n">
-        <v>0</v>
+        <v>91.94088229596224</v>
       </c>
       <c r="D159" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E159" t="n">
-        <v>0</v>
+        <v>98.08404054001248</v>
       </c>
       <c r="F159" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>91.94088229596213</v>
       </c>
       <c r="H159" t="n">
-        <v>11.5962616328708</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="I159" t="n">
-        <v>0</v>
+        <v>98.08404054001259</v>
       </c>
       <c r="J159" t="n">
-        <v>11.5962616328708</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="K159" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B160" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C160" t="n">
-        <v>0</v>
+        <v>98.27067454516778</v>
       </c>
       <c r="D160" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E160" t="n">
-        <v>0</v>
+        <v>100.6013494594263</v>
       </c>
       <c r="F160" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>98.27067454516778</v>
       </c>
       <c r="H160" t="n">
-        <v>13.14097355775553</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="I160" t="n">
-        <v>0</v>
+        <v>100.6013494594263</v>
       </c>
       <c r="J160" t="n">
-        <v>13.14097355775553</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="K160" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B161" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C161" t="n">
-        <v>0</v>
+        <v>104.1608299065391</v>
       </c>
       <c r="D161" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E161" t="n">
-        <v>0</v>
+        <v>119.1264998400339</v>
       </c>
       <c r="F161" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>104.1608299065391</v>
       </c>
       <c r="H161" t="n">
-        <v>14.27557164628169</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="I161" t="n">
-        <v>0</v>
+        <v>119.1264998400339</v>
       </c>
       <c r="J161" t="n">
-        <v>14.27557164628169</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="K161" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B162" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C162" t="n">
-        <v>39.59728786117897</v>
+        <v>0</v>
       </c>
       <c r="D162" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E162" t="n">
-        <v>47.8543316979744</v>
+        <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G162" t="n">
-        <v>39.59728786117897</v>
+        <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="I162" t="n">
-        <v>47.85433169797439</v>
+        <v>0</v>
       </c>
       <c r="J162" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="K162" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B163" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C163" t="n">
-        <v>39.59728786117897</v>
+        <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E163" t="n">
-        <v>47.8543316979744</v>
+        <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G163" t="n">
-        <v>39.59728786117897</v>
+        <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="I163" t="n">
-        <v>47.85433169797439</v>
+        <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="K163" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B164" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C164" t="n">
-        <v>71.75129840733827</v>
+        <v>31.61809716730435</v>
       </c>
       <c r="D164" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E164" t="n">
-        <v>74.38500477712547</v>
+        <v>32.52006418480708</v>
       </c>
       <c r="F164" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G164" t="n">
-        <v>71.71956197435875</v>
+        <v>31.61809716730435</v>
       </c>
       <c r="H164" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="I164" t="n">
-        <v>74.69601385550129</v>
+        <v>32.52006418480708</v>
       </c>
       <c r="J164" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="K164" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B165" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C165" t="n">
-        <v>73.48511640622674</v>
+        <v>41.59206472065583</v>
       </c>
       <c r="D165" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E165" t="n">
-        <v>74.66170808015809</v>
+        <v>41.6514941696421</v>
       </c>
       <c r="F165" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G165" t="n">
-        <v>73.95054330755171</v>
+        <v>41.59206472065583</v>
       </c>
       <c r="H165" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="I165" t="n">
-        <v>74.63605658928228</v>
+        <v>41.6514941696421</v>
       </c>
       <c r="J165" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="K165" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B166" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C166" t="n">
-        <v>73.48511640622677</v>
+        <v>41.86820285275004</v>
       </c>
       <c r="D166" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E166" t="n">
-        <v>74.71423671798929</v>
+        <v>43.90678153607401</v>
       </c>
       <c r="F166" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G166" t="n">
-        <v>73.9505433075517</v>
+        <v>41.86820285275004</v>
       </c>
       <c r="H166" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="I166" t="n">
-        <v>74.68858522711346</v>
+        <v>43.90678153607402</v>
       </c>
       <c r="J166" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="K166" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B167" s="2" t="n">
@@ -6607,182 +6607,182 @@
         <v>0</v>
       </c>
       <c r="D167" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E167" t="n">
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="I167" t="n">
         <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="K167" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B168" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C168" t="n">
-        <v>0.02977653854697432</v>
+        <v>0</v>
       </c>
       <c r="D168" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E168" t="n">
-        <v>0.02977737867431036</v>
+        <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G168" t="n">
-        <v>0.02751219859073388</v>
+        <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="I168" t="n">
-        <v>0.02752624896539657</v>
+        <v>0</v>
       </c>
       <c r="J168" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="K168" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B169" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C169" t="n">
-        <v>2.967718325364301</v>
+        <v>0</v>
       </c>
       <c r="D169" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E169" t="n">
-        <v>2.956100977482098</v>
+        <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G169" t="n">
-        <v>2.965768224848834</v>
+        <v>0</v>
       </c>
       <c r="H169" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="I169" t="n">
-        <v>2.960875411830202</v>
+        <v>0</v>
       </c>
       <c r="J169" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="K169" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B170" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C170" t="n">
-        <v>3.446156620345086</v>
+        <v>0</v>
       </c>
       <c r="D170" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E170" t="n">
-        <v>3.414089625963657</v>
+        <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G170" t="n">
-        <v>3.430683773463028</v>
+        <v>0</v>
       </c>
       <c r="H170" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="I170" t="n">
-        <v>3.411838496254744</v>
+        <v>0</v>
       </c>
       <c r="J170" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="K170" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B171" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C171" t="n">
-        <v>3.846519619733094</v>
+        <v>0</v>
       </c>
       <c r="D171" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E171" t="n">
-        <v>3.908230379620092</v>
+        <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G171" t="n">
-        <v>3.821442015738854</v>
+        <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="I171" t="n">
-        <v>3.888535178070369</v>
+        <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="K171" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B172" s="2" t="n">
@@ -6792,34 +6792,34 @@
         <v>0</v>
       </c>
       <c r="D172" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E172" t="n">
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
       </c>
       <c r="H172" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="I172" t="n">
         <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="K172" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B173" s="2" t="n">
@@ -6829,34 +6829,34 @@
         <v>0</v>
       </c>
       <c r="D173" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E173" t="n">
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
       </c>
       <c r="H173" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="I173" t="n">
         <v>0</v>
       </c>
       <c r="J173" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="K173" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B174" s="2" t="n">
@@ -6866,34 +6866,34 @@
         <v>0</v>
       </c>
       <c r="D174" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E174" t="n">
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
       </c>
       <c r="H174" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="I174" t="n">
         <v>0</v>
       </c>
       <c r="J174" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="K174" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B175" s="2" t="n">
@@ -6903,34 +6903,34 @@
         <v>0</v>
       </c>
       <c r="D175" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E175" t="n">
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
       </c>
       <c r="H175" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="I175" t="n">
         <v>0</v>
       </c>
       <c r="J175" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="K175" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B176" s="2" t="n">
@@ -6940,34 +6940,34 @@
         <v>0</v>
       </c>
       <c r="D176" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E176" t="n">
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="I176" t="n">
         <v>0</v>
       </c>
       <c r="J176" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="K176" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B177" s="2" t="n">
@@ -6977,34 +6977,34 @@
         <v>0</v>
       </c>
       <c r="D177" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E177" t="n">
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>24.58434289929532</v>
+        <v>44.11202657958206</v>
       </c>
       <c r="I177" t="n">
         <v>0</v>
       </c>
       <c r="J177" t="n">
-        <v>24.58434289929532</v>
+        <v>44.11202657958206</v>
       </c>
       <c r="K177" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B178" s="2" t="n">
@@ -7014,34 +7014,34 @@
         <v>0</v>
       </c>
       <c r="D178" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E178" t="n">
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
       </c>
       <c r="H178" t="n">
-        <v>24.58434289929532</v>
+        <v>56.32317648042529</v>
       </c>
       <c r="I178" t="n">
         <v>0</v>
       </c>
       <c r="J178" t="n">
-        <v>24.58434289929532</v>
+        <v>56.32317648042529</v>
       </c>
       <c r="K178" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B179" s="2" t="n">
@@ -7051,34 +7051,34 @@
         <v>0</v>
       </c>
       <c r="D179" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E179" t="n">
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
       </c>
       <c r="H179" t="n">
-        <v>24.58434289929532</v>
+        <v>64.37357229752645</v>
       </c>
       <c r="I179" t="n">
         <v>0</v>
       </c>
       <c r="J179" t="n">
-        <v>24.58434289929532</v>
+        <v>64.37357229752645</v>
       </c>
       <c r="K179" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B180" s="2" t="n">
@@ -7088,34 +7088,34 @@
         <v>0</v>
       </c>
       <c r="D180" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
       </c>
       <c r="H180" t="n">
-        <v>24.58434289929532</v>
+        <v>70.23571266572199</v>
       </c>
       <c r="I180" t="n">
         <v>0</v>
       </c>
       <c r="J180" t="n">
-        <v>24.58434289929532</v>
+        <v>70.23571266572199</v>
       </c>
       <c r="K180" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B181" s="2" t="n">
@@ -7125,34 +7125,34 @@
         <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E181" t="n">
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>24.58434289929532</v>
+        <v>74.77346264547654</v>
       </c>
       <c r="I181" t="n">
         <v>0</v>
       </c>
       <c r="J181" t="n">
-        <v>24.58434289929532</v>
+        <v>74.77346264547654</v>
       </c>
       <c r="K181" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B182" s="2" t="n">
@@ -7162,34 +7162,34 @@
         <v>0</v>
       </c>
       <c r="D182" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E182" t="n">
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
       </c>
       <c r="H182" t="n">
-        <v>64.10204165540358</v>
+        <v>29.86037089025183</v>
       </c>
       <c r="I182" t="n">
         <v>0</v>
       </c>
       <c r="J182" t="n">
-        <v>64.10204165540358</v>
+        <v>29.86037089025183</v>
       </c>
       <c r="K182" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B183" s="2" t="n">
@@ -7199,34 +7199,34 @@
         <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E183" t="n">
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
       </c>
       <c r="H183" t="n">
-        <v>89.06458097131986</v>
+        <v>34.33201180311551</v>
       </c>
       <c r="I183" t="n">
         <v>0</v>
       </c>
       <c r="J183" t="n">
-        <v>89.06458097131986</v>
+        <v>34.33201180311551</v>
       </c>
       <c r="K183" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B184" s="2" t="n">
@@ -7236,34 +7236,34 @@
         <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E184" t="n">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
       </c>
       <c r="H184" t="n">
-        <v>109.4032782230057</v>
+        <v>37.280012572315</v>
       </c>
       <c r="I184" t="n">
         <v>0</v>
       </c>
       <c r="J184" t="n">
-        <v>109.4032782230057</v>
+        <v>37.280012572315</v>
       </c>
       <c r="K184" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B185" s="2" t="n">
@@ -7273,34 +7273,34 @@
         <v>0</v>
       </c>
       <c r="D185" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E185" t="n">
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
       </c>
       <c r="H185" t="n">
-        <v>126.4499170226973</v>
+        <v>39.42668892304613</v>
       </c>
       <c r="I185" t="n">
         <v>0</v>
       </c>
       <c r="J185" t="n">
-        <v>126.4499170226973</v>
+        <v>39.42668892304613</v>
       </c>
       <c r="K185" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B186" s="2" t="n">
@@ -7310,34 +7310,34 @@
         <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E186" t="n">
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
       </c>
       <c r="H186" t="n">
-        <v>141.0167308443426</v>
+        <v>41.0883824266543</v>
       </c>
       <c r="I186" t="n">
         <v>0</v>
       </c>
       <c r="J186" t="n">
-        <v>141.0167308443426</v>
+        <v>41.0883824266543</v>
       </c>
       <c r="K186" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B187" s="2" t="n">
@@ -7347,145 +7347,145 @@
         <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E187" t="n">
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
       </c>
       <c r="H187" t="n">
-        <v>2.377740552910585</v>
+        <v>44.11202657958206</v>
       </c>
       <c r="I187" t="n">
         <v>0</v>
       </c>
       <c r="J187" t="n">
-        <v>2.377740552910585</v>
+        <v>44.11202657958206</v>
       </c>
       <c r="K187" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B188" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C188" t="n">
-        <v>0</v>
+        <v>17.17726521125602</v>
       </c>
       <c r="D188" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E188" t="n">
-        <v>0</v>
+        <v>6.924244161127699</v>
       </c>
       <c r="F188" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G188" t="n">
-        <v>0</v>
+        <v>17.17726521125604</v>
       </c>
       <c r="H188" t="n">
-        <v>3.512902367783275</v>
+        <v>56.32317648042529</v>
       </c>
       <c r="I188" t="n">
-        <v>0</v>
+        <v>6.924244161127699</v>
       </c>
       <c r="J188" t="n">
-        <v>3.512902367783275</v>
+        <v>56.32317648042529</v>
       </c>
       <c r="K188" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B189" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C189" t="n">
-        <v>0</v>
+        <v>17.17726521125602</v>
       </c>
       <c r="D189" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E189" t="n">
-        <v>0</v>
+        <v>6.924244161127698</v>
       </c>
       <c r="F189" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G189" t="n">
-        <v>0</v>
+        <v>17.17726521125604</v>
       </c>
       <c r="H189" t="n">
-        <v>4.437796754214907</v>
+        <v>64.37357229752645</v>
       </c>
       <c r="I189" t="n">
-        <v>0</v>
+        <v>6.924244161127699</v>
       </c>
       <c r="J189" t="n">
-        <v>4.437796754214907</v>
+        <v>64.37357229752645</v>
       </c>
       <c r="K189" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B190" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C190" t="n">
-        <v>0</v>
+        <v>17.17726521125602</v>
       </c>
       <c r="D190" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E190" t="n">
-        <v>0</v>
+        <v>6.924244161127699</v>
       </c>
       <c r="F190" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G190" t="n">
-        <v>0</v>
+        <v>17.17726521125604</v>
       </c>
       <c r="H190" t="n">
-        <v>5.21298605657082</v>
+        <v>70.23571266572199</v>
       </c>
       <c r="I190" t="n">
-        <v>0</v>
+        <v>6.924244161127699</v>
       </c>
       <c r="J190" t="n">
-        <v>5.21298605657082</v>
+        <v>70.23571266572199</v>
       </c>
       <c r="K190" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B191" s="2" t="n">
@@ -7495,367 +7495,359 @@
         <v>0</v>
       </c>
       <c r="D191" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="E191" t="n">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>24.58434289929532</v>
+        <v>740.8666506213059</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
       </c>
       <c r="H191" t="n">
-        <v>5.87540627774392</v>
+        <v>74.77346264547654</v>
       </c>
       <c r="I191" t="n">
         <v>0</v>
       </c>
       <c r="J191" t="n">
-        <v>5.87540627774392</v>
+        <v>74.77346264547654</v>
       </c>
       <c r="K191" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B192" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C192" t="n">
-        <v>37.42670714758817</v>
+        <v>0</v>
       </c>
       <c r="D192" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E192" t="n">
-        <v>28.95748566899951</v>
+        <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G192" t="n">
-        <v>37.42670714758816</v>
+        <v>0</v>
       </c>
       <c r="H192" t="n">
-        <v>64.10204165540358</v>
+        <v>29.86037089025183</v>
       </c>
       <c r="I192" t="n">
-        <v>28.95748566899952</v>
+        <v>0</v>
       </c>
       <c r="J192" t="n">
-        <v>64.10204165540358</v>
+        <v>29.86037089025183</v>
       </c>
       <c r="K192" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B193" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C193" t="n">
-        <v>37.42670714758817</v>
+        <v>1.660282353034576</v>
       </c>
       <c r="D193" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E193" t="n">
-        <v>28.95748566899951</v>
+        <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G193" t="n">
-        <v>37.42670714758816</v>
+        <v>1.660282353034576</v>
       </c>
       <c r="H193" t="n">
-        <v>89.06458097131986</v>
+        <v>34.33201180311551</v>
       </c>
       <c r="I193" t="n">
-        <v>28.95748566899952</v>
+        <v>0</v>
       </c>
       <c r="J193" t="n">
-        <v>89.06458097131986</v>
+        <v>34.33201180311551</v>
       </c>
       <c r="K193" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B194" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C194" t="n">
-        <v>37.42870522213487</v>
+        <v>1.660282353034576</v>
       </c>
       <c r="D194" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E194" t="n">
-        <v>28.95748566899951</v>
+        <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G194" t="n">
-        <v>37.52705437389957</v>
+        <v>1.660282353034576</v>
       </c>
       <c r="H194" t="n">
-        <v>109.4032782230057</v>
+        <v>37.280012572315</v>
       </c>
       <c r="I194" t="n">
-        <v>28.95748566899952</v>
+        <v>0</v>
       </c>
       <c r="J194" t="n">
-        <v>109.4032782230057</v>
+        <v>37.280012572315</v>
       </c>
       <c r="K194" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B195" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C195" t="n">
-        <v>0.001998074546704755</v>
+        <v>1.660282353034576</v>
       </c>
       <c r="D195" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E195" t="n">
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G195" t="n">
-        <v>0.1003472263114094</v>
+        <v>1.660282353034576</v>
       </c>
       <c r="H195" t="n">
-        <v>126.4499170226973</v>
+        <v>39.42668892304613</v>
       </c>
       <c r="I195" t="n">
         <v>0</v>
       </c>
       <c r="J195" t="n">
-        <v>126.4499170226973</v>
+        <v>39.42668892304613</v>
       </c>
       <c r="K195" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B196" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C196" t="n">
-        <v>0.001998074546704755</v>
+        <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="E196" t="n">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>552.4317025740247</v>
+        <v>285.007225067906</v>
       </c>
       <c r="G196" t="n">
-        <v>0.1003472263114094</v>
+        <v>0</v>
       </c>
       <c r="H196" t="n">
-        <v>141.0167308443426</v>
+        <v>41.0883824266543</v>
       </c>
       <c r="I196" t="n">
         <v>0</v>
       </c>
       <c r="J196" t="n">
-        <v>141.0167308443426</v>
+        <v>41.0883824266543</v>
       </c>
       <c r="K196" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B197" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C197" t="n">
-        <v>0.0650486978000249</v>
+        <v>0</v>
       </c>
       <c r="D197" t="n">
-        <v>24.58434289929532</v>
+        <v>4</v>
       </c>
       <c r="E197" t="n">
-        <v>0.01024911355676481</v>
+        <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>24.58434289929532</v>
+        <v>4</v>
       </c>
       <c r="G197" t="n">
-        <v>0.03919183118612408</v>
+        <v>0</v>
       </c>
       <c r="H197" t="n">
-        <v>2.377740552910585</v>
+        <v>1.717300224897027</v>
       </c>
       <c r="I197" t="n">
-        <v>0.0102208614884418</v>
+        <v>0</v>
       </c>
       <c r="J197" t="n">
-        <v>2.377740552910585</v>
-      </c>
-      <c r="K197" t="n">
-        <v>0.08</v>
-      </c>
+        <v>1.717300224897027</v>
+      </c>
+      <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B198" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C198" t="n">
-        <v>0.3450438561495588</v>
+        <v>0</v>
       </c>
       <c r="D198" t="n">
-        <v>24.58434289929532</v>
+        <v>4</v>
       </c>
       <c r="E198" t="n">
-        <v>0.01024911355676481</v>
+        <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>24.58434289929532</v>
+        <v>4</v>
       </c>
       <c r="G198" t="n">
-        <v>0.4057773302666071</v>
+        <v>0</v>
       </c>
       <c r="H198" t="n">
-        <v>3.512902367783275</v>
+        <v>2.246209584507109</v>
       </c>
       <c r="I198" t="n">
-        <v>0.0102208614884418</v>
+        <v>0</v>
       </c>
       <c r="J198" t="n">
-        <v>3.512902367783275</v>
-      </c>
-      <c r="K198" t="n">
-        <v>0.08</v>
-      </c>
+        <v>2.246209584507109</v>
+      </c>
+      <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B199" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C199" t="n">
-        <v>0.3450438561495588</v>
+        <v>0</v>
       </c>
       <c r="D199" t="n">
-        <v>24.58434289929532</v>
+        <v>4</v>
       </c>
       <c r="E199" t="n">
-        <v>0.01024911355676481</v>
+        <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>24.58434289929532</v>
+        <v>4</v>
       </c>
       <c r="G199" t="n">
-        <v>0.4057773302666071</v>
+        <v>0</v>
       </c>
       <c r="H199" t="n">
-        <v>4.437796754214907</v>
+        <v>2.4982276762293</v>
       </c>
       <c r="I199" t="n">
-        <v>0.0102208614884418</v>
+        <v>0</v>
       </c>
       <c r="J199" t="n">
-        <v>4.437796754214907</v>
-      </c>
-      <c r="K199" t="n">
-        <v>0.08</v>
-      </c>
+        <v>2.4982276762293</v>
+      </c>
+      <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B200" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C200" t="n">
-        <v>0.2799951583495339</v>
+        <v>0</v>
       </c>
       <c r="D200" t="n">
-        <v>24.58434289929532</v>
+        <v>4</v>
       </c>
       <c r="E200" t="n">
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>24.58434289929532</v>
+        <v>4</v>
       </c>
       <c r="G200" t="n">
-        <v>0.366585499080483</v>
+        <v>0</v>
       </c>
       <c r="H200" t="n">
-        <v>5.21298605657082</v>
+        <v>2.648951845381237</v>
       </c>
       <c r="I200" t="n">
         <v>0</v>
       </c>
       <c r="J200" t="n">
-        <v>5.21298605657082</v>
-      </c>
-      <c r="K200" t="n">
-        <v>0.08</v>
-      </c>
+        <v>2.648951845381237</v>
+      </c>
+      <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B201" s="2" t="n">
@@ -7865,34 +7857,32 @@
         <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>24.58434289929532</v>
+        <v>4</v>
       </c>
       <c r="E201" t="n">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>24.58434289929532</v>
+        <v>4</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
       </c>
       <c r="H201" t="n">
-        <v>5.87540627774392</v>
+        <v>2.752635411261187</v>
       </c>
       <c r="I201" t="n">
         <v>0</v>
       </c>
       <c r="J201" t="n">
-        <v>5.87540627774392</v>
-      </c>
-      <c r="K201" t="n">
-        <v>0.08</v>
-      </c>
+        <v>2.752635411261187</v>
+      </c>
+      <c r="K201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B202" s="2" t="n">
@@ -7914,20 +7904,20 @@
         <v>0</v>
       </c>
       <c r="H202" t="n">
-        <v>1.084828228313528</v>
+        <v>1.717300224897027</v>
       </c>
       <c r="I202" t="n">
         <v>0</v>
       </c>
       <c r="J202" t="n">
-        <v>1.084828228313528</v>
+        <v>1.717300224897027</v>
       </c>
       <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B203" s="2" t="n">
@@ -7949,20 +7939,20 @@
         <v>0</v>
       </c>
       <c r="H203" t="n">
-        <v>1.748391275895091</v>
+        <v>2.246209584507109</v>
       </c>
       <c r="I203" t="n">
         <v>0</v>
       </c>
       <c r="J203" t="n">
-        <v>1.748391275895091</v>
+        <v>2.246209584507109</v>
       </c>
       <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B204" s="2" t="n">
@@ -7984,20 +7974,20 @@
         <v>0</v>
       </c>
       <c r="H204" t="n">
-        <v>2.182785755513471</v>
+        <v>2.4982276762293</v>
       </c>
       <c r="I204" t="n">
         <v>0</v>
       </c>
       <c r="J204" t="n">
-        <v>2.182785755513471</v>
+        <v>2.4982276762293</v>
       </c>
       <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B205" s="2" t="n">
@@ -8019,20 +8009,20 @@
         <v>0</v>
       </c>
       <c r="H205" t="n">
-        <v>2.483031451106882</v>
+        <v>2.648951845381237</v>
       </c>
       <c r="I205" t="n">
         <v>0</v>
       </c>
       <c r="J205" t="n">
-        <v>2.483031451106882</v>
+        <v>2.648951845381237</v>
       </c>
       <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B206" s="2" t="n">
@@ -8054,20 +8044,20 @@
         <v>0</v>
       </c>
       <c r="H206" t="n">
-        <v>2.699949766579019</v>
+        <v>2.752635411261187</v>
       </c>
       <c r="I206" t="n">
         <v>0</v>
       </c>
       <c r="J206" t="n">
-        <v>2.699949766579019</v>
+        <v>2.752635411261187</v>
       </c>
       <c r="K206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_window_retrofit</t>
         </is>
       </c>
       <c r="B207" s="2" t="n">
@@ -8089,20 +8079,20 @@
         <v>0</v>
       </c>
       <c r="H207" t="n">
-        <v>1.084828228313528</v>
+        <v>1.717300224897027</v>
       </c>
       <c r="I207" t="n">
         <v>0</v>
       </c>
       <c r="J207" t="n">
-        <v>1.084828228313528</v>
+        <v>1.717300224897027</v>
       </c>
       <c r="K207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_window_retrofit</t>
         </is>
       </c>
       <c r="B208" s="2" t="n">
@@ -8124,20 +8114,20 @@
         <v>0</v>
       </c>
       <c r="H208" t="n">
-        <v>1.748391275895091</v>
+        <v>2.246209584507109</v>
       </c>
       <c r="I208" t="n">
         <v>0</v>
       </c>
       <c r="J208" t="n">
-        <v>1.748391275895091</v>
+        <v>2.246209584507109</v>
       </c>
       <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_window_retrofit</t>
         </is>
       </c>
       <c r="B209" s="2" t="n">
@@ -8159,20 +8149,20 @@
         <v>0</v>
       </c>
       <c r="H209" t="n">
-        <v>2.182785755513471</v>
+        <v>2.4982276762293</v>
       </c>
       <c r="I209" t="n">
         <v>0</v>
       </c>
       <c r="J209" t="n">
-        <v>2.182785755513471</v>
+        <v>2.4982276762293</v>
       </c>
       <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_window_retrofit</t>
         </is>
       </c>
       <c r="B210" s="2" t="n">
@@ -8194,20 +8184,20 @@
         <v>0</v>
       </c>
       <c r="H210" t="n">
-        <v>2.483031451106882</v>
+        <v>2.648951845381237</v>
       </c>
       <c r="I210" t="n">
         <v>0</v>
       </c>
       <c r="J210" t="n">
-        <v>2.483031451106882</v>
+        <v>2.648951845381237</v>
       </c>
       <c r="K210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_window_retrofit</t>
         </is>
       </c>
       <c r="B211" s="2" t="n">
@@ -8229,190 +8219,15 @@
         <v>0</v>
       </c>
       <c r="H211" t="n">
-        <v>2.699949766579019</v>
+        <v>2.752635411261187</v>
       </c>
       <c r="I211" t="n">
         <v>0</v>
       </c>
       <c r="J211" t="n">
-        <v>2.699949766579019</v>
+        <v>2.752635411261187</v>
       </c>
       <c r="K211" t="inlineStr"/>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>SH_window_retrofit</t>
-        </is>
-      </c>
-      <c r="B212" s="2" t="n">
-        <v>46023</v>
-      </c>
-      <c r="C212" t="n">
-        <v>0</v>
-      </c>
-      <c r="D212" t="n">
-        <v>4</v>
-      </c>
-      <c r="E212" t="n">
-        <v>0</v>
-      </c>
-      <c r="F212" t="n">
-        <v>4</v>
-      </c>
-      <c r="G212" t="n">
-        <v>0</v>
-      </c>
-      <c r="H212" t="n">
-        <v>1.084828228313528</v>
-      </c>
-      <c r="I212" t="n">
-        <v>0</v>
-      </c>
-      <c r="J212" t="n">
-        <v>1.084828228313528</v>
-      </c>
-      <c r="K212" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>SH_window_retrofit</t>
-        </is>
-      </c>
-      <c r="B213" s="2" t="n">
-        <v>47849</v>
-      </c>
-      <c r="C213" t="n">
-        <v>0</v>
-      </c>
-      <c r="D213" t="n">
-        <v>4</v>
-      </c>
-      <c r="E213" t="n">
-        <v>0</v>
-      </c>
-      <c r="F213" t="n">
-        <v>4</v>
-      </c>
-      <c r="G213" t="n">
-        <v>0</v>
-      </c>
-      <c r="H213" t="n">
-        <v>1.748391275895091</v>
-      </c>
-      <c r="I213" t="n">
-        <v>0</v>
-      </c>
-      <c r="J213" t="n">
-        <v>1.748391275895091</v>
-      </c>
-      <c r="K213" t="inlineStr"/>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>SH_window_retrofit</t>
-        </is>
-      </c>
-      <c r="B214" s="2" t="n">
-        <v>49675</v>
-      </c>
-      <c r="C214" t="n">
-        <v>0</v>
-      </c>
-      <c r="D214" t="n">
-        <v>4</v>
-      </c>
-      <c r="E214" t="n">
-        <v>0</v>
-      </c>
-      <c r="F214" t="n">
-        <v>4</v>
-      </c>
-      <c r="G214" t="n">
-        <v>0</v>
-      </c>
-      <c r="H214" t="n">
-        <v>2.182785755513471</v>
-      </c>
-      <c r="I214" t="n">
-        <v>0</v>
-      </c>
-      <c r="J214" t="n">
-        <v>2.182785755513471</v>
-      </c>
-      <c r="K214" t="inlineStr"/>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>SH_window_retrofit</t>
-        </is>
-      </c>
-      <c r="B215" s="2" t="n">
-        <v>51502</v>
-      </c>
-      <c r="C215" t="n">
-        <v>0</v>
-      </c>
-      <c r="D215" t="n">
-        <v>4</v>
-      </c>
-      <c r="E215" t="n">
-        <v>0</v>
-      </c>
-      <c r="F215" t="n">
-        <v>4</v>
-      </c>
-      <c r="G215" t="n">
-        <v>0</v>
-      </c>
-      <c r="H215" t="n">
-        <v>2.483031451106882</v>
-      </c>
-      <c r="I215" t="n">
-        <v>0</v>
-      </c>
-      <c r="J215" t="n">
-        <v>2.483031451106882</v>
-      </c>
-      <c r="K215" t="inlineStr"/>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>SH_window_retrofit</t>
-        </is>
-      </c>
-      <c r="B216" s="2" t="n">
-        <v>53328</v>
-      </c>
-      <c r="C216" t="n">
-        <v>0</v>
-      </c>
-      <c r="D216" t="n">
-        <v>4</v>
-      </c>
-      <c r="E216" t="n">
-        <v>0</v>
-      </c>
-      <c r="F216" t="n">
-        <v>4</v>
-      </c>
-      <c r="G216" t="n">
-        <v>0</v>
-      </c>
-      <c r="H216" t="n">
-        <v>2.699949766579019</v>
-      </c>
-      <c r="I216" t="n">
-        <v>0</v>
-      </c>
-      <c r="J216" t="n">
-        <v>2.699949766579019</v>
-      </c>
-      <c r="K216" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Ascona/investment_decision/aggregated_investment_decision.xlsx
+++ b/data/Ascona/investment_decision/aggregated_investment_decision.xlsx
@@ -445,42 +445,42 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>scen_all_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>scen_all_candidate_unit</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>scen_base_invested_available_unit</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>scen_base_candidate_unit</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_invested_available_unit</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_candidate_unit</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -499,28 +499,28 @@
         <v>46023</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1366.847597082856</v>
       </c>
       <c r="D2" t="n">
-        <v>1603792.017964014</v>
+        <v>1605043.354558521</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>847.7443384878072</v>
       </c>
       <c r="F2" t="n">
-        <v>1603792.017964014</v>
+        <v>1605043.354558521</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>956.4278098584418</v>
       </c>
       <c r="H2" t="n">
-        <v>1603792.017964014</v>
+        <v>1605043.354558521</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1124.281344650894</v>
       </c>
       <c r="J2" t="n">
-        <v>1603792.017964014</v>
+        <v>1605043.354558521</v>
       </c>
       <c r="K2" t="n">
         <v>0.003</v>
@@ -536,28 +536,28 @@
         <v>47849</v>
       </c>
       <c r="C3" t="n">
-        <v>2107.998814484529</v>
+        <v>3616.440094609093</v>
       </c>
       <c r="D3" t="n">
-        <v>1603792.017964014</v>
+        <v>1605043.354558521</v>
       </c>
       <c r="E3" t="n">
-        <v>1928.298028259503</v>
+        <v>3289.772295648221</v>
       </c>
       <c r="F3" t="n">
-        <v>1603792.017964014</v>
+        <v>1605043.354558521</v>
       </c>
       <c r="G3" t="n">
-        <v>2107.998814484535</v>
+        <v>3568.403681074913</v>
       </c>
       <c r="H3" t="n">
-        <v>1603792.017964014</v>
+        <v>1605043.354558521</v>
       </c>
       <c r="I3" t="n">
-        <v>1928.298028259503</v>
+        <v>3289.772295648221</v>
       </c>
       <c r="J3" t="n">
-        <v>1603792.017964014</v>
+        <v>1605043.354558521</v>
       </c>
       <c r="K3" t="n">
         <v>0.003</v>
@@ -573,28 +573,28 @@
         <v>49675</v>
       </c>
       <c r="C4" t="n">
-        <v>5931.052512637291</v>
+        <v>7052.903073940413</v>
       </c>
       <c r="D4" t="n">
-        <v>1603792.017964014</v>
+        <v>1605043.354558521</v>
       </c>
       <c r="E4" t="n">
-        <v>5778.584426112904</v>
+        <v>7580.749456673175</v>
       </c>
       <c r="F4" t="n">
-        <v>1603792.017964014</v>
+        <v>1605043.354558521</v>
       </c>
       <c r="G4" t="n">
-        <v>5931.052512637296</v>
+        <v>7052.742258777374</v>
       </c>
       <c r="H4" t="n">
-        <v>1603792.017964014</v>
+        <v>1605043.354558521</v>
       </c>
       <c r="I4" t="n">
-        <v>5778.584426112898</v>
+        <v>7635.685350249907</v>
       </c>
       <c r="J4" t="n">
-        <v>1603792.017964014</v>
+        <v>1605043.354558521</v>
       </c>
       <c r="K4" t="n">
         <v>0.003</v>
@@ -610,28 +610,28 @@
         <v>51502</v>
       </c>
       <c r="C5" t="n">
-        <v>6981.790938079661</v>
+        <v>8425.584725451325</v>
       </c>
       <c r="D5" t="n">
-        <v>1603792.017964014</v>
+        <v>1605043.354558521</v>
       </c>
       <c r="E5" t="n">
-        <v>6904.609400347793</v>
+        <v>8764.035479909719</v>
       </c>
       <c r="F5" t="n">
-        <v>1603792.017964014</v>
+        <v>1605043.354558521</v>
       </c>
       <c r="G5" t="n">
-        <v>6981.790938079661</v>
+        <v>8469.860149724183</v>
       </c>
       <c r="H5" t="n">
-        <v>1603792.017964014</v>
+        <v>1605043.354558521</v>
       </c>
       <c r="I5" t="n">
-        <v>6904.609400347793</v>
+        <v>8764.035479909719</v>
       </c>
       <c r="J5" t="n">
-        <v>1603792.017964014</v>
+        <v>1605043.354558521</v>
       </c>
       <c r="K5" t="n">
         <v>0.003</v>
@@ -647,28 +647,28 @@
         <v>53328</v>
       </c>
       <c r="C6" t="n">
-        <v>6981.790938079661</v>
+        <v>8425.847023822984</v>
       </c>
       <c r="D6" t="n">
-        <v>1603792.017964014</v>
+        <v>1605043.354558521</v>
       </c>
       <c r="E6" t="n">
-        <v>6904.609400347794</v>
+        <v>8764.297778281376</v>
       </c>
       <c r="F6" t="n">
-        <v>1603792.017964014</v>
+        <v>1605043.354558521</v>
       </c>
       <c r="G6" t="n">
-        <v>6981.790938079661</v>
+        <v>8470.122448095841</v>
       </c>
       <c r="H6" t="n">
-        <v>1603792.017964014</v>
+        <v>1605043.354558521</v>
       </c>
       <c r="I6" t="n">
-        <v>6904.609400347792</v>
+        <v>8764.297778281376</v>
       </c>
       <c r="J6" t="n">
-        <v>1603792.017964014</v>
+        <v>1605043.354558521</v>
       </c>
       <c r="K6" t="n">
         <v>0.003</v>
@@ -687,25 +687,25 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>2405.688026946022</v>
+        <v>1428.094882948866</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2405.688026946022</v>
+        <v>2407.565031837782</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1427.050483977316</v>
+        <v>2407.565031837782</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1427.050483977316</v>
+        <v>1428.094882948866</v>
       </c>
       <c r="K7" t="n">
         <v>2</v>
@@ -724,25 +724,25 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>2405.688026946022</v>
+        <v>1709.588185921052</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2405.688026946022</v>
+        <v>2407.565031837782</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1708.304501463547</v>
+        <v>2407.565031837782</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1708.304501463547</v>
+        <v>1709.588185921052</v>
       </c>
       <c r="K8" t="n">
         <v>2</v>
@@ -761,25 +761,25 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>2405.688026946022</v>
+        <v>1824.896331921844</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2405.688026946022</v>
+        <v>2407.565031837782</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1823.514628913067</v>
+        <v>2407.565031837782</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1823.514628913067</v>
+        <v>1824.896331921844</v>
       </c>
       <c r="K9" t="n">
         <v>2</v>
@@ -798,25 +798,25 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>2405.688026946022</v>
+        <v>1886.533812811128</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2405.688026946022</v>
+        <v>2407.565031837782</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1885.099714401069</v>
+        <v>2407.565031837782</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1885.099714401069</v>
+        <v>1886.533812811128</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
@@ -835,25 +835,25 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>2405.688026946022</v>
+        <v>1925.049290525592</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2405.688026946022</v>
+        <v>2407.565031837782</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1923.582451745854</v>
+        <v>2407.565031837782</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1923.582451745854</v>
+        <v>1925.049290525592</v>
       </c>
       <c r="K11" t="n">
         <v>2</v>
@@ -872,25 +872,25 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>38.83232050396268</v>
+        <v>12.02681808690701</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>38.83232050396268</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>11.85896762513558</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>11.85896762513558</v>
+        <v>12.02681808690701</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -909,25 +909,25 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>38.83232050396268</v>
+        <v>16.55360533516066</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>38.83232050396268</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>16.32257745401947</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>16.32257745401947</v>
+        <v>16.55360533516066</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -946,25 +946,25 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>38.83232050396268</v>
+        <v>18.8204631381465</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>38.83232050396268</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>18.55779820003381</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>18.55779820003381</v>
+        <v>18.8204631381465</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -983,25 +983,25 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>38.83232050396268</v>
+        <v>20.15059880314304</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>38.83232050396268</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>19.86937002844656</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>19.86937002844656</v>
+        <v>20.15059880314304</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1020,25 +1020,25 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>38.83232050396268</v>
+        <v>21.01808582652089</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>38.83232050396268</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>20.72475010080856</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>20.72475010080856</v>
+        <v>21.01808582652089</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1054,28 +1054,28 @@
         <v>46023</v>
       </c>
       <c r="C17" t="n">
-        <v>1.668885927770414</v>
+        <v>1.744576111630544</v>
       </c>
       <c r="D17" t="n">
-        <v>38.83232050396268</v>
+        <v>12.02681808690701</v>
       </c>
       <c r="E17" t="n">
-        <v>1.668885927770414</v>
+        <v>1.744576111630546</v>
       </c>
       <c r="F17" t="n">
-        <v>38.83232050396268</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="G17" t="n">
-        <v>1.668885927770413</v>
+        <v>1.744576111630544</v>
       </c>
       <c r="H17" t="n">
-        <v>11.85896762513558</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="I17" t="n">
-        <v>1.668885927770414</v>
+        <v>1.744576111630545</v>
       </c>
       <c r="J17" t="n">
-        <v>11.85896762513558</v>
+        <v>12.02681808690701</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
@@ -1091,28 +1091,28 @@
         <v>47849</v>
       </c>
       <c r="C18" t="n">
-        <v>1.668885927770414</v>
+        <v>1.764862770177136</v>
       </c>
       <c r="D18" t="n">
-        <v>38.83232050396268</v>
+        <v>16.55360533516066</v>
       </c>
       <c r="E18" t="n">
-        <v>1.668885927770414</v>
+        <v>1.764862770177137</v>
       </c>
       <c r="F18" t="n">
-        <v>38.83232050396268</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="G18" t="n">
-        <v>1.668885927770413</v>
+        <v>1.764862770177136</v>
       </c>
       <c r="H18" t="n">
-        <v>16.32257745401947</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="I18" t="n">
-        <v>1.668885927770414</v>
+        <v>1.764862770177137</v>
       </c>
       <c r="J18" t="n">
-        <v>16.32257745401947</v>
+        <v>16.55360533516066</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -1128,28 +1128,28 @@
         <v>49675</v>
       </c>
       <c r="C19" t="n">
-        <v>1.72203695031119</v>
+        <v>1.781337669389687</v>
       </c>
       <c r="D19" t="n">
-        <v>38.83232050396268</v>
+        <v>18.8204631381465</v>
       </c>
       <c r="E19" t="n">
-        <v>1.723041410039284</v>
+        <v>1.781088598481704</v>
       </c>
       <c r="F19" t="n">
-        <v>38.83232050396268</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="G19" t="n">
-        <v>1.72203695031119</v>
+        <v>1.781337669389687</v>
       </c>
       <c r="H19" t="n">
-        <v>18.55779820003381</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="I19" t="n">
-        <v>1.723041410039284</v>
+        <v>1.781088598481703</v>
       </c>
       <c r="J19" t="n">
-        <v>18.55779820003381</v>
+        <v>18.8204631381465</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -1165,28 +1165,28 @@
         <v>51502</v>
       </c>
       <c r="C20" t="n">
-        <v>1.780896937953275</v>
+        <v>1.803614190664855</v>
       </c>
       <c r="D20" t="n">
-        <v>38.83232050396268</v>
+        <v>20.15059880314304</v>
       </c>
       <c r="E20" t="n">
-        <v>1.781102472681083</v>
+        <v>1.803614190664857</v>
       </c>
       <c r="F20" t="n">
-        <v>38.83232050396268</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="G20" t="n">
-        <v>1.780896937953274</v>
+        <v>1.803614190664855</v>
       </c>
       <c r="H20" t="n">
-        <v>19.86937002844656</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="I20" t="n">
-        <v>1.781102472681083</v>
+        <v>1.803614190664857</v>
       </c>
       <c r="J20" t="n">
-        <v>19.86937002844656</v>
+        <v>20.15059880314304</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
@@ -1202,28 +1202,28 @@
         <v>53328</v>
       </c>
       <c r="C21" t="n">
-        <v>1.783030930674917</v>
+        <v>1.785025082779787</v>
       </c>
       <c r="D21" t="n">
-        <v>38.83232050396268</v>
+        <v>21.01808582652089</v>
       </c>
       <c r="E21" t="n">
-        <v>1.783030930674916</v>
+        <v>1.785025082779787</v>
       </c>
       <c r="F21" t="n">
-        <v>38.83232050396268</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="G21" t="n">
-        <v>1.783030930674915</v>
+        <v>1.785025082779787</v>
       </c>
       <c r="H21" t="n">
-        <v>20.72475010080856</v>
+        <v>39.3819486954109</v>
       </c>
       <c r="I21" t="n">
-        <v>1.783030930674915</v>
+        <v>1.785025082779787</v>
       </c>
       <c r="J21" t="n">
-        <v>20.72475010080856</v>
+        <v>21.01808582652089</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -1239,25 +1239,25 @@
         <v>46023</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5865130888845524</v>
+        <v>0.6194873295756993</v>
       </c>
       <c r="D22" t="n">
         <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5865130888845524</v>
+        <v>0.6194873295756993</v>
       </c>
       <c r="F22" t="n">
         <v>6</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5865130888845524</v>
+        <v>0.6194873295756993</v>
       </c>
       <c r="H22" t="n">
         <v>6</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5865130888845524</v>
+        <v>0.6194873295756993</v>
       </c>
       <c r="J22" t="n">
         <v>6</v>
@@ -1276,25 +1276,25 @@
         <v>47849</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6112755175735319</v>
+        <v>0.6256357628933464</v>
       </c>
       <c r="D23" t="n">
         <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6120610294491871</v>
+        <v>0.6256357628933464</v>
       </c>
       <c r="F23" t="n">
         <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6112755175735309</v>
+        <v>0.6256357628933464</v>
       </c>
       <c r="H23" t="n">
         <v>6</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6120610294491871</v>
+        <v>0.6256357628933464</v>
       </c>
       <c r="J23" t="n">
         <v>6</v>
@@ -1313,25 +1313,25 @@
         <v>49675</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6316737420741051</v>
+        <v>0.6434850026070589</v>
       </c>
       <c r="D24" t="n">
         <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6330825941800524</v>
+        <v>0.6428807147761446</v>
       </c>
       <c r="F24" t="n">
         <v>6</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6316737420741051</v>
+        <v>0.6434850026070589</v>
       </c>
       <c r="H24" t="n">
         <v>6</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6330825941800524</v>
+        <v>0.6428807147761446</v>
       </c>
       <c r="J24" t="n">
         <v>6</v>
@@ -1350,25 +1350,25 @@
         <v>51502</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6693645873036504</v>
+        <v>0.7008934244329993</v>
       </c>
       <c r="D25" t="n">
         <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6693578099306406</v>
+        <v>0.7005898223247637</v>
       </c>
       <c r="F25" t="n">
         <v>6</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6693645873036504</v>
+        <v>0.7008934244329994</v>
       </c>
       <c r="H25" t="n">
         <v>6</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6693578099306406</v>
+        <v>0.7005898223247637</v>
       </c>
       <c r="J25" t="n">
         <v>6</v>
@@ -1387,25 +1387,25 @@
         <v>53328</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6693645873036504</v>
+        <v>0.7008934244329994</v>
       </c>
       <c r="D26" t="n">
         <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6693578099306406</v>
+        <v>0.7005898223247637</v>
       </c>
       <c r="F26" t="n">
         <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6693645873036504</v>
+        <v>0.7008934244329994</v>
       </c>
       <c r="H26" t="n">
         <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6693578099306406</v>
+        <v>0.7005898223247637</v>
       </c>
       <c r="J26" t="n">
         <v>6</v>
@@ -1427,7 +1427,7 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0.0867453946648023</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -1439,7 +1439,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0867453946648023</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0.1343372936492743</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1476,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1343372936492743</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0.1647522628953677</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1513,7 +1513,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1647522628953677</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -1538,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0.1862401701876625</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1550,7 +1550,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1862401701876625</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0.202571092960545</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.202571092960545</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -1609,28 +1609,28 @@
         <v>46023</v>
       </c>
       <c r="C32" t="n">
-        <v>0.06987360984846264</v>
+        <v>0.07333373253921144</v>
       </c>
       <c r="D32" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="E32" t="n">
-        <v>0.06987360984846264</v>
+        <v>0.07333373253921149</v>
       </c>
       <c r="F32" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="G32" t="n">
-        <v>0.06987360984846257</v>
+        <v>0.07333373253921144</v>
       </c>
       <c r="H32" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="I32" t="n">
-        <v>0.06987360984846264</v>
+        <v>0.07333373253921147</v>
       </c>
       <c r="J32" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="K32" t="n">
         <v>175</v>
@@ -1646,28 +1646,28 @@
         <v>47849</v>
       </c>
       <c r="C33" t="n">
-        <v>0.06987360984846264</v>
+        <v>0.07426112264419851</v>
       </c>
       <c r="D33" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="E33" t="n">
-        <v>0.06987360984846264</v>
+        <v>0.07426112264419851</v>
       </c>
       <c r="F33" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="G33" t="n">
-        <v>0.06987360984846258</v>
+        <v>0.07426112264419849</v>
       </c>
       <c r="H33" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="I33" t="n">
-        <v>0.06987360984846264</v>
+        <v>0.07426112264419851</v>
       </c>
       <c r="J33" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="K33" t="n">
         <v>175</v>
@@ -1683,28 +1683,28 @@
         <v>49675</v>
       </c>
       <c r="C34" t="n">
-        <v>0.07230337087889811</v>
+        <v>0.07501426089391512</v>
       </c>
       <c r="D34" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="E34" t="n">
-        <v>0.07234928903789667</v>
+        <v>0.07500287479526445</v>
       </c>
       <c r="F34" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="G34" t="n">
-        <v>0.07230337087889811</v>
+        <v>0.07501426089391512</v>
       </c>
       <c r="H34" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="I34" t="n">
-        <v>0.07234928903789668</v>
+        <v>0.07500287479526441</v>
       </c>
       <c r="J34" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="K34" t="n">
         <v>175</v>
@@ -1720,28 +1720,28 @@
         <v>51502</v>
       </c>
       <c r="C35" t="n">
-        <v>0.07499411317110753</v>
+        <v>0.07775327686857787</v>
       </c>
       <c r="D35" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="E35" t="n">
-        <v>0.07500350904437884</v>
+        <v>0.07768388210098112</v>
       </c>
       <c r="F35" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="G35" t="n">
-        <v>0.07499411317110766</v>
+        <v>0.07775327686857789</v>
       </c>
       <c r="H35" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="I35" t="n">
-        <v>0.07500350904437879</v>
+        <v>0.07768388210098112</v>
       </c>
       <c r="J35" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="K35" t="n">
         <v>175</v>
@@ -1757,28 +1757,28 @@
         <v>53328</v>
       </c>
       <c r="C36" t="n">
-        <v>0.07509166712409703</v>
+        <v>0.07860306465760961</v>
       </c>
       <c r="D36" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="E36" t="n">
-        <v>0.075091667124097</v>
+        <v>0.07853366989001288</v>
       </c>
       <c r="F36" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="G36" t="n">
-        <v>0.07509166712409697</v>
+        <v>0.07860306465760961</v>
       </c>
       <c r="H36" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="I36" t="n">
-        <v>0.07509166712409697</v>
+        <v>0.0785336698900129</v>
       </c>
       <c r="J36" t="n">
-        <v>27.49357745081168</v>
+        <v>27.51502893528894</v>
       </c>
       <c r="K36" t="n">
         <v>175</v>
@@ -1797,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>5.878502256181318</v>
+        <v>0.47079117807104</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.47079117807104</v>
+        <v>5.878502256181318</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -1834,7 +1834,7 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>5.878502256181318</v>
+        <v>0.742930397094833</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -1846,7 +1846,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.742930397094833</v>
+        <v>5.878502256181318</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>5.878502256181318</v>
+        <v>0.9247372801783194</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.9247372801783194</v>
+        <v>5.878502256181318</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>5.878502256181318</v>
+        <v>1.058489268339244</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -1920,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.058489268339244</v>
+        <v>5.878502256181318</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -1945,7 +1945,7 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>5.878502256181318</v>
+        <v>1.163707434539444</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.163707434539444</v>
+        <v>5.878502256181318</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>11.33205254203628</v>
+        <v>0.9075492589321255</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9075492589321255</v>
+        <v>11.33205254203628</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>11.33205254203628</v>
+        <v>1.432154982351485</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -2031,7 +2031,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1.432154982351485</v>
+        <v>11.33205254203628</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>11.33205254203628</v>
+        <v>1.782626082271459</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -2068,7 +2068,7 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1.782626082271459</v>
+        <v>11.33205254203628</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>11.33205254203628</v>
+        <v>2.040461240172037</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -2105,7 +2105,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>2.040461240172037</v>
+        <v>11.33205254203628</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -2130,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>11.33205254203628</v>
+        <v>2.243291440076036</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -2142,7 +2142,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>2.243291440076036</v>
+        <v>11.33205254203628</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1567600601648352</v>
+        <v>0.01255443141522774</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.01255443141522774</v>
+        <v>0.1567600601648352</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -2204,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1567600601648352</v>
+        <v>0.01981147725586221</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.01981147725586221</v>
+        <v>0.1567600601648352</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -2241,7 +2241,7 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1567600601648352</v>
+        <v>0.02465966080475518</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -2253,7 +2253,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.02465966080475518</v>
+        <v>0.1567600601648352</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1567600601648352</v>
+        <v>0.02822638048904651</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -2290,7 +2290,7 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.02822638048904651</v>
+        <v>0.1567600601648352</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0.1567600601648352</v>
+        <v>0.03103219825438517</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -2327,7 +2327,7 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.03103219825438517</v>
+        <v>0.1567600601648352</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -2756,25 +2756,25 @@
         <v>47849</v>
       </c>
       <c r="C63" t="n">
-        <v>0.5720909640975366</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
         <v>77.9217936042</v>
       </c>
       <c r="E63" t="n">
-        <v>0.4216803319583462</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
         <v>77.9217936042</v>
       </c>
       <c r="G63" t="n">
-        <v>0.5720909640975366</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
         <v>77.9217936042</v>
       </c>
       <c r="I63" t="n">
-        <v>0.4216803319583462</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
         <v>77.9217936042</v>
@@ -2793,25 +2793,25 @@
         <v>49675</v>
       </c>
       <c r="C64" t="n">
-        <v>5.465095428241168</v>
+        <v>13.29658105361883</v>
       </c>
       <c r="D64" t="n">
         <v>77.9217936042</v>
       </c>
       <c r="E64" t="n">
-        <v>5.208964280291676</v>
+        <v>13.29658105361883</v>
       </c>
       <c r="F64" t="n">
         <v>77.9217936042</v>
       </c>
       <c r="G64" t="n">
-        <v>5.465095428241169</v>
+        <v>13.29658105361883</v>
       </c>
       <c r="H64" t="n">
         <v>77.9217936042</v>
       </c>
       <c r="I64" t="n">
-        <v>5.208964280291676</v>
+        <v>13.29658105361883</v>
       </c>
       <c r="J64" t="n">
         <v>77.9217936042</v>
@@ -2830,25 +2830,25 @@
         <v>51502</v>
       </c>
       <c r="C65" t="n">
-        <v>12.75210305814845</v>
+        <v>17.47261798574383</v>
       </c>
       <c r="D65" t="n">
         <v>77.9217936042</v>
       </c>
       <c r="E65" t="n">
-        <v>12.75210305814845</v>
+        <v>17.45178163844321</v>
       </c>
       <c r="F65" t="n">
         <v>77.9217936042</v>
       </c>
       <c r="G65" t="n">
-        <v>12.75210305814845</v>
+        <v>17.47261798574383</v>
       </c>
       <c r="H65" t="n">
         <v>77.9217936042</v>
       </c>
       <c r="I65" t="n">
-        <v>12.75210305814845</v>
+        <v>17.45178163844321</v>
       </c>
       <c r="J65" t="n">
         <v>77.9217936042</v>
@@ -2867,25 +2867,25 @@
         <v>53328</v>
       </c>
       <c r="C66" t="n">
-        <v>12.75210305814844</v>
+        <v>17.47261798574383</v>
       </c>
       <c r="D66" t="n">
         <v>77.9217936042</v>
       </c>
       <c r="E66" t="n">
-        <v>12.75210305814844</v>
+        <v>17.45178163844321</v>
       </c>
       <c r="F66" t="n">
         <v>77.9217936042</v>
       </c>
       <c r="G66" t="n">
-        <v>12.75210305814845</v>
+        <v>17.47261798574383</v>
       </c>
       <c r="H66" t="n">
         <v>77.9217936042</v>
       </c>
       <c r="I66" t="n">
-        <v>12.75210305814844</v>
+        <v>17.45178163844321</v>
       </c>
       <c r="J66" t="n">
         <v>77.9217936042</v>
@@ -2978,25 +2978,25 @@
         <v>49675</v>
       </c>
       <c r="C69" t="n">
-        <v>0.04332084431076671</v>
+        <v>8.05126057</v>
       </c>
       <c r="D69" t="n">
         <v>111.621575016</v>
       </c>
       <c r="E69" t="n">
-        <v>0.04692132372220224</v>
+        <v>8.212549189999995</v>
       </c>
       <c r="F69" t="n">
         <v>111.621575016</v>
       </c>
       <c r="G69" t="n">
-        <v>0.04332084431076752</v>
+        <v>8.05126057</v>
       </c>
       <c r="H69" t="n">
         <v>111.621575016</v>
       </c>
       <c r="I69" t="n">
-        <v>0.04692132372220077</v>
+        <v>8.212549189999995</v>
       </c>
       <c r="J69" t="n">
         <v>111.621575016</v>
@@ -3015,25 +3015,25 @@
         <v>51502</v>
       </c>
       <c r="C70" t="n">
-        <v>2.398406122036903</v>
+        <v>9.05126057</v>
       </c>
       <c r="D70" t="n">
         <v>111.621575016</v>
       </c>
       <c r="E70" t="n">
-        <v>2.402006601448339</v>
+        <v>9.212549189999995</v>
       </c>
       <c r="F70" t="n">
         <v>111.621575016</v>
       </c>
       <c r="G70" t="n">
-        <v>2.398406122036905</v>
+        <v>9.05126057</v>
       </c>
       <c r="H70" t="n">
         <v>111.621575016</v>
       </c>
       <c r="I70" t="n">
-        <v>2.402006601448337</v>
+        <v>9.212549189999995</v>
       </c>
       <c r="J70" t="n">
         <v>111.621575016</v>
@@ -3052,25 +3052,25 @@
         <v>53328</v>
       </c>
       <c r="C71" t="n">
-        <v>2.398406122036903</v>
+        <v>9.05126057</v>
       </c>
       <c r="D71" t="n">
         <v>111.621575016</v>
       </c>
       <c r="E71" t="n">
-        <v>2.402006601448339</v>
+        <v>9.212549189999995</v>
       </c>
       <c r="F71" t="n">
         <v>111.621575016</v>
       </c>
       <c r="G71" t="n">
-        <v>2.398406122036905</v>
+        <v>9.05126057</v>
       </c>
       <c r="H71" t="n">
         <v>111.621575016</v>
       </c>
       <c r="I71" t="n">
-        <v>2.402006601448337</v>
+        <v>9.212549189999995</v>
       </c>
       <c r="J71" t="n">
         <v>111.621575016</v>
@@ -3570,25 +3570,25 @@
         <v>51502</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>0.2904207328749978</v>
       </c>
       <c r="D85" t="n">
         <v>77.9217936042</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>0.3112570801756448</v>
       </c>
       <c r="F85" t="n">
         <v>77.9217936042</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>0.2904207328749928</v>
       </c>
       <c r="H85" t="n">
         <v>77.9217936042</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>0.3112570801756448</v>
       </c>
       <c r="J85" t="n">
         <v>77.9217936042</v>
@@ -3607,25 +3607,25 @@
         <v>53328</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>0.2904207328749978</v>
       </c>
       <c r="D86" t="n">
         <v>77.9217936042</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>0.3112570801756448</v>
       </c>
       <c r="F86" t="n">
         <v>77.9217936042</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>0.2904207328749928</v>
       </c>
       <c r="H86" t="n">
         <v>77.9217936042</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>0.3112570801756448</v>
       </c>
       <c r="J86" t="n">
         <v>77.9217936042</v>
@@ -4572,19 +4572,19 @@
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>0.1191671853885055</v>
+        <v>0</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="F112" t="n">
-        <v>0.1191671853885055</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="I112" t="n">
         <v>0</v>
@@ -4606,22 +4606,22 @@
         <v>47849</v>
       </c>
       <c r="C113" t="n">
-        <v>0.1191671853885055</v>
+        <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>0.1191671853885055</v>
+        <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>0.1191671853885055</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="F113" t="n">
-        <v>0.1191671853885055</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
@@ -4643,22 +4643,22 @@
         <v>49675</v>
       </c>
       <c r="C114" t="n">
-        <v>0.1191671853885055</v>
+        <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>0.1191671853885055</v>
+        <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>0.1191671853885055</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="F114" t="n">
-        <v>0.1191671853885055</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="I114" t="n">
         <v>0</v>
@@ -4680,22 +4680,22 @@
         <v>51502</v>
       </c>
       <c r="C115" t="n">
-        <v>0.1191671853885055</v>
+        <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>0.1191671853885055</v>
+        <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>0.1191671853885055</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="F115" t="n">
-        <v>0.1191671853885055</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
@@ -4717,22 +4717,22 @@
         <v>53328</v>
       </c>
       <c r="C116" t="n">
-        <v>0.1191671853885055</v>
+        <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>0.1191671853885055</v>
+        <v>0</v>
       </c>
       <c r="E116" t="n">
-        <v>0.1191671853885055</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="F116" t="n">
-        <v>0.1191671853885055</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="I116" t="n">
         <v>0</v>
@@ -4757,7 +4757,7 @@
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>408.2479934734613</v>
+        <v>245.0708881712023</v>
       </c>
       <c r="E117" t="n">
         <v>0</v>
@@ -4769,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>245.0708881712023</v>
+        <v>408.2479934734613</v>
       </c>
       <c r="I117" t="n">
         <v>0</v>
@@ -4794,7 +4794,7 @@
         <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>408.2479934734613</v>
+        <v>293.6728799384529</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>293.6728799384529</v>
+        <v>408.2479934734613</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
@@ -4831,7 +4831,7 @@
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>408.2479934734613</v>
+        <v>313.6885407026189</v>
       </c>
       <c r="E119" t="n">
         <v>0</v>
@@ -4843,7 +4843,7 @@
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>313.6885407026189</v>
+        <v>408.2479934734613</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
@@ -4868,7 +4868,7 @@
         <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>408.2479934734613</v>
+        <v>324.5386626470429</v>
       </c>
       <c r="E120" t="n">
         <v>0</v>
@@ -4880,7 +4880,7 @@
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>324.5386626470429</v>
+        <v>408.2479934734613</v>
       </c>
       <c r="I120" t="n">
         <v>0</v>
@@ -4905,7 +4905,7 @@
         <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>408.2479934734613</v>
+        <v>331.4339421130536</v>
       </c>
       <c r="E121" t="n">
         <v>0</v>
@@ -4917,7 +4917,7 @@
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>331.4339421130536</v>
+        <v>408.2479934734613</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
@@ -4942,7 +4942,7 @@
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>172.0646688421795</v>
+        <v>109.1637891589338</v>
       </c>
       <c r="E122" t="n">
         <v>0</v>
@@ -4954,7 +4954,7 @@
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>109.1637891589338</v>
+        <v>172.0646688421795</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
@@ -4979,7 +4979,7 @@
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>172.0646688421795</v>
+        <v>127.8986970423353</v>
       </c>
       <c r="E123" t="n">
         <v>0</v>
@@ -4991,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>127.8986970423353</v>
+        <v>172.0646688421795</v>
       </c>
       <c r="I123" t="n">
         <v>0</v>
@@ -5016,7 +5016,7 @@
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>172.0646688421795</v>
+        <v>135.6142565699748</v>
       </c>
       <c r="E124" t="n">
         <v>0</v>
@@ -5028,7 +5028,7 @@
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>135.6142565699748</v>
+        <v>172.0646688421795</v>
       </c>
       <c r="I124" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>172.0646688421795</v>
+        <v>139.7967196288124</v>
       </c>
       <c r="E125" t="n">
         <v>0</v>
@@ -5065,7 +5065,7 @@
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>139.7967196288124</v>
+        <v>172.0646688421795</v>
       </c>
       <c r="I125" t="n">
         <v>0</v>
@@ -5087,10 +5087,10 @@
         <v>53328</v>
       </c>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>143.3937505848484</v>
       </c>
       <c r="D126" t="n">
-        <v>172.0646688421795</v>
+        <v>142.4546852991219</v>
       </c>
       <c r="E126" t="n">
         <v>0</v>
@@ -5099,10 +5099,10 @@
         <v>172.0646688421795</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>172.0646688421795</v>
       </c>
       <c r="H126" t="n">
-        <v>142.4546852991219</v>
+        <v>172.0646688421795</v>
       </c>
       <c r="I126" t="n">
         <v>0</v>
@@ -5127,25 +5127,25 @@
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E127" t="n">
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K127" t="n">
         <v>0.017</v>
@@ -5161,28 +5161,28 @@
         <v>47849</v>
       </c>
       <c r="C128" t="n">
-        <v>3.34944850319345</v>
+        <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E128" t="n">
-        <v>17.92036485449546</v>
+        <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G128" t="n">
-        <v>3.349448503193331</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I128" t="n">
-        <v>17.92036485449547</v>
+        <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K128" t="n">
         <v>0.017</v>
@@ -5198,28 +5198,28 @@
         <v>49675</v>
       </c>
       <c r="C129" t="n">
-        <v>3.34944850319345</v>
+        <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E129" t="n">
-        <v>18.0215590373562</v>
+        <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G129" t="n">
-        <v>3.349448503193331</v>
+        <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I129" t="n">
-        <v>18.0215590373562</v>
+        <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K129" t="n">
         <v>0.017</v>
@@ -5235,28 +5235,28 @@
         <v>51502</v>
       </c>
       <c r="C130" t="n">
-        <v>3.34944850319345</v>
+        <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E130" t="n">
-        <v>18.0215590373562</v>
+        <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G130" t="n">
-        <v>3.349448503193331</v>
+        <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I130" t="n">
-        <v>18.0215590373562</v>
+        <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K130" t="n">
         <v>0.017</v>
@@ -5275,25 +5275,25 @@
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E131" t="n">
-        <v>0.1011941828607345</v>
+        <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I131" t="n">
-        <v>0.1011941828607345</v>
+        <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K131" t="n">
         <v>0.017</v>
@@ -5312,25 +5312,25 @@
         <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E132" t="n">
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I132" t="n">
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K132" t="n">
         <v>0.08</v>
@@ -5349,25 +5349,25 @@
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E133" t="n">
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I133" t="n">
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K133" t="n">
         <v>0.08</v>
@@ -5383,28 +5383,28 @@
         <v>49675</v>
       </c>
       <c r="C134" t="n">
-        <v>0.5081714412488159</v>
+        <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E134" t="n">
-        <v>2.7343000445237</v>
+        <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G134" t="n">
-        <v>0.5081714412488149</v>
+        <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I134" t="n">
-        <v>2.734300044523696</v>
+        <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K134" t="n">
         <v>0.08</v>
@@ -5420,28 +5420,28 @@
         <v>51502</v>
       </c>
       <c r="C135" t="n">
-        <v>0.5081714412488159</v>
+        <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E135" t="n">
-        <v>2.7343000445237</v>
+        <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G135" t="n">
-        <v>0.5081714412488149</v>
+        <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I135" t="n">
-        <v>2.734300044523696</v>
+        <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K135" t="n">
         <v>0.08</v>
@@ -5457,28 +5457,28 @@
         <v>53328</v>
       </c>
       <c r="C136" t="n">
-        <v>0.5081714412488159</v>
+        <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E136" t="n">
-        <v>2.7343000445237</v>
+        <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G136" t="n">
-        <v>0.5081714412488149</v>
+        <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I136" t="n">
-        <v>2.734300044523696</v>
+        <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K136" t="n">
         <v>0.08</v>
@@ -5494,28 +5494,28 @@
         <v>46023</v>
       </c>
       <c r="C137" t="n">
-        <v>0</v>
+        <v>5.960600090932976</v>
       </c>
       <c r="D137" t="n">
-        <v>740.8666506213059</v>
+        <v>253.5104218084386</v>
       </c>
       <c r="E137" t="n">
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>247.4515096086553</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I137" t="n">
-        <v>0</v>
+        <v>12.65336872859879</v>
       </c>
       <c r="J137" t="n">
-        <v>247.4515096086553</v>
+        <v>253.5104218084386</v>
       </c>
       <c r="K137" t="n">
         <v>0.017</v>
@@ -5531,28 +5531,28 @@
         <v>47849</v>
       </c>
       <c r="C138" t="n">
-        <v>0</v>
+        <v>88.26550936886187</v>
       </c>
       <c r="D138" t="n">
-        <v>740.8666506213059</v>
+        <v>325.9321163739264</v>
       </c>
       <c r="E138" t="n">
-        <v>0</v>
+        <v>79.83264197043273</v>
       </c>
       <c r="F138" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>78.71727381904972</v>
       </c>
       <c r="H138" t="n">
-        <v>318.6220023864096</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I138" t="n">
-        <v>0</v>
+        <v>98.58609171733501</v>
       </c>
       <c r="J138" t="n">
-        <v>318.6220023864096</v>
+        <v>325.9321163739264</v>
       </c>
       <c r="K138" t="n">
         <v>0.017</v>
@@ -5568,28 +5568,28 @@
         <v>49675</v>
       </c>
       <c r="C139" t="n">
-        <v>134.9610879995077</v>
+        <v>191.6302427530083</v>
       </c>
       <c r="D139" t="n">
-        <v>740.8666506213059</v>
+        <v>358.2067876833306</v>
       </c>
       <c r="E139" t="n">
-        <v>128.3457928130431</v>
+        <v>195.2558906349682</v>
       </c>
       <c r="F139" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G139" t="n">
-        <v>134.9610879995078</v>
+        <v>182.0820072031962</v>
       </c>
       <c r="H139" t="n">
-        <v>350.3390766016955</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I139" t="n">
-        <v>128.3457928130431</v>
+        <v>210.7284675877406</v>
       </c>
       <c r="J139" t="n">
-        <v>350.3390766016955</v>
+        <v>358.2067876833306</v>
       </c>
       <c r="K139" t="n">
         <v>0.017</v>
@@ -5605,28 +5605,28 @@
         <v>51502</v>
       </c>
       <c r="C140" t="n">
-        <v>167.7989381927821</v>
+        <v>221.6291925914218</v>
       </c>
       <c r="D140" t="n">
-        <v>740.8666506213059</v>
+        <v>375.6247269598206</v>
       </c>
       <c r="E140" t="n">
-        <v>162.8208749881784</v>
+        <v>239.4653241681159</v>
       </c>
       <c r="F140" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G140" t="n">
-        <v>167.7989381927822</v>
+        <v>226.4404884914111</v>
       </c>
       <c r="H140" t="n">
-        <v>367.4560928344465</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I140" t="n">
-        <v>162.8208749881783</v>
+        <v>239.4653241681159</v>
       </c>
       <c r="J140" t="n">
-        <v>367.4560928344465</v>
+        <v>375.6247269598206</v>
       </c>
       <c r="K140" t="n">
         <v>0.017</v>
@@ -5642,28 +5642,28 @@
         <v>53328</v>
       </c>
       <c r="C141" t="n">
-        <v>182.4354965458602</v>
+        <v>217.5719096054682</v>
       </c>
       <c r="D141" t="n">
-        <v>740.8666506213059</v>
+        <v>386.3769324110056</v>
       </c>
       <c r="E141" t="n">
-        <v>169.2415278060546</v>
+        <v>229.35037238597</v>
       </c>
       <c r="F141" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G141" t="n">
-        <v>182.4354965458602</v>
+        <v>217.5719096054682</v>
       </c>
       <c r="H141" t="n">
-        <v>378.0225365637701</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I141" t="n">
-        <v>169.2415278060546</v>
+        <v>229.35037238597</v>
       </c>
       <c r="J141" t="n">
-        <v>378.0225365637701</v>
+        <v>386.3769324110056</v>
       </c>
       <c r="K141" t="n">
         <v>0.017</v>
@@ -5679,28 +5679,28 @@
         <v>46023</v>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>13.4311923973082</v>
       </c>
       <c r="D142" t="n">
-        <v>285.007225067906</v>
+        <v>108.0450732373359</v>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>15.0839205582699</v>
       </c>
       <c r="F142" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>10.06307866641668</v>
       </c>
       <c r="H142" t="n">
-        <v>104.3219211043365</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I142" t="n">
-        <v>0</v>
+        <v>17.17662148034987</v>
       </c>
       <c r="J142" t="n">
-        <v>104.3219211043365</v>
+        <v>108.0450732373359</v>
       </c>
       <c r="K142" t="n">
         <v>0.08</v>
@@ -5716,28 +5716,28 @@
         <v>47849</v>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>35.18998804486672</v>
       </c>
       <c r="D143" t="n">
-        <v>285.007225067906</v>
+        <v>134.6260026807604</v>
       </c>
       <c r="E143" t="n">
-        <v>0</v>
+        <v>36.47578356606153</v>
       </c>
       <c r="F143" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>32.04704500241666</v>
       </c>
       <c r="H143" t="n">
-        <v>130.3840765833794</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I143" t="n">
-        <v>0</v>
+        <v>38.51773563563869</v>
       </c>
       <c r="J143" t="n">
-        <v>130.3840765833794</v>
+        <v>134.6260026807604</v>
       </c>
       <c r="K143" t="n">
         <v>0.08</v>
@@ -5753,28 +5753,28 @@
         <v>49675</v>
       </c>
       <c r="C144" t="n">
-        <v>49.15790618822192</v>
+        <v>76.23526232575273</v>
       </c>
       <c r="D144" t="n">
-        <v>285.007225067906</v>
+        <v>146.4717730128704</v>
       </c>
       <c r="E144" t="n">
-        <v>47.56605966096768</v>
+        <v>76.5058830904856</v>
       </c>
       <c r="F144" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G144" t="n">
-        <v>49.15790618822192</v>
+        <v>73.58627931722778</v>
       </c>
       <c r="H144" t="n">
-        <v>141.9986557056627</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I144" t="n">
-        <v>47.56605966096768</v>
+        <v>78.59791010693893</v>
       </c>
       <c r="J144" t="n">
-        <v>141.9986557056627</v>
+        <v>146.4717730128704</v>
       </c>
       <c r="K144" t="n">
         <v>0.08</v>
@@ -5790,28 +5790,28 @@
         <v>51502</v>
       </c>
       <c r="C145" t="n">
-        <v>63.92297824658233</v>
+        <v>89.62070182681427</v>
       </c>
       <c r="D145" t="n">
-        <v>285.007225067906</v>
+        <v>152.86467803582</v>
       </c>
       <c r="E145" t="n">
-        <v>63.28300450181493</v>
+        <v>91.5873071905466</v>
       </c>
       <c r="F145" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G145" t="n">
-        <v>63.92297824658233</v>
+        <v>89.62070182681427</v>
       </c>
       <c r="H145" t="n">
-        <v>148.2667918528765</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I145" t="n">
-        <v>63.28300450181493</v>
+        <v>91.5873071905466</v>
       </c>
       <c r="J145" t="n">
-        <v>148.2667918528765</v>
+        <v>152.86467803582</v>
       </c>
       <c r="K145" t="n">
         <v>0.08</v>
@@ -5827,28 +5827,28 @@
         <v>53328</v>
       </c>
       <c r="C146" t="n">
-        <v>65.81529390877152</v>
+        <v>84.44828512094161</v>
       </c>
       <c r="D146" t="n">
-        <v>285.007225067906</v>
+        <v>156.8110592434665</v>
       </c>
       <c r="E146" t="n">
-        <v>63.76201717990671</v>
+        <v>87.12987160549112</v>
       </c>
       <c r="F146" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G146" t="n">
-        <v>65.81529390877152</v>
+        <v>84.44828512094161</v>
       </c>
       <c r="H146" t="n">
-        <v>152.1361524345734</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I146" t="n">
-        <v>63.76201717990671</v>
+        <v>87.12987160549112</v>
       </c>
       <c r="J146" t="n">
-        <v>152.1361524345734</v>
+        <v>156.8110592434665</v>
       </c>
       <c r="K146" t="n">
         <v>0.08</v>
@@ -5867,25 +5867,25 @@
         <v>0</v>
       </c>
       <c r="D147" t="n">
-        <v>740.8666506213059</v>
+        <v>253.5104218084386</v>
       </c>
       <c r="E147" t="n">
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>247.4515096086553</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I147" t="n">
         <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>247.4515096086553</v>
+        <v>253.5104218084386</v>
       </c>
       <c r="K147" t="n">
         <v>0.017</v>
@@ -5904,25 +5904,25 @@
         <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>740.8666506213059</v>
+        <v>325.9321163739264</v>
       </c>
       <c r="E148" t="n">
         <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>318.6220023864096</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I148" t="n">
         <v>0</v>
       </c>
       <c r="J148" t="n">
-        <v>318.6220023864096</v>
+        <v>325.9321163739264</v>
       </c>
       <c r="K148" t="n">
         <v>0.017</v>
@@ -5941,25 +5941,25 @@
         <v>0</v>
       </c>
       <c r="D149" t="n">
-        <v>740.8666506213059</v>
+        <v>358.2067876833306</v>
       </c>
       <c r="E149" t="n">
         <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
       </c>
       <c r="H149" t="n">
-        <v>350.3390766016955</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I149" t="n">
         <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>350.3390766016955</v>
+        <v>358.2067876833306</v>
       </c>
       <c r="K149" t="n">
         <v>0.017</v>
@@ -5978,25 +5978,25 @@
         <v>0</v>
       </c>
       <c r="D150" t="n">
-        <v>740.8666506213059</v>
+        <v>375.6247269598206</v>
       </c>
       <c r="E150" t="n">
         <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
       </c>
       <c r="H150" t="n">
-        <v>367.4560928344465</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I150" t="n">
         <v>0</v>
       </c>
       <c r="J150" t="n">
-        <v>367.4560928344465</v>
+        <v>375.6247269598206</v>
       </c>
       <c r="K150" t="n">
         <v>0.017</v>
@@ -6015,25 +6015,25 @@
         <v>0</v>
       </c>
       <c r="D151" t="n">
-        <v>740.8666506213059</v>
+        <v>386.3769324110056</v>
       </c>
       <c r="E151" t="n">
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
       </c>
       <c r="H151" t="n">
-        <v>378.0225365637701</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I151" t="n">
         <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>378.0225365637701</v>
+        <v>386.3769324110056</v>
       </c>
       <c r="K151" t="n">
         <v>0.017</v>
@@ -6052,25 +6052,25 @@
         <v>0</v>
       </c>
       <c r="D152" t="n">
-        <v>285.007225067906</v>
+        <v>108.0450732373359</v>
       </c>
       <c r="E152" t="n">
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>104.3219211043365</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I152" t="n">
         <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>104.3219211043365</v>
+        <v>108.0450732373359</v>
       </c>
       <c r="K152" t="n">
         <v>0.08</v>
@@ -6089,25 +6089,25 @@
         <v>0</v>
       </c>
       <c r="D153" t="n">
-        <v>285.007225067906</v>
+        <v>134.6260026807604</v>
       </c>
       <c r="E153" t="n">
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>130.3840765833794</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I153" t="n">
         <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>130.3840765833794</v>
+        <v>134.6260026807604</v>
       </c>
       <c r="K153" t="n">
         <v>0.08</v>
@@ -6126,25 +6126,25 @@
         <v>0</v>
       </c>
       <c r="D154" t="n">
-        <v>285.007225067906</v>
+        <v>146.4717730128704</v>
       </c>
       <c r="E154" t="n">
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
       </c>
       <c r="H154" t="n">
-        <v>141.9986557056627</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I154" t="n">
         <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>141.9986557056627</v>
+        <v>146.4717730128704</v>
       </c>
       <c r="K154" t="n">
         <v>0.08</v>
@@ -6163,25 +6163,25 @@
         <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>285.007225067906</v>
+        <v>152.86467803582</v>
       </c>
       <c r="E155" t="n">
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>148.2667918528765</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I155" t="n">
         <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>148.2667918528765</v>
+        <v>152.86467803582</v>
       </c>
       <c r="K155" t="n">
         <v>0.08</v>
@@ -6200,25 +6200,25 @@
         <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>285.007225067906</v>
+        <v>156.8110592434665</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>152.1361524345734</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I156" t="n">
         <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>152.1361524345734</v>
+        <v>156.8110592434665</v>
       </c>
       <c r="K156" t="n">
         <v>0.08</v>
@@ -6237,25 +6237,25 @@
         <v>0</v>
       </c>
       <c r="D157" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E157" t="n">
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K157" t="n">
         <v>0.017</v>
@@ -6271,28 +6271,28 @@
         <v>47849</v>
       </c>
       <c r="C158" t="n">
-        <v>0</v>
+        <v>0.9479368870480998</v>
       </c>
       <c r="D158" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E158" t="n">
-        <v>0</v>
+        <v>0.3816178865997413</v>
       </c>
       <c r="F158" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>0.9479368870480998</v>
       </c>
       <c r="H158" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>0.3816178865997413</v>
       </c>
       <c r="J158" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K158" t="n">
         <v>0.017</v>
@@ -6308,28 +6308,28 @@
         <v>49675</v>
       </c>
       <c r="C159" t="n">
-        <v>91.94088229596224</v>
+        <v>143.9526841727568</v>
       </c>
       <c r="D159" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E159" t="n">
-        <v>98.08404054001248</v>
+        <v>115.3946325531683</v>
       </c>
       <c r="F159" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G159" t="n">
-        <v>91.94088229596213</v>
+        <v>143.9562315660591</v>
       </c>
       <c r="H159" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I159" t="n">
-        <v>98.08404054001259</v>
+        <v>117.506464132988</v>
       </c>
       <c r="J159" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K159" t="n">
         <v>0.017</v>
@@ -6345,28 +6345,28 @@
         <v>51502</v>
       </c>
       <c r="C160" t="n">
-        <v>98.27067454516778</v>
+        <v>175.5020756782621</v>
       </c>
       <c r="D160" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E160" t="n">
-        <v>100.6013494594263</v>
+        <v>155.3213163420436</v>
       </c>
       <c r="F160" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G160" t="n">
-        <v>98.27067454516778</v>
+        <v>175.179858208031</v>
       </c>
       <c r="H160" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I160" t="n">
-        <v>100.6013494594263</v>
+        <v>155.3213163420436</v>
       </c>
       <c r="J160" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K160" t="n">
         <v>0.017</v>
@@ -6382,28 +6382,28 @@
         <v>53328</v>
       </c>
       <c r="C161" t="n">
-        <v>104.1608299065391</v>
+        <v>223.8356393722509</v>
       </c>
       <c r="D161" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E161" t="n">
-        <v>119.1264998400339</v>
+        <v>204.4093979862431</v>
       </c>
       <c r="F161" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G161" t="n">
-        <v>104.1608299065391</v>
+        <v>222.8589756015262</v>
       </c>
       <c r="H161" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I161" t="n">
-        <v>119.1264998400339</v>
+        <v>204.4093979862431</v>
       </c>
       <c r="J161" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K161" t="n">
         <v>0.017</v>
@@ -6422,25 +6422,25 @@
         <v>0</v>
       </c>
       <c r="D162" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E162" t="n">
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I162" t="n">
         <v>0</v>
       </c>
       <c r="J162" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K162" t="n">
         <v>0.08</v>
@@ -6459,25 +6459,25 @@
         <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E163" t="n">
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I163" t="n">
         <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K163" t="n">
         <v>0.08</v>
@@ -6493,28 +6493,28 @@
         <v>49675</v>
       </c>
       <c r="C164" t="n">
-        <v>31.61809716730435</v>
+        <v>39.26266514781521</v>
       </c>
       <c r="D164" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E164" t="n">
-        <v>32.52006418480708</v>
+        <v>36.86501081974302</v>
       </c>
       <c r="F164" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G164" t="n">
-        <v>31.61809716730435</v>
+        <v>38.54353442544863</v>
       </c>
       <c r="H164" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I164" t="n">
-        <v>32.52006418480708</v>
+        <v>36.85659398226964</v>
       </c>
       <c r="J164" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K164" t="n">
         <v>0.08</v>
@@ -6530,28 +6530,28 @@
         <v>51502</v>
       </c>
       <c r="C165" t="n">
-        <v>41.59206472065583</v>
+        <v>59.64028466233725</v>
       </c>
       <c r="D165" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E165" t="n">
-        <v>41.6514941696421</v>
+        <v>57.71234434075127</v>
       </c>
       <c r="F165" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G165" t="n">
-        <v>41.59206472065583</v>
+        <v>59.64028466233724</v>
       </c>
       <c r="H165" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I165" t="n">
-        <v>41.6514941696421</v>
+        <v>57.71234434075127</v>
       </c>
       <c r="J165" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K165" t="n">
         <v>0.08</v>
@@ -6567,28 +6567,28 @@
         <v>53328</v>
       </c>
       <c r="C166" t="n">
-        <v>41.86820285275004</v>
+        <v>68.84331447848078</v>
       </c>
       <c r="D166" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E166" t="n">
-        <v>43.90678153607401</v>
+        <v>66.20039303607763</v>
       </c>
       <c r="F166" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G166" t="n">
-        <v>41.86820285275004</v>
+        <v>68.84331447848078</v>
       </c>
       <c r="H166" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I166" t="n">
-        <v>43.90678153607402</v>
+        <v>66.20039303607763</v>
       </c>
       <c r="J166" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K166" t="n">
         <v>0.08</v>
@@ -6607,25 +6607,25 @@
         <v>0</v>
       </c>
       <c r="D167" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E167" t="n">
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I167" t="n">
         <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K167" t="n">
         <v>0.017</v>
@@ -6644,25 +6644,25 @@
         <v>0</v>
       </c>
       <c r="D168" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E168" t="n">
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I168" t="n">
         <v>0</v>
       </c>
       <c r="J168" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K168" t="n">
         <v>0.017</v>
@@ -6681,25 +6681,25 @@
         <v>0</v>
       </c>
       <c r="D169" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E169" t="n">
         <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
       </c>
       <c r="H169" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I169" t="n">
         <v>0</v>
       </c>
       <c r="J169" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K169" t="n">
         <v>0.017</v>
@@ -6718,25 +6718,25 @@
         <v>0</v>
       </c>
       <c r="D170" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E170" t="n">
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
       </c>
       <c r="H170" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I170" t="n">
         <v>0</v>
       </c>
       <c r="J170" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K170" t="n">
         <v>0.017</v>
@@ -6755,25 +6755,25 @@
         <v>0</v>
       </c>
       <c r="D171" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E171" t="n">
         <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I171" t="n">
         <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K171" t="n">
         <v>0.017</v>
@@ -6792,25 +6792,25 @@
         <v>0</v>
       </c>
       <c r="D172" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E172" t="n">
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
       </c>
       <c r="H172" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I172" t="n">
         <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K172" t="n">
         <v>0.08</v>
@@ -6829,25 +6829,25 @@
         <v>0</v>
       </c>
       <c r="D173" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E173" t="n">
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
       </c>
       <c r="H173" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I173" t="n">
         <v>0</v>
       </c>
       <c r="J173" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K173" t="n">
         <v>0.08</v>
@@ -6866,25 +6866,25 @@
         <v>0</v>
       </c>
       <c r="D174" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E174" t="n">
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
       </c>
       <c r="H174" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I174" t="n">
         <v>0</v>
       </c>
       <c r="J174" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K174" t="n">
         <v>0.08</v>
@@ -6903,25 +6903,25 @@
         <v>0</v>
       </c>
       <c r="D175" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E175" t="n">
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
       </c>
       <c r="H175" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I175" t="n">
         <v>0</v>
       </c>
       <c r="J175" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K175" t="n">
         <v>0.08</v>
@@ -6940,25 +6940,25 @@
         <v>0</v>
       </c>
       <c r="D176" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E176" t="n">
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I176" t="n">
         <v>0</v>
       </c>
       <c r="J176" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K176" t="n">
         <v>0.08</v>
@@ -6977,25 +6977,25 @@
         <v>0</v>
       </c>
       <c r="D177" t="n">
-        <v>740.8666506213059</v>
+        <v>46.59616059878885</v>
       </c>
       <c r="E177" t="n">
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>44.11202657958206</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I177" t="n">
         <v>0</v>
       </c>
       <c r="J177" t="n">
-        <v>44.11202657958206</v>
+        <v>46.59616059878885</v>
       </c>
       <c r="K177" t="n">
         <v>0.017</v>
@@ -7014,25 +7014,25 @@
         <v>0</v>
       </c>
       <c r="D178" t="n">
-        <v>740.8666506213059</v>
+        <v>59.02198672273944</v>
       </c>
       <c r="E178" t="n">
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
       </c>
       <c r="H178" t="n">
-        <v>56.32317648042529</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I178" t="n">
         <v>0</v>
       </c>
       <c r="J178" t="n">
-        <v>56.32317648042529</v>
+        <v>59.02198672273944</v>
       </c>
       <c r="K178" t="n">
         <v>0.017</v>
@@ -7051,25 +7051,25 @@
         <v>0</v>
       </c>
       <c r="D179" t="n">
-        <v>740.8666506213059</v>
+        <v>67.21391127239798</v>
       </c>
       <c r="E179" t="n">
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
       </c>
       <c r="H179" t="n">
-        <v>64.37357229752645</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I179" t="n">
         <v>0</v>
       </c>
       <c r="J179" t="n">
-        <v>64.37357229752645</v>
+        <v>67.21391127239798</v>
       </c>
       <c r="K179" t="n">
         <v>0.017</v>
@@ -7088,25 +7088,25 @@
         <v>0</v>
       </c>
       <c r="D180" t="n">
-        <v>740.8666506213059</v>
+        <v>73.17911008830633</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
       </c>
       <c r="H180" t="n">
-        <v>70.23571266572199</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I180" t="n">
         <v>0</v>
       </c>
       <c r="J180" t="n">
-        <v>70.23571266572199</v>
+        <v>73.17911008830633</v>
       </c>
       <c r="K180" t="n">
         <v>0.017</v>
@@ -7125,25 +7125,25 @@
         <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>740.8666506213059</v>
+        <v>77.79663527637209</v>
       </c>
       <c r="E181" t="n">
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>74.77346264547654</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I181" t="n">
         <v>0</v>
       </c>
       <c r="J181" t="n">
-        <v>74.77346264547654</v>
+        <v>77.79663527637209</v>
       </c>
       <c r="K181" t="n">
         <v>0.017</v>
@@ -7162,25 +7162,25 @@
         <v>0</v>
       </c>
       <c r="D182" t="n">
-        <v>285.007225067906</v>
+        <v>32.10134655363332</v>
       </c>
       <c r="E182" t="n">
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
       </c>
       <c r="H182" t="n">
-        <v>29.86037089025183</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I182" t="n">
         <v>0</v>
       </c>
       <c r="J182" t="n">
-        <v>29.86037089025183</v>
+        <v>32.10134655363332</v>
       </c>
       <c r="K182" t="n">
         <v>0.08</v>
@@ -7199,25 +7199,25 @@
         <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>285.007225067906</v>
+        <v>36.66199663864789</v>
       </c>
       <c r="E183" t="n">
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
       </c>
       <c r="H183" t="n">
-        <v>34.33201180311551</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I183" t="n">
         <v>0</v>
       </c>
       <c r="J183" t="n">
-        <v>34.33201180311551</v>
+        <v>36.66199663864789</v>
       </c>
       <c r="K183" t="n">
         <v>0.08</v>
@@ -7236,25 +7236,25 @@
         <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>285.007225067906</v>
+        <v>39.66867812776202</v>
       </c>
       <c r="E184" t="n">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
       </c>
       <c r="H184" t="n">
-        <v>37.280012572315</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I184" t="n">
         <v>0</v>
       </c>
       <c r="J184" t="n">
-        <v>37.280012572315</v>
+        <v>39.66867812776202</v>
       </c>
       <c r="K184" t="n">
         <v>0.08</v>
@@ -7273,25 +7273,25 @@
         <v>0</v>
       </c>
       <c r="D185" t="n">
-        <v>285.007225067906</v>
+        <v>41.8580846280239</v>
       </c>
       <c r="E185" t="n">
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
       </c>
       <c r="H185" t="n">
-        <v>39.42668892304613</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I185" t="n">
         <v>0</v>
       </c>
       <c r="J185" t="n">
-        <v>39.42668892304613</v>
+        <v>41.8580846280239</v>
       </c>
       <c r="K185" t="n">
         <v>0.08</v>
@@ -7310,25 +7310,25 @@
         <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>285.007225067906</v>
+        <v>43.552854571804</v>
       </c>
       <c r="E186" t="n">
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
       </c>
       <c r="H186" t="n">
-        <v>41.0883824266543</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I186" t="n">
         <v>0</v>
       </c>
       <c r="J186" t="n">
-        <v>41.0883824266543</v>
+        <v>43.552854571804</v>
       </c>
       <c r="K186" t="n">
         <v>0.08</v>
@@ -7344,28 +7344,28 @@
         <v>46023</v>
       </c>
       <c r="C187" t="n">
-        <v>0</v>
+        <v>27.62587522183637</v>
       </c>
       <c r="D187" t="n">
-        <v>740.8666506213059</v>
+        <v>46.59616059878885</v>
       </c>
       <c r="E187" t="n">
-        <v>0</v>
+        <v>46.37932496873859</v>
       </c>
       <c r="F187" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G187" t="n">
-        <v>0</v>
+        <v>42.63985297213146</v>
       </c>
       <c r="H187" t="n">
-        <v>44.11202657958206</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I187" t="n">
-        <v>0</v>
+        <v>27.62587522183637</v>
       </c>
       <c r="J187" t="n">
-        <v>44.11202657958206</v>
+        <v>46.59616059878885</v>
       </c>
       <c r="K187" t="n">
         <v>0.017</v>
@@ -7381,28 +7381,28 @@
         <v>47849</v>
       </c>
       <c r="C188" t="n">
-        <v>17.17726521125602</v>
+        <v>33.99771171912063</v>
       </c>
       <c r="D188" t="n">
-        <v>740.8666506213059</v>
+        <v>59.02198672273944</v>
       </c>
       <c r="E188" t="n">
-        <v>6.924244161127699</v>
+        <v>47.44801062004103</v>
       </c>
       <c r="F188" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G188" t="n">
-        <v>17.17726521125604</v>
+        <v>43.54594726893275</v>
       </c>
       <c r="H188" t="n">
-        <v>56.32317648042529</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I188" t="n">
-        <v>6.924244161127699</v>
+        <v>28.69456087313882</v>
       </c>
       <c r="J188" t="n">
-        <v>56.32317648042529</v>
+        <v>59.02198672273944</v>
       </c>
       <c r="K188" t="n">
         <v>0.017</v>
@@ -7418,28 +7418,28 @@
         <v>49675</v>
       </c>
       <c r="C189" t="n">
-        <v>17.17726521125602</v>
+        <v>33.99771171912063</v>
       </c>
       <c r="D189" t="n">
-        <v>740.8666506213059</v>
+        <v>67.21391127239798</v>
       </c>
       <c r="E189" t="n">
-        <v>6.924244161127698</v>
+        <v>47.44801062004103</v>
       </c>
       <c r="F189" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G189" t="n">
-        <v>17.17726521125604</v>
+        <v>43.54594726893275</v>
       </c>
       <c r="H189" t="n">
-        <v>64.37357229752645</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I189" t="n">
-        <v>6.924244161127699</v>
+        <v>28.69456087313882</v>
       </c>
       <c r="J189" t="n">
-        <v>64.37357229752645</v>
+        <v>67.21391127239798</v>
       </c>
       <c r="K189" t="n">
         <v>0.017</v>
@@ -7455,28 +7455,28 @@
         <v>51502</v>
       </c>
       <c r="C190" t="n">
-        <v>17.17726521125602</v>
+        <v>6.371836497284264</v>
       </c>
       <c r="D190" t="n">
-        <v>740.8666506213059</v>
+        <v>73.17911008830633</v>
       </c>
       <c r="E190" t="n">
-        <v>6.924244161127699</v>
+        <v>1.068685651302448</v>
       </c>
       <c r="F190" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G190" t="n">
-        <v>17.17726521125604</v>
+        <v>0.9060942968012863</v>
       </c>
       <c r="H190" t="n">
-        <v>70.23571266572199</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I190" t="n">
-        <v>6.924244161127699</v>
+        <v>1.068685651302448</v>
       </c>
       <c r="J190" t="n">
-        <v>70.23571266572199</v>
+        <v>73.17911008830633</v>
       </c>
       <c r="K190" t="n">
         <v>0.017</v>
@@ -7495,25 +7495,25 @@
         <v>0</v>
       </c>
       <c r="D191" t="n">
-        <v>740.8666506213059</v>
+        <v>77.79663527637209</v>
       </c>
       <c r="E191" t="n">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>740.8666506213059</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
       </c>
       <c r="H191" t="n">
-        <v>74.77346264547654</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I191" t="n">
         <v>0</v>
       </c>
       <c r="J191" t="n">
-        <v>74.77346264547654</v>
+        <v>77.79663527637209</v>
       </c>
       <c r="K191" t="n">
         <v>0.017</v>
@@ -7529,28 +7529,28 @@
         <v>46023</v>
       </c>
       <c r="C192" t="n">
-        <v>0</v>
+        <v>9.418528307983514</v>
       </c>
       <c r="D192" t="n">
-        <v>285.007225067906</v>
+        <v>32.10134655363332</v>
       </c>
       <c r="E192" t="n">
-        <v>0</v>
+        <v>11.51122923006349</v>
       </c>
       <c r="F192" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G192" t="n">
-        <v>0</v>
+        <v>12.78664203887503</v>
       </c>
       <c r="H192" t="n">
-        <v>29.86037089025183</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I192" t="n">
-        <v>0</v>
+        <v>9.418528307983514</v>
       </c>
       <c r="J192" t="n">
-        <v>29.86037089025183</v>
+        <v>32.10134655363332</v>
       </c>
       <c r="K192" t="n">
         <v>0.08</v>
@@ -7566,28 +7566,28 @@
         <v>47849</v>
       </c>
       <c r="C193" t="n">
-        <v>1.660282353034576</v>
+        <v>9.418528307983514</v>
       </c>
       <c r="D193" t="n">
-        <v>285.007225067906</v>
+        <v>36.66199663864789</v>
       </c>
       <c r="E193" t="n">
-        <v>0</v>
+        <v>11.51122923006349</v>
       </c>
       <c r="F193" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G193" t="n">
-        <v>1.660282353034576</v>
+        <v>12.78664203887503</v>
       </c>
       <c r="H193" t="n">
-        <v>34.33201180311551</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I193" t="n">
-        <v>0</v>
+        <v>9.418528307983514</v>
       </c>
       <c r="J193" t="n">
-        <v>34.33201180311551</v>
+        <v>36.66199663864789</v>
       </c>
       <c r="K193" t="n">
         <v>0.08</v>
@@ -7603,28 +7603,28 @@
         <v>49675</v>
       </c>
       <c r="C194" t="n">
-        <v>1.660282353034576</v>
+        <v>9.418528307983514</v>
       </c>
       <c r="D194" t="n">
-        <v>285.007225067906</v>
+        <v>39.66867812776202</v>
       </c>
       <c r="E194" t="n">
-        <v>0</v>
+        <v>11.51122923006349</v>
       </c>
       <c r="F194" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G194" t="n">
-        <v>1.660282353034576</v>
+        <v>12.78664203887503</v>
       </c>
       <c r="H194" t="n">
-        <v>37.280012572315</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I194" t="n">
-        <v>0</v>
+        <v>9.418528307983514</v>
       </c>
       <c r="J194" t="n">
-        <v>37.280012572315</v>
+        <v>39.66867812776202</v>
       </c>
       <c r="K194" t="n">
         <v>0.08</v>
@@ -7640,28 +7640,28 @@
         <v>51502</v>
       </c>
       <c r="C195" t="n">
-        <v>1.660282353034576</v>
+        <v>0</v>
       </c>
       <c r="D195" t="n">
-        <v>285.007225067906</v>
+        <v>41.8580846280239</v>
       </c>
       <c r="E195" t="n">
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G195" t="n">
-        <v>1.660282353034576</v>
+        <v>0</v>
       </c>
       <c r="H195" t="n">
-        <v>39.42668892304613</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I195" t="n">
         <v>0</v>
       </c>
       <c r="J195" t="n">
-        <v>39.42668892304613</v>
+        <v>41.8580846280239</v>
       </c>
       <c r="K195" t="n">
         <v>0.08</v>
@@ -7680,25 +7680,25 @@
         <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>285.007225067906</v>
+        <v>43.552854571804</v>
       </c>
       <c r="E196" t="n">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>285.007225067906</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
       </c>
       <c r="H196" t="n">
-        <v>41.0883824266543</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I196" t="n">
         <v>0</v>
       </c>
       <c r="J196" t="n">
-        <v>41.0883824266543</v>
+        <v>43.552854571804</v>
       </c>
       <c r="K196" t="n">
         <v>0.08</v>
@@ -7717,7 +7717,7 @@
         <v>0</v>
       </c>
       <c r="D197" t="n">
-        <v>4</v>
+        <v>1.717300224897027</v>
       </c>
       <c r="E197" t="n">
         <v>0</v>
@@ -7729,7 +7729,7 @@
         <v>0</v>
       </c>
       <c r="H197" t="n">
-        <v>1.717300224897027</v>
+        <v>4</v>
       </c>
       <c r="I197" t="n">
         <v>0</v>
@@ -7752,7 +7752,7 @@
         <v>0</v>
       </c>
       <c r="D198" t="n">
-        <v>4</v>
+        <v>2.246209584507109</v>
       </c>
       <c r="E198" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         <v>0</v>
       </c>
       <c r="H198" t="n">
-        <v>2.246209584507109</v>
+        <v>4</v>
       </c>
       <c r="I198" t="n">
         <v>0</v>
@@ -7787,7 +7787,7 @@
         <v>0</v>
       </c>
       <c r="D199" t="n">
-        <v>4</v>
+        <v>2.4982276762293</v>
       </c>
       <c r="E199" t="n">
         <v>0</v>
@@ -7799,7 +7799,7 @@
         <v>0</v>
       </c>
       <c r="H199" t="n">
-        <v>2.4982276762293</v>
+        <v>4</v>
       </c>
       <c r="I199" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>0</v>
       </c>
       <c r="D200" t="n">
-        <v>4</v>
+        <v>2.648951845381237</v>
       </c>
       <c r="E200" t="n">
         <v>0</v>
@@ -7834,7 +7834,7 @@
         <v>0</v>
       </c>
       <c r="H200" t="n">
-        <v>2.648951845381237</v>
+        <v>4</v>
       </c>
       <c r="I200" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
         <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>4</v>
+        <v>2.752635411261187</v>
       </c>
       <c r="E201" t="n">
         <v>0</v>
@@ -7869,7 +7869,7 @@
         <v>0</v>
       </c>
       <c r="H201" t="n">
-        <v>2.752635411261187</v>
+        <v>4</v>
       </c>
       <c r="I201" t="n">
         <v>0</v>
@@ -7892,7 +7892,7 @@
         <v>0</v>
       </c>
       <c r="D202" t="n">
-        <v>4</v>
+        <v>1.717300224897027</v>
       </c>
       <c r="E202" t="n">
         <v>0</v>
@@ -7904,7 +7904,7 @@
         <v>0</v>
       </c>
       <c r="H202" t="n">
-        <v>1.717300224897027</v>
+        <v>4</v>
       </c>
       <c r="I202" t="n">
         <v>0</v>
@@ -7927,7 +7927,7 @@
         <v>0</v>
       </c>
       <c r="D203" t="n">
-        <v>4</v>
+        <v>2.246209584507109</v>
       </c>
       <c r="E203" t="n">
         <v>0</v>
@@ -7939,7 +7939,7 @@
         <v>0</v>
       </c>
       <c r="H203" t="n">
-        <v>2.246209584507109</v>
+        <v>4</v>
       </c>
       <c r="I203" t="n">
         <v>0</v>
@@ -7962,7 +7962,7 @@
         <v>0</v>
       </c>
       <c r="D204" t="n">
-        <v>4</v>
+        <v>2.4982276762293</v>
       </c>
       <c r="E204" t="n">
         <v>0</v>
@@ -7974,7 +7974,7 @@
         <v>0</v>
       </c>
       <c r="H204" t="n">
-        <v>2.4982276762293</v>
+        <v>4</v>
       </c>
       <c r="I204" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
         <v>0</v>
       </c>
       <c r="D205" t="n">
-        <v>4</v>
+        <v>2.648951845381237</v>
       </c>
       <c r="E205" t="n">
         <v>0</v>
@@ -8009,7 +8009,7 @@
         <v>0</v>
       </c>
       <c r="H205" t="n">
-        <v>2.648951845381237</v>
+        <v>4</v>
       </c>
       <c r="I205" t="n">
         <v>0</v>
@@ -8032,7 +8032,7 @@
         <v>0</v>
       </c>
       <c r="D206" t="n">
-        <v>4</v>
+        <v>2.752635411261187</v>
       </c>
       <c r="E206" t="n">
         <v>0</v>
@@ -8044,7 +8044,7 @@
         <v>0</v>
       </c>
       <c r="H206" t="n">
-        <v>2.752635411261187</v>
+        <v>4</v>
       </c>
       <c r="I206" t="n">
         <v>0</v>
@@ -8067,7 +8067,7 @@
         <v>0</v>
       </c>
       <c r="D207" t="n">
-        <v>4</v>
+        <v>1.717300224897027</v>
       </c>
       <c r="E207" t="n">
         <v>0</v>
@@ -8079,7 +8079,7 @@
         <v>0</v>
       </c>
       <c r="H207" t="n">
-        <v>1.717300224897027</v>
+        <v>4</v>
       </c>
       <c r="I207" t="n">
         <v>0</v>
@@ -8102,7 +8102,7 @@
         <v>0</v>
       </c>
       <c r="D208" t="n">
-        <v>4</v>
+        <v>2.246209584507109</v>
       </c>
       <c r="E208" t="n">
         <v>0</v>
@@ -8114,7 +8114,7 @@
         <v>0</v>
       </c>
       <c r="H208" t="n">
-        <v>2.246209584507109</v>
+        <v>4</v>
       </c>
       <c r="I208" t="n">
         <v>0</v>
@@ -8137,7 +8137,7 @@
         <v>0</v>
       </c>
       <c r="D209" t="n">
-        <v>4</v>
+        <v>2.4982276762293</v>
       </c>
       <c r="E209" t="n">
         <v>0</v>
@@ -8149,7 +8149,7 @@
         <v>0</v>
       </c>
       <c r="H209" t="n">
-        <v>2.4982276762293</v>
+        <v>4</v>
       </c>
       <c r="I209" t="n">
         <v>0</v>
@@ -8172,7 +8172,7 @@
         <v>0</v>
       </c>
       <c r="D210" t="n">
-        <v>4</v>
+        <v>2.648951845381237</v>
       </c>
       <c r="E210" t="n">
         <v>0</v>
@@ -8184,7 +8184,7 @@
         <v>0</v>
       </c>
       <c r="H210" t="n">
-        <v>2.648951845381237</v>
+        <v>4</v>
       </c>
       <c r="I210" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
         <v>0</v>
       </c>
       <c r="D211" t="n">
-        <v>4</v>
+        <v>2.752635411261187</v>
       </c>
       <c r="E211" t="n">
         <v>0</v>
@@ -8219,7 +8219,7 @@
         <v>0</v>
       </c>
       <c r="H211" t="n">
-        <v>2.752635411261187</v>
+        <v>4</v>
       </c>
       <c r="I211" t="n">
         <v>0</v>

--- a/data/Ascona/investment_decision/aggregated_investment_decision.xlsx
+++ b/data/Ascona/investment_decision/aggregated_investment_decision.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K211"/>
+  <dimension ref="A1:K216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,42 +445,42 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>scen_base_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>scen_base_candidate_unit</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>scen_base_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>scen_base_candidate_unit</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_dr_invested_available_unit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_candidate_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -499,25 +499,25 @@
         <v>46023</v>
       </c>
       <c r="C2" t="n">
-        <v>1366.847597082856</v>
+        <v>714.1214113422864</v>
       </c>
       <c r="D2" t="n">
         <v>1605043.354558521</v>
       </c>
       <c r="E2" t="n">
-        <v>847.7443384878072</v>
+        <v>720.9452547858833</v>
       </c>
       <c r="F2" t="n">
         <v>1605043.354558521</v>
       </c>
       <c r="G2" t="n">
-        <v>956.4278098584418</v>
+        <v>714.1214113422863</v>
       </c>
       <c r="H2" t="n">
         <v>1605043.354558521</v>
       </c>
       <c r="I2" t="n">
-        <v>1124.281344650894</v>
+        <v>720.9452547858848</v>
       </c>
       <c r="J2" t="n">
         <v>1605043.354558521</v>
@@ -536,25 +536,25 @@
         <v>47849</v>
       </c>
       <c r="C3" t="n">
-        <v>3616.440094609093</v>
+        <v>1978.675657349517</v>
       </c>
       <c r="D3" t="n">
         <v>1605043.354558521</v>
       </c>
       <c r="E3" t="n">
-        <v>3289.772295648221</v>
+        <v>2121.716569184455</v>
       </c>
       <c r="F3" t="n">
         <v>1605043.354558521</v>
       </c>
       <c r="G3" t="n">
-        <v>3568.403681074913</v>
+        <v>1978.675657349516</v>
       </c>
       <c r="H3" t="n">
         <v>1605043.354558521</v>
       </c>
       <c r="I3" t="n">
-        <v>3289.772295648221</v>
+        <v>2121.716569184455</v>
       </c>
       <c r="J3" t="n">
         <v>1605043.354558521</v>
@@ -573,25 +573,25 @@
         <v>49675</v>
       </c>
       <c r="C4" t="n">
-        <v>7052.903073940413</v>
+        <v>5201.491406860947</v>
       </c>
       <c r="D4" t="n">
         <v>1605043.354558521</v>
       </c>
       <c r="E4" t="n">
-        <v>7580.749456673175</v>
+        <v>5203.219153523965</v>
       </c>
       <c r="F4" t="n">
         <v>1605043.354558521</v>
       </c>
       <c r="G4" t="n">
-        <v>7052.742258777374</v>
+        <v>5201.49140686095</v>
       </c>
       <c r="H4" t="n">
         <v>1605043.354558521</v>
       </c>
       <c r="I4" t="n">
-        <v>7635.685350249907</v>
+        <v>5203.219153523969</v>
       </c>
       <c r="J4" t="n">
         <v>1605043.354558521</v>
@@ -610,25 +610,25 @@
         <v>51502</v>
       </c>
       <c r="C5" t="n">
-        <v>8425.584725451325</v>
+        <v>6395.510628842872</v>
       </c>
       <c r="D5" t="n">
         <v>1605043.354558521</v>
       </c>
       <c r="E5" t="n">
-        <v>8764.035479909719</v>
+        <v>6289.059761992062</v>
       </c>
       <c r="F5" t="n">
         <v>1605043.354558521</v>
       </c>
       <c r="G5" t="n">
-        <v>8469.860149724183</v>
+        <v>6395.510628842871</v>
       </c>
       <c r="H5" t="n">
         <v>1605043.354558521</v>
       </c>
       <c r="I5" t="n">
-        <v>8764.035479909719</v>
+        <v>6289.059761992061</v>
       </c>
       <c r="J5" t="n">
         <v>1605043.354558521</v>
@@ -647,25 +647,25 @@
         <v>53328</v>
       </c>
       <c r="C6" t="n">
-        <v>8425.847023822984</v>
+        <v>6395.510628842872</v>
       </c>
       <c r="D6" t="n">
         <v>1605043.354558521</v>
       </c>
       <c r="E6" t="n">
-        <v>8764.297778281376</v>
+        <v>6289.059761992063</v>
       </c>
       <c r="F6" t="n">
         <v>1605043.354558521</v>
       </c>
       <c r="G6" t="n">
-        <v>8470.122448095841</v>
+        <v>6395.510628842871</v>
       </c>
       <c r="H6" t="n">
         <v>1605043.354558521</v>
       </c>
       <c r="I6" t="n">
-        <v>8764.297778281376</v>
+        <v>6289.059761992061</v>
       </c>
       <c r="J6" t="n">
         <v>1605043.354558521</v>
@@ -677,7 +677,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh</t>
+          <t>BLVL_Li-ion_s_12.5 kWh</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -687,34 +687,34 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1428.094882948866</v>
+        <v>3846.786195505618</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2407.565031837782</v>
+        <v>2336.996515957009</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2407.565031837782</v>
+        <v>2336.996515957009</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1428.094882948866</v>
+        <v>3846.786195505618</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh</t>
+          <t>BLVL_Li-ion_s_12.5 kWh</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -724,34 +724,34 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1709.588185921052</v>
+        <v>3846.786195505618</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2407.565031837782</v>
+        <v>2770.900177208512</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2407.565031837782</v>
+        <v>2770.900177208512</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1709.588185921052</v>
+        <v>3846.786195505618</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh</t>
+          <t>BLVL_Li-ion_s_12.5 kWh</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -761,34 +761,34 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1824.896331921844</v>
+        <v>3846.786195505618</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2407.565031837782</v>
+        <v>2948.640202259162</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2407.565031837782</v>
+        <v>2948.640202259162</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1824.896331921844</v>
+        <v>3846.786195505618</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh</t>
+          <t>BLVL_Li-ion_s_12.5 kWh</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -798,34 +798,34 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1886.533812811128</v>
+        <v>3846.786195505618</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2407.565031837782</v>
+        <v>3043.65037957348</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2407.565031837782</v>
+        <v>3043.65037957348</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1886.533812811128</v>
+        <v>3846.786195505618</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh</t>
+          <t>BLVL_Li-ion_s_12.5 kWh</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -835,28 +835,28 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1925.049290525592</v>
+        <v>3846.786195505618</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2407.565031837782</v>
+        <v>3103.019489313216</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2407.565031837782</v>
+        <v>3103.019489313216</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1925.049290525592</v>
+        <v>3846.786195505618</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="12">
@@ -872,25 +872,25 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
+        <v>39.3819486954109</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
         <v>12.02681808690701</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12.02681808690701</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
         <v>39.3819486954109</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>39.3819486954109</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>12.02681808690701</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -909,25 +909,25 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
+        <v>39.3819486954109</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
         <v>16.55360533516066</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>16.55360533516066</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
         <v>39.3819486954109</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>39.3819486954109</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>16.55360533516066</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -946,25 +946,25 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
+        <v>39.3819486954109</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
         <v>18.8204631381465</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>18.8204631381465</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
         <v>39.3819486954109</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>39.3819486954109</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>18.8204631381465</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -983,25 +983,25 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
+        <v>39.3819486954109</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
         <v>20.15059880314304</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>20.15059880314304</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
         <v>39.3819486954109</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>39.3819486954109</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>20.15059880314304</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1020,25 +1020,25 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
+        <v>39.3819486954109</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
         <v>21.01808582652089</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>21.01808582652089</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
         <v>39.3819486954109</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>39.3819486954109</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>21.01808582652089</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1054,28 +1054,28 @@
         <v>46023</v>
       </c>
       <c r="C17" t="n">
-        <v>1.744576111630544</v>
+        <v>1.525321643316135</v>
       </c>
       <c r="D17" t="n">
+        <v>39.3819486954109</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.532093267471386</v>
+      </c>
+      <c r="F17" t="n">
         <v>12.02681808690701</v>
       </c>
-      <c r="E17" t="n">
-        <v>1.744576111630546</v>
-      </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
+        <v>1.525321643316133</v>
+      </c>
+      <c r="H17" t="n">
+        <v>12.02681808690701</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.532093267471388</v>
+      </c>
+      <c r="J17" t="n">
         <v>39.3819486954109</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1.744576111630544</v>
-      </c>
-      <c r="H17" t="n">
-        <v>39.3819486954109</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1.744576111630545</v>
-      </c>
-      <c r="J17" t="n">
-        <v>12.02681808690701</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
@@ -1091,28 +1091,28 @@
         <v>47849</v>
       </c>
       <c r="C18" t="n">
-        <v>1.764862770177136</v>
+        <v>1.551227221376899</v>
       </c>
       <c r="D18" t="n">
+        <v>39.3819486954109</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.568377997554964</v>
+      </c>
+      <c r="F18" t="n">
         <v>16.55360533516066</v>
       </c>
-      <c r="E18" t="n">
-        <v>1.764862770177137</v>
-      </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
+        <v>1.551227221376899</v>
+      </c>
+      <c r="H18" t="n">
+        <v>16.55360533516066</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.568377997554965</v>
+      </c>
+      <c r="J18" t="n">
         <v>39.3819486954109</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1.764862770177136</v>
-      </c>
-      <c r="H18" t="n">
-        <v>39.3819486954109</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1.764862770177137</v>
-      </c>
-      <c r="J18" t="n">
-        <v>16.55360533516066</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -1128,28 +1128,28 @@
         <v>49675</v>
       </c>
       <c r="C19" t="n">
-        <v>1.781337669389687</v>
+        <v>1.720976778552193</v>
       </c>
       <c r="D19" t="n">
+        <v>39.3819486954109</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.745651208309831</v>
+      </c>
+      <c r="F19" t="n">
         <v>18.8204631381465</v>
       </c>
-      <c r="E19" t="n">
-        <v>1.781088598481704</v>
-      </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
+        <v>1.720976778552194</v>
+      </c>
+      <c r="H19" t="n">
+        <v>18.8204631381465</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.745651208309831</v>
+      </c>
+      <c r="J19" t="n">
         <v>39.3819486954109</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1.781337669389687</v>
-      </c>
-      <c r="H19" t="n">
-        <v>39.3819486954109</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1.781088598481703</v>
-      </c>
-      <c r="J19" t="n">
-        <v>18.8204631381465</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -1165,28 +1165,28 @@
         <v>51502</v>
       </c>
       <c r="C20" t="n">
-        <v>1.803614190664855</v>
+        <v>1.782873138712769</v>
       </c>
       <c r="D20" t="n">
+        <v>39.3819486954109</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.793252290735582</v>
+      </c>
+      <c r="F20" t="n">
         <v>20.15059880314304</v>
       </c>
-      <c r="E20" t="n">
-        <v>1.803614190664857</v>
-      </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
+        <v>1.782873138712769</v>
+      </c>
+      <c r="H20" t="n">
+        <v>20.15059880314304</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.79325229073558</v>
+      </c>
+      <c r="J20" t="n">
         <v>39.3819486954109</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1.803614190664855</v>
-      </c>
-      <c r="H20" t="n">
-        <v>39.3819486954109</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1.803614190664857</v>
-      </c>
-      <c r="J20" t="n">
-        <v>20.15059880314304</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
@@ -1202,28 +1202,28 @@
         <v>53328</v>
       </c>
       <c r="C21" t="n">
-        <v>1.785025082779787</v>
+        <v>1.756967560652004</v>
       </c>
       <c r="D21" t="n">
+        <v>39.3819486954109</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.756967560652003</v>
+      </c>
+      <c r="F21" t="n">
         <v>21.01808582652089</v>
       </c>
-      <c r="E21" t="n">
-        <v>1.785025082779787</v>
-      </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
+        <v>1.756967560652003</v>
+      </c>
+      <c r="H21" t="n">
+        <v>21.01808582652089</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.756967560652003</v>
+      </c>
+      <c r="J21" t="n">
         <v>39.3819486954109</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1.785025082779787</v>
-      </c>
-      <c r="H21" t="n">
-        <v>39.3819486954109</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.785025082779787</v>
-      </c>
-      <c r="J21" t="n">
-        <v>21.01808582652089</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -1239,25 +1239,25 @@
         <v>46023</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6194873295756993</v>
+        <v>0.5476129634601548</v>
       </c>
       <c r="D22" t="n">
         <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6194873295756993</v>
+        <v>0.5583871662540419</v>
       </c>
       <c r="F22" t="n">
         <v>6</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6194873295756993</v>
+        <v>0.5476129634601534</v>
       </c>
       <c r="H22" t="n">
         <v>6</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6194873295756993</v>
+        <v>0.5583871662540427</v>
       </c>
       <c r="J22" t="n">
         <v>6</v>
@@ -1276,25 +1276,25 @@
         <v>47849</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6256357628933464</v>
+        <v>0.5628491511351607</v>
       </c>
       <c r="D23" t="n">
         <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6256357628933464</v>
+        <v>0.5741847858089697</v>
       </c>
       <c r="F23" t="n">
         <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6256357628933464</v>
+        <v>0.5628491511351607</v>
       </c>
       <c r="H23" t="n">
         <v>6</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6256357628933464</v>
+        <v>0.5741847858089705</v>
       </c>
       <c r="J23" t="n">
         <v>6</v>
@@ -1313,25 +1313,25 @@
         <v>49675</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6434850026070589</v>
+        <v>0.6351462431848859</v>
       </c>
       <c r="D24" t="n">
         <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6428807147761446</v>
+        <v>0.6413460671108137</v>
       </c>
       <c r="F24" t="n">
         <v>6</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6434850026070589</v>
+        <v>0.6351462431848859</v>
       </c>
       <c r="H24" t="n">
         <v>6</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6428807147761446</v>
+        <v>0.6413460671108145</v>
       </c>
       <c r="J24" t="n">
         <v>6</v>
@@ -1350,25 +1350,25 @@
         <v>51502</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7008934244329993</v>
+        <v>0.6870241671988843</v>
       </c>
       <c r="D25" t="n">
         <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7005898223247637</v>
+        <v>0.6870241671988843</v>
       </c>
       <c r="F25" t="n">
         <v>6</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7008934244329994</v>
+        <v>0.6870241671988843</v>
       </c>
       <c r="H25" t="n">
         <v>6</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7005898223247637</v>
+        <v>0.6870241671988843</v>
       </c>
       <c r="J25" t="n">
         <v>6</v>
@@ -1387,25 +1387,25 @@
         <v>53328</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7008934244329994</v>
+        <v>0.6870241671988844</v>
       </c>
       <c r="D26" t="n">
         <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7005898223247637</v>
+        <v>0.6870241671988843</v>
       </c>
       <c r="F26" t="n">
         <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>0.7008934244329994</v>
+        <v>0.6870241671988843</v>
       </c>
       <c r="H26" t="n">
         <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7005898223247637</v>
+        <v>0.6870241671988842</v>
       </c>
       <c r="J26" t="n">
         <v>6</v>
@@ -1417,7 +1417,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
@@ -1427,34 +1427,34 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
         <v>0.0867453946648023</v>
       </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0.0867453946648023</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0867453946648023</v>
+        <v>10</v>
       </c>
       <c r="K27" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1464,34 +1464,34 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
         <v>0.1343372936492743</v>
       </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0.1343372936492743</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1343372936492743</v>
+        <v>10</v>
       </c>
       <c r="K28" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -1501,34 +1501,34 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
         <v>0.1647522628953677</v>
       </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0.1647522628953677</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.1647522628953677</v>
+        <v>10</v>
       </c>
       <c r="K29" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1538,34 +1538,34 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
         <v>0.1862401701876625</v>
       </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1</v>
-      </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0.1862401701876625</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.1862401701876625</v>
+        <v>10</v>
       </c>
       <c r="K30" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
@@ -1575,28 +1575,28 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
         <v>0.202571092960545</v>
       </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1</v>
-      </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0.202571092960545</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0.202571092960545</v>
+        <v>10</v>
       </c>
       <c r="K31" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="32">
@@ -1609,25 +1609,25 @@
         <v>46023</v>
       </c>
       <c r="C32" t="n">
-        <v>0.07333373253921144</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
         <v>27.51502893528894</v>
       </c>
       <c r="E32" t="n">
-        <v>0.07333373253921149</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
         <v>27.51502893528894</v>
       </c>
       <c r="G32" t="n">
-        <v>0.07333373253921144</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
         <v>27.51502893528894</v>
       </c>
       <c r="I32" t="n">
-        <v>0.07333373253921147</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>27.51502893528894</v>
@@ -1646,25 +1646,25 @@
         <v>47849</v>
       </c>
       <c r="C33" t="n">
-        <v>0.07426112264419851</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
         <v>27.51502893528894</v>
       </c>
       <c r="E33" t="n">
-        <v>0.07426112264419851</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
         <v>27.51502893528894</v>
       </c>
       <c r="G33" t="n">
-        <v>0.07426112264419849</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
         <v>27.51502893528894</v>
       </c>
       <c r="I33" t="n">
-        <v>0.07426112264419851</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>27.51502893528894</v>
@@ -1683,25 +1683,25 @@
         <v>49675</v>
       </c>
       <c r="C34" t="n">
-        <v>0.07501426089391512</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
         <v>27.51502893528894</v>
       </c>
       <c r="E34" t="n">
-        <v>0.07500287479526445</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
         <v>27.51502893528894</v>
       </c>
       <c r="G34" t="n">
-        <v>0.07501426089391512</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
         <v>27.51502893528894</v>
       </c>
       <c r="I34" t="n">
-        <v>0.07500287479526441</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>27.51502893528894</v>
@@ -1720,25 +1720,25 @@
         <v>51502</v>
       </c>
       <c r="C35" t="n">
-        <v>0.07775327686857787</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
         <v>27.51502893528894</v>
       </c>
       <c r="E35" t="n">
-        <v>0.07768388210098112</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
         <v>27.51502893528894</v>
       </c>
       <c r="G35" t="n">
-        <v>0.07775327686857789</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
         <v>27.51502893528894</v>
       </c>
       <c r="I35" t="n">
-        <v>0.07768388210098112</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>27.51502893528894</v>
@@ -1757,25 +1757,25 @@
         <v>53328</v>
       </c>
       <c r="C36" t="n">
-        <v>0.07860306465760961</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
         <v>27.51502893528894</v>
       </c>
       <c r="E36" t="n">
-        <v>0.07853366989001288</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
         <v>27.51502893528894</v>
       </c>
       <c r="G36" t="n">
-        <v>0.07860306465760961</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
         <v>27.51502893528894</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0785336698900129</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>27.51502893528894</v>
@@ -1787,7 +1787,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DLVL_Li-ion_s_8 MWh</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
@@ -1797,34 +1797,34 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0.47079117807104</v>
+        <v>15.67600601648351</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>5.878502256181318</v>
+        <v>1.255443141522773</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>5.878502256181318</v>
+        <v>1.255443141522773</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0.47079117807104</v>
+        <v>15.67600601648351</v>
       </c>
       <c r="K37" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DLVL_Li-ion_s_8 MWh</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1834,34 +1834,34 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0.742930397094833</v>
+        <v>15.67600601648351</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>5.878502256181318</v>
+        <v>1.981147725586221</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>5.878502256181318</v>
+        <v>1.981147725586221</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0.742930397094833</v>
+        <v>15.67600601648351</v>
       </c>
       <c r="K38" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DLVL_Li-ion_s_8 MWh</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
@@ -1871,34 +1871,34 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9247372801783194</v>
+        <v>15.67600601648351</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>5.878502256181318</v>
+        <v>2.465966080475518</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>5.878502256181318</v>
+        <v>2.465966080475518</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.9247372801783194</v>
+        <v>15.67600601648351</v>
       </c>
       <c r="K39" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DLVL_Li-ion_s_8 MWh</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -1908,34 +1908,34 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>1.058489268339244</v>
+        <v>15.67600601648351</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>5.878502256181318</v>
+        <v>2.822638048904651</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>5.878502256181318</v>
+        <v>2.822638048904651</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>1.058489268339244</v>
+        <v>15.67600601648351</v>
       </c>
       <c r="K40" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DLVL_Li-ion_s_8 MWh</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
@@ -1945,34 +1945,34 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>1.163707434539444</v>
+        <v>15.67600601648351</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>5.878502256181318</v>
+        <v>3.103219825438517</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>5.878502256181318</v>
+        <v>3.103219825438517</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>1.163707434539444</v>
+        <v>15.67600601648351</v>
       </c>
       <c r="K41" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DLVL_NMC_s_4.15 MWh</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -1982,25 +1982,25 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
+        <v>11.33205254203628</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
         <v>0.9075492589321255</v>
       </c>
-      <c r="E42" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" t="n">
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.9075492589321255</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
         <v>11.33205254203628</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>11.33205254203628</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0.9075492589321255</v>
       </c>
       <c r="K42" t="n">
         <v>4.15</v>
@@ -2009,7 +2009,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DLVL_NMC_s_4.15 MWh</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -2019,25 +2019,25 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
+        <v>11.33205254203628</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
         <v>1.432154982351485</v>
       </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" t="n">
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.432154982351485</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
         <v>11.33205254203628</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>11.33205254203628</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
-        <v>1.432154982351485</v>
       </c>
       <c r="K43" t="n">
         <v>4.15</v>
@@ -2046,7 +2046,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DLVL_NMC_s_4.15 MWh</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2056,25 +2056,25 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
+        <v>11.33205254203628</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
         <v>1.782626082271459</v>
       </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="n">
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.782626082271459</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
         <v>11.33205254203628</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>11.33205254203628</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>1.782626082271459</v>
       </c>
       <c r="K44" t="n">
         <v>4.15</v>
@@ -2083,7 +2083,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DLVL_NMC_s_4.15 MWh</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
@@ -2093,25 +2093,25 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
+        <v>11.33205254203628</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
         <v>2.040461240172037</v>
       </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" t="n">
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2.040461240172037</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
         <v>11.33205254203628</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>11.33205254203628</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.040461240172037</v>
       </c>
       <c r="K45" t="n">
         <v>4.15</v>
@@ -2120,7 +2120,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DLVL_NMC_s_4.15 MWh</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2130,25 +2130,25 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
+        <v>11.33205254203628</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
         <v>2.243291440076036</v>
       </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2.243291440076036</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
         <v>11.33205254203628</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>11.33205254203628</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>2.243291440076036</v>
       </c>
       <c r="K46" t="n">
         <v>4.15</v>
@@ -2167,25 +2167,25 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
+        <v>0.1567600601648352</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
         <v>0.01255443141522774</v>
       </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" t="n">
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.01255443141522774</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
         <v>0.1567600601648352</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.1567600601648352</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0.01255443141522774</v>
       </c>
       <c r="K47" t="n">
         <v>300</v>
@@ -2204,25 +2204,25 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
+        <v>0.1567600601648352</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
         <v>0.01981147725586221</v>
       </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="n">
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.01981147725586221</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
         <v>0.1567600601648352</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.1567600601648352</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.01981147725586221</v>
       </c>
       <c r="K48" t="n">
         <v>300</v>
@@ -2241,25 +2241,25 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
+        <v>0.1567600601648352</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
         <v>0.02465966080475518</v>
       </c>
-      <c r="E49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" t="n">
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.02465966080475518</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
         <v>0.1567600601648352</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.1567600601648352</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0.02465966080475518</v>
       </c>
       <c r="K49" t="n">
         <v>300</v>
@@ -2278,25 +2278,25 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
+        <v>0.1567600601648352</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
         <v>0.02822638048904651</v>
       </c>
-      <c r="E50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" t="n">
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.02822638048904651</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
         <v>0.1567600601648352</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.1567600601648352</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0.02822638048904651</v>
       </c>
       <c r="K50" t="n">
         <v>300</v>
@@ -2315,25 +2315,25 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
+        <v>0.1567600601648352</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
         <v>0.03103219825438517</v>
       </c>
-      <c r="E51" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" t="n">
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.03103219825438517</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
         <v>0.1567600601648352</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.1567600601648352</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0.03103219825438517</v>
       </c>
       <c r="K51" t="n">
         <v>300</v>
@@ -2342,7 +2342,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_VRF_s_500 kWh</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2352,34 +2352,34 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>100</v>
+        <v>94.05603609890109</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>100</v>
+        <v>7.532658849136641</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>100</v>
+        <v>7.532658849136641</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>100</v>
+        <v>94.05603609890109</v>
       </c>
       <c r="K52" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_VRF_s_500 kWh</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
@@ -2389,34 +2389,34 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>100</v>
+        <v>94.05603609890109</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>100</v>
+        <v>11.88688635351733</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>100</v>
+        <v>11.88688635351733</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>100</v>
+        <v>94.05603609890109</v>
       </c>
       <c r="K53" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_VRF_s_500 kWh</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2426,34 +2426,34 @@
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>100</v>
+        <v>94.05603609890109</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>100</v>
+        <v>14.79579648285311</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>100</v>
+        <v>14.79579648285311</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>100</v>
+        <v>94.05603609890109</v>
       </c>
       <c r="K54" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_VRF_s_500 kWh</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
@@ -2463,34 +2463,34 @@
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>100</v>
+        <v>94.05603609890109</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>100</v>
+        <v>16.9358282934279</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>100</v>
+        <v>16.9358282934279</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>100</v>
+        <v>94.05603609890109</v>
       </c>
       <c r="K55" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_VRF_s_500 kWh</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -2500,34 +2500,34 @@
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>100</v>
+        <v>94.05603609890109</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>100</v>
+        <v>18.6193189526311</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>100</v>
+        <v>18.6193189526311</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>100</v>
+        <v>94.05603609890109</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
@@ -2558,13 +2558,13 @@
         <v>100</v>
       </c>
       <c r="K57" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -2595,13 +2595,13 @@
         <v>100</v>
       </c>
       <c r="K58" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
@@ -2632,13 +2632,13 @@
         <v>100</v>
       </c>
       <c r="K59" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -2669,13 +2669,13 @@
         <v>100</v>
       </c>
       <c r="K60" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
@@ -2706,13 +2706,13 @@
         <v>100</v>
       </c>
       <c r="K61" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_40 kW</t>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -2722,34 +2722,34 @@
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>77.9217936042</v>
+        <v>100</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>77.9217936042</v>
+        <v>100</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>77.9217936042</v>
+        <v>100</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>77.9217936042</v>
+        <v>100</v>
       </c>
       <c r="K62" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_40 kW</t>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
@@ -2759,145 +2759,145 @@
         <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>77.9217936042</v>
+        <v>100</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>77.9217936042</v>
+        <v>100</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>77.9217936042</v>
+        <v>100</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>77.9217936042</v>
+        <v>100</v>
       </c>
       <c r="K63" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_40 kW</t>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C64" t="n">
-        <v>13.29658105361883</v>
+        <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>77.9217936042</v>
+        <v>100</v>
       </c>
       <c r="E64" t="n">
-        <v>13.29658105361883</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>77.9217936042</v>
+        <v>100</v>
       </c>
       <c r="G64" t="n">
-        <v>13.29658105361883</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>77.9217936042</v>
+        <v>100</v>
       </c>
       <c r="I64" t="n">
-        <v>13.29658105361883</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>77.9217936042</v>
+        <v>100</v>
       </c>
       <c r="K64" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_40 kW</t>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C65" t="n">
-        <v>17.47261798574383</v>
+        <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>77.9217936042</v>
+        <v>100</v>
       </c>
       <c r="E65" t="n">
-        <v>17.45178163844321</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>77.9217936042</v>
+        <v>100</v>
       </c>
       <c r="G65" t="n">
-        <v>17.47261798574383</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>77.9217936042</v>
+        <v>100</v>
       </c>
       <c r="I65" t="n">
-        <v>17.45178163844321</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>77.9217936042</v>
+        <v>100</v>
       </c>
       <c r="K65" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_40 kW</t>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C66" t="n">
-        <v>17.47261798574383</v>
+        <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>77.9217936042</v>
+        <v>100</v>
       </c>
       <c r="E66" t="n">
-        <v>17.45178163844321</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>77.9217936042</v>
+        <v>100</v>
       </c>
       <c r="G66" t="n">
-        <v>17.47261798574383</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>77.9217936042</v>
+        <v>100</v>
       </c>
       <c r="I66" t="n">
-        <v>17.45178163844321</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>77.9217936042</v>
+        <v>100</v>
       </c>
       <c r="K66" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_8 kW</t>
+          <t>HW_ElectricBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
@@ -2907,34 +2907,34 @@
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K67" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_8 kW</t>
+          <t>HW_ElectricBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -2944,145 +2944,145 @@
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K68" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_8 kW</t>
+          <t>HW_ElectricBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C69" t="n">
-        <v>8.05126057</v>
+        <v>18.71551193330387</v>
       </c>
       <c r="D69" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E69" t="n">
-        <v>8.212549189999995</v>
+        <v>18.51861718642766</v>
       </c>
       <c r="F69" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G69" t="n">
-        <v>8.05126057</v>
+        <v>18.71551193330387</v>
       </c>
       <c r="H69" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I69" t="n">
-        <v>8.212549189999995</v>
+        <v>18.51861718642769</v>
       </c>
       <c r="J69" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K69" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_8 kW</t>
+          <t>HW_ElectricBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C70" t="n">
-        <v>9.05126057</v>
+        <v>19.51901623052802</v>
       </c>
       <c r="D70" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E70" t="n">
-        <v>9.212549189999995</v>
+        <v>19.2956811135907</v>
       </c>
       <c r="F70" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G70" t="n">
-        <v>9.05126057</v>
+        <v>19.51901623052802</v>
       </c>
       <c r="H70" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I70" t="n">
-        <v>9.212549189999995</v>
+        <v>19.29568111359072</v>
       </c>
       <c r="J70" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K70" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_8 kW</t>
+          <t>HW_ElectricBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C71" t="n">
-        <v>9.05126057</v>
+        <v>19.51901623052802</v>
       </c>
       <c r="D71" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E71" t="n">
-        <v>9.212549189999995</v>
+        <v>19.2956811135907</v>
       </c>
       <c r="F71" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G71" t="n">
-        <v>9.05126057</v>
+        <v>19.51901623052802</v>
       </c>
       <c r="H71" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I71" t="n">
-        <v>9.212549189999995</v>
+        <v>19.29568111359072</v>
       </c>
       <c r="J71" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K71" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_40 kW</t>
+          <t>HW_ElectricBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3092,34 +3092,34 @@
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="K72" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_40 kW</t>
+          <t>HW_ElectricBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
@@ -3129,145 +3129,145 @@
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="K73" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_40 kW</t>
+          <t>HW_ElectricBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>19.42421714877702</v>
       </c>
       <c r="D74" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>19.42421714877702</v>
       </c>
       <c r="F74" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>19.42421714877702</v>
       </c>
       <c r="H74" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>19.42421714877702</v>
       </c>
       <c r="J74" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="K74" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_40 kW</t>
+          <t>HW_ElectricBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>19.80443112870009</v>
       </c>
       <c r="D75" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>19.8044311287001</v>
       </c>
       <c r="F75" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>19.80443112870007</v>
       </c>
       <c r="H75" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>19.80443112870009</v>
       </c>
       <c r="J75" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="K75" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_40 kW</t>
+          <t>HW_ElectricBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>19.80443112870009</v>
       </c>
       <c r="D76" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>19.8044311287001</v>
       </c>
       <c r="F76" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>19.80443112870007</v>
       </c>
       <c r="H76" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>19.80443112870009</v>
       </c>
       <c r="J76" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="K76" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_8 kW</t>
+          <t>HW_GasBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
@@ -3277,34 +3277,34 @@
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K77" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_8 kW</t>
+          <t>HW_GasBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3314,34 +3314,34 @@
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K78" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_8 kW</t>
+          <t>HW_GasBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
@@ -3351,34 +3351,34 @@
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K79" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_8 kW</t>
+          <t>HW_GasBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -3388,34 +3388,34 @@
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K80" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_8 kW</t>
+          <t>HW_GasBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
@@ -3425,34 +3425,34 @@
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K81" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_40 kW</t>
+          <t>HW_GasBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -3462,34 +3462,34 @@
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="K82" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_40 kW</t>
+          <t>HW_GasBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
@@ -3499,34 +3499,34 @@
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="K83" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_40 kW</t>
+          <t>HW_GasBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -3536,108 +3536,108 @@
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="K84" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_40 kW</t>
+          <t>HW_GasBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C85" t="n">
-        <v>0.2904207328749978</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="E85" t="n">
-        <v>0.3112570801756448</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="G85" t="n">
-        <v>0.2904207328749928</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="I85" t="n">
-        <v>0.3112570801756448</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="K85" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_40 kW</t>
+          <t>HW_GasBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C86" t="n">
-        <v>0.2904207328749978</v>
+        <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="E86" t="n">
-        <v>0.3112570801756448</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="G86" t="n">
-        <v>0.2904207328749928</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="I86" t="n">
-        <v>0.3112570801756448</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="K86" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_8 kW</t>
+          <t>HW_HPAS_s_40 kW</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
@@ -3647,34 +3647,34 @@
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K87" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_8 kW</t>
+          <t>HW_HPAS_s_40 kW</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -3684,145 +3684,145 @@
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K88" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_8 kW</t>
+          <t>HW_HPAS_s_40 kW</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>9.195480666696133</v>
       </c>
       <c r="D89" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>9.530435033195769</v>
       </c>
       <c r="F89" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>9.195480666696128</v>
       </c>
       <c r="H89" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>9.530435033195744</v>
       </c>
       <c r="J89" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K89" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_8 kW</t>
+          <t>HW_HPAS_s_40 kW</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>12.53984206263778</v>
       </c>
       <c r="D90" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>12.90123679919853</v>
       </c>
       <c r="F90" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>12.53984206263777</v>
       </c>
       <c r="H90" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>12.9012367991985</v>
       </c>
       <c r="J90" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K90" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_8 kW</t>
+          <t>HW_HPAS_s_40 kW</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>12.53984206263778</v>
       </c>
       <c r="D91" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>12.90123679919853</v>
       </c>
       <c r="F91" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>12.53984206263777</v>
       </c>
       <c r="H91" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>12.9012367991985</v>
       </c>
       <c r="J91" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K91" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_40 kW</t>
+          <t>HW_HPAS_s_8 kW</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -3832,34 +3832,34 @@
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="K92" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_40 kW</t>
+          <t>HW_HPAS_s_8 kW</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
@@ -3869,145 +3869,145 @@
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="K93" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_40 kW</t>
+          <t>HW_HPAS_s_8 kW</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>2.730611164648288</v>
       </c>
       <c r="D94" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>2.730611164648288</v>
       </c>
       <c r="F94" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>2.730611164648289</v>
       </c>
       <c r="H94" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>2.730611164648288</v>
       </c>
       <c r="J94" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="K94" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_40 kW</t>
+          <t>HW_HPAS_s_8 kW</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>5.977929917848765</v>
       </c>
       <c r="D95" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>5.97792991784874</v>
       </c>
       <c r="F95" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>5.977929917848741</v>
       </c>
       <c r="H95" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>5.977929917848735</v>
       </c>
       <c r="J95" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="K95" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_40 kW</t>
+          <t>HW_HPAS_s_8 kW</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>6.334072496374012</v>
       </c>
       <c r="D96" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>6.328245591107197</v>
       </c>
       <c r="F96" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>6.334072496373993</v>
       </c>
       <c r="H96" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>6.328245591107189</v>
       </c>
       <c r="J96" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="K96" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_8 kW</t>
+          <t>HW_HPGS_s_40 kW</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
@@ -4017,34 +4017,34 @@
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K97" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_8 kW</t>
+          <t>HW_HPGS_s_40 kW</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4054,34 +4054,34 @@
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K98" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_8 kW</t>
+          <t>HW_HPGS_s_40 kW</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
@@ -4091,34 +4091,34 @@
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K99" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_8 kW</t>
+          <t>HW_HPGS_s_40 kW</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -4128,34 +4128,34 @@
         <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K100" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_8 kW</t>
+          <t>HW_HPGS_s_40 kW</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
@@ -4165,34 +4165,34 @@
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K101" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_40 kW</t>
+          <t>HW_HPGS_s_8 kW</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
@@ -4202,34 +4202,34 @@
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="K102" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_40 kW</t>
+          <t>HW_HPGS_s_8 kW</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
@@ -4239,34 +4239,34 @@
         <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="I103" t="n">
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="K103" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_40 kW</t>
+          <t>HW_HPGS_s_8 kW</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
@@ -4276,34 +4276,34 @@
         <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="I104" t="n">
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="K104" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_40 kW</t>
+          <t>HW_HPGS_s_8 kW</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
@@ -4313,34 +4313,34 @@
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="E105" t="n">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="K105" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_40 kW</t>
+          <t>HW_HPGS_s_8 kW</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
@@ -4350,34 +4350,34 @@
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>77.9217936042</v>
+        <v>111.621575016</v>
       </c>
       <c r="K106" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_8 kW</t>
+          <t>HW_OilBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
@@ -4387,34 +4387,34 @@
         <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E107" t="n">
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K107" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_8 kW</t>
+          <t>HW_OilBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
@@ -4424,34 +4424,34 @@
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E108" t="n">
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I108" t="n">
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K108" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_8 kW</t>
+          <t>HW_OilBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
@@ -4461,34 +4461,34 @@
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E109" t="n">
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I109" t="n">
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K109" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_8 kW</t>
+          <t>HW_OilBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
@@ -4498,34 +4498,34 @@
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E110" t="n">
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I110" t="n">
         <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K110" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_8 kW</t>
+          <t>HW_OilBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
@@ -4535,34 +4535,34 @@
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="E111" t="n">
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>111.621575016</v>
+        <v>77.9217936042</v>
       </c>
       <c r="K111" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>HW_OilBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
@@ -4572,34 +4572,34 @@
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>111.621575016</v>
       </c>
       <c r="E112" t="n">
-        <v>0.1191671854059678</v>
+        <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>0.1191671854059678</v>
+        <v>111.621575016</v>
       </c>
       <c r="G112" t="n">
-        <v>0.1191671854059678</v>
+        <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>0.1191671854059678</v>
+        <v>111.621575016</v>
       </c>
       <c r="I112" t="n">
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
+        <v>111.621575016</v>
       </c>
       <c r="K112" t="n">
-        <v>1</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>HW_OilBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
@@ -4609,34 +4609,34 @@
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>111.621575016</v>
       </c>
       <c r="E113" t="n">
-        <v>0.1191671854059678</v>
+        <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>0.1191671854059678</v>
+        <v>111.621575016</v>
       </c>
       <c r="G113" t="n">
-        <v>0.1191671854059678</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>0.1191671854059678</v>
+        <v>111.621575016</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>111.621575016</v>
       </c>
       <c r="K113" t="n">
-        <v>1</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>HW_OilBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
@@ -4646,34 +4646,34 @@
         <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>111.621575016</v>
       </c>
       <c r="E114" t="n">
-        <v>0.1191671854059678</v>
+        <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>0.1191671854059678</v>
+        <v>111.621575016</v>
       </c>
       <c r="G114" t="n">
-        <v>0.1191671854059678</v>
+        <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>0.1191671854059678</v>
+        <v>111.621575016</v>
       </c>
       <c r="I114" t="n">
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>0</v>
+        <v>111.621575016</v>
       </c>
       <c r="K114" t="n">
-        <v>1</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>HW_OilBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
@@ -4683,34 +4683,34 @@
         <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>111.621575016</v>
       </c>
       <c r="E115" t="n">
-        <v>0.1191671854059678</v>
+        <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>0.1191671854059678</v>
+        <v>111.621575016</v>
       </c>
       <c r="G115" t="n">
-        <v>0.1191671854059678</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>0.1191671854059678</v>
+        <v>111.621575016</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
+        <v>111.621575016</v>
       </c>
       <c r="K115" t="n">
-        <v>1</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>HW_OilBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
@@ -4720,219 +4720,219 @@
         <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>111.621575016</v>
       </c>
       <c r="E116" t="n">
-        <v>0.1191671854059678</v>
+        <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>0.1191671854059678</v>
+        <v>111.621575016</v>
       </c>
       <c r="G116" t="n">
-        <v>0.1191671854059678</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>0.1191671854059678</v>
+        <v>111.621575016</v>
       </c>
       <c r="I116" t="n">
         <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>111.621575016</v>
       </c>
       <c r="K116" t="n">
-        <v>1</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_10 kW</t>
+          <t>RE_GPV_s_1 MW</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="D117" t="n">
-        <v>245.0708881712023</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="E117" t="n">
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>408.2479934734613</v>
+        <v>0</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>408.2479934734613</v>
+        <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="J117" t="n">
-        <v>245.0708881712023</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="K117" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_10 kW</t>
+          <t>RE_GPV_s_1 MW</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="D118" t="n">
-        <v>293.6728799384529</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>408.2479934734613</v>
+        <v>0</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>408.2479934734613</v>
+        <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>0</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="J118" t="n">
-        <v>293.6728799384529</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="K118" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_10 kW</t>
+          <t>RE_GPV_s_1 MW</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="D119" t="n">
-        <v>313.6885407026189</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="E119" t="n">
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>408.2479934734613</v>
+        <v>0</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>408.2479934734613</v>
+        <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>0</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="J119" t="n">
-        <v>313.6885407026189</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="K119" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_10 kW</t>
+          <t>RE_GPV_s_1 MW</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C120" t="n">
-        <v>0</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="D120" t="n">
-        <v>324.5386626470429</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="E120" t="n">
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>408.2479934734613</v>
+        <v>0</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>408.2479934734613</v>
+        <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="J120" t="n">
-        <v>324.5386626470429</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="K120" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_10 kW</t>
+          <t>RE_GPV_s_1 MW</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C121" t="n">
-        <v>0</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="D121" t="n">
-        <v>331.4339421130536</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="E121" t="n">
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>408.2479934734613</v>
+        <v>0</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>408.2479934734613</v>
+        <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="J121" t="n">
-        <v>331.4339421130536</v>
+        <v>0.1191671854059678</v>
       </c>
       <c r="K121" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_30 kW</t>
+          <t>RE_RTPV_s_10 kW</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
@@ -4942,34 +4942,34 @@
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>109.1637891589338</v>
+        <v>408.2479934734613</v>
       </c>
       <c r="E122" t="n">
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>172.0646688421795</v>
+        <v>245.0708881712023</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>172.0646688421795</v>
+        <v>245.0708881712023</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>109.1637891589338</v>
+        <v>408.2479934734613</v>
       </c>
       <c r="K122" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_30 kW</t>
+          <t>RE_RTPV_s_10 kW</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
@@ -4979,34 +4979,34 @@
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>127.8986970423353</v>
+        <v>408.2479934734613</v>
       </c>
       <c r="E123" t="n">
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>172.0646688421795</v>
+        <v>293.6728799384529</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>172.0646688421795</v>
+        <v>293.6728799384529</v>
       </c>
       <c r="I123" t="n">
         <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>127.8986970423353</v>
+        <v>408.2479934734613</v>
       </c>
       <c r="K123" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_30 kW</t>
+          <t>RE_RTPV_s_10 kW</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
@@ -5016,34 +5016,34 @@
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>135.6142565699748</v>
+        <v>408.2479934734613</v>
       </c>
       <c r="E124" t="n">
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>172.0646688421795</v>
+        <v>313.6885407026189</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>172.0646688421795</v>
+        <v>313.6885407026189</v>
       </c>
       <c r="I124" t="n">
         <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>135.6142565699748</v>
+        <v>408.2479934734613</v>
       </c>
       <c r="K124" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_30 kW</t>
+          <t>RE_RTPV_s_10 kW</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
@@ -5053,71 +5053,71 @@
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>139.7967196288124</v>
+        <v>408.2479934734613</v>
       </c>
       <c r="E125" t="n">
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>172.0646688421795</v>
+        <v>324.5386626470429</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>172.0646688421795</v>
+        <v>324.5386626470429</v>
       </c>
       <c r="I125" t="n">
         <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>139.7967196288124</v>
+        <v>408.2479934734613</v>
       </c>
       <c r="K125" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_30 kW</t>
+          <t>RE_RTPV_s_10 kW</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C126" t="n">
-        <v>143.3937505848484</v>
+        <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>142.4546852991219</v>
+        <v>408.2479934734613</v>
       </c>
       <c r="E126" t="n">
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>172.0646688421795</v>
+        <v>331.4339421130536</v>
       </c>
       <c r="G126" t="n">
-        <v>172.0646688421795</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>172.0646688421795</v>
+        <v>331.4339421130536</v>
       </c>
       <c r="I126" t="n">
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>142.4546852991219</v>
+        <v>408.2479934734613</v>
       </c>
       <c r="K126" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>RE_RTPV_s_30 kW</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
@@ -5127,34 +5127,34 @@
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>755.5999710264347</v>
+        <v>172.0646688421795</v>
       </c>
       <c r="E127" t="n">
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>755.5999710264347</v>
+        <v>109.1637891589338</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>755.5999710264347</v>
+        <v>109.1637891589338</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>755.5999710264347</v>
+        <v>172.0646688421795</v>
       </c>
       <c r="K127" t="n">
-        <v>0.017</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>RE_RTPV_s_30 kW</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
@@ -5164,34 +5164,34 @@
         <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>755.5999710264347</v>
+        <v>172.0646688421795</v>
       </c>
       <c r="E128" t="n">
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>755.5999710264347</v>
+        <v>127.8986970423353</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>755.5999710264347</v>
+        <v>127.8986970423353</v>
       </c>
       <c r="I128" t="n">
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>755.5999710264347</v>
+        <v>172.0646688421795</v>
       </c>
       <c r="K128" t="n">
-        <v>0.017</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>RE_RTPV_s_30 kW</t>
         </is>
       </c>
       <c r="B129" s="2" t="n">
@@ -5201,34 +5201,34 @@
         <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>755.5999710264347</v>
+        <v>172.0646688421795</v>
       </c>
       <c r="E129" t="n">
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>755.5999710264347</v>
+        <v>135.6142565699748</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>755.5999710264347</v>
+        <v>135.6142565699748</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>755.5999710264347</v>
+        <v>172.0646688421795</v>
       </c>
       <c r="K129" t="n">
-        <v>0.017</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>RE_RTPV_s_30 kW</t>
         </is>
       </c>
       <c r="B130" s="2" t="n">
@@ -5238,34 +5238,34 @@
         <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>755.5999710264347</v>
+        <v>172.0646688421795</v>
       </c>
       <c r="E130" t="n">
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>755.5999710264347</v>
+        <v>139.7967196288124</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>755.5999710264347</v>
+        <v>139.7967196288124</v>
       </c>
       <c r="I130" t="n">
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>755.5999710264347</v>
+        <v>172.0646688421795</v>
       </c>
       <c r="K130" t="n">
-        <v>0.017</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>RE_RTPV_s_30 kW</t>
         </is>
       </c>
       <c r="B131" s="2" t="n">
@@ -5275,34 +5275,34 @@
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>755.5999710264347</v>
+        <v>172.0646688421795</v>
       </c>
       <c r="E131" t="n">
-        <v>0</v>
+        <v>143.3937505848484</v>
       </c>
       <c r="F131" t="n">
-        <v>755.5999710264347</v>
+        <v>142.4546852991219</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>755.5999710264347</v>
+        <v>142.4546852991219</v>
       </c>
       <c r="I131" t="n">
-        <v>0</v>
+        <v>172.0646688421795</v>
       </c>
       <c r="J131" t="n">
-        <v>755.5999710264347</v>
+        <v>172.0646688421795</v>
       </c>
       <c r="K131" t="n">
-        <v>0.017</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B132" s="2" t="n">
@@ -5312,34 +5312,34 @@
         <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E132" t="n">
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I132" t="n">
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K132" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B133" s="2" t="n">
@@ -5349,34 +5349,34 @@
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E133" t="n">
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I133" t="n">
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K133" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B134" s="2" t="n">
@@ -5386,34 +5386,34 @@
         <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E134" t="n">
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I134" t="n">
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K134" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B135" s="2" t="n">
@@ -5423,34 +5423,34 @@
         <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E135" t="n">
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I135" t="n">
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K135" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B136" s="2" t="n">
@@ -5460,589 +5460,589 @@
         <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E136" t="n">
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I136" t="n">
         <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K136" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B137" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C137" t="n">
-        <v>5.960600090932976</v>
+        <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>253.5104218084386</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E137" t="n">
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I137" t="n">
-        <v>12.65336872859879</v>
+        <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>253.5104218084386</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K137" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B138" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C138" t="n">
-        <v>88.26550936886187</v>
+        <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>325.9321163739264</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E138" t="n">
-        <v>79.83264197043273</v>
+        <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G138" t="n">
-        <v>78.71727381904972</v>
+        <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I138" t="n">
-        <v>98.58609171733501</v>
+        <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>325.9321163739264</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K138" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B139" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C139" t="n">
-        <v>191.6302427530083</v>
+        <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>358.2067876833306</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E139" t="n">
-        <v>195.2558906349682</v>
+        <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G139" t="n">
-        <v>182.0820072031962</v>
+        <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I139" t="n">
-        <v>210.7284675877406</v>
+        <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>358.2067876833306</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K139" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B140" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C140" t="n">
-        <v>221.6291925914218</v>
+        <v>0</v>
       </c>
       <c r="D140" t="n">
-        <v>375.6247269598206</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E140" t="n">
-        <v>239.4653241681159</v>
+        <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G140" t="n">
-        <v>226.4404884914111</v>
+        <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I140" t="n">
-        <v>239.4653241681159</v>
+        <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>375.6247269598206</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K140" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B141" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C141" t="n">
-        <v>217.5719096054682</v>
+        <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>386.3769324110056</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E141" t="n">
-        <v>229.35037238597</v>
+        <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G141" t="n">
-        <v>217.5719096054682</v>
+        <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I141" t="n">
-        <v>229.35037238597</v>
+        <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>386.3769324110056</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K141" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B142" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C142" t="n">
-        <v>13.4311923973082</v>
+        <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>108.0450732373359</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E142" t="n">
-        <v>15.0839205582699</v>
+        <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>292.3269650394689</v>
+        <v>253.5104218084386</v>
       </c>
       <c r="G142" t="n">
-        <v>10.06307866641668</v>
+        <v>0</v>
       </c>
       <c r="H142" t="n">
-        <v>292.3269650394689</v>
+        <v>253.5104218084386</v>
       </c>
       <c r="I142" t="n">
-        <v>17.17662148034987</v>
+        <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>108.0450732373359</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K142" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B143" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C143" t="n">
-        <v>35.18998804486672</v>
+        <v>73.90290829888177</v>
       </c>
       <c r="D143" t="n">
-        <v>134.6260026807604</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E143" t="n">
-        <v>36.47578356606153</v>
+        <v>76.0944436154585</v>
       </c>
       <c r="F143" t="n">
-        <v>292.3269650394689</v>
+        <v>325.9321163739264</v>
       </c>
       <c r="G143" t="n">
-        <v>32.04704500241666</v>
+        <v>73.9029082988818</v>
       </c>
       <c r="H143" t="n">
-        <v>292.3269650394689</v>
+        <v>325.9321163739264</v>
       </c>
       <c r="I143" t="n">
-        <v>38.51773563563869</v>
+        <v>76.0944436154585</v>
       </c>
       <c r="J143" t="n">
-        <v>134.6260026807604</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K143" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B144" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C144" t="n">
-        <v>76.23526232575273</v>
+        <v>206.649404514661</v>
       </c>
       <c r="D144" t="n">
-        <v>146.4717730128704</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E144" t="n">
-        <v>76.5058830904856</v>
+        <v>197.8756303150148</v>
       </c>
       <c r="F144" t="n">
-        <v>292.3269650394689</v>
+        <v>358.2067876833306</v>
       </c>
       <c r="G144" t="n">
-        <v>73.58627931722778</v>
+        <v>206.649404514661</v>
       </c>
       <c r="H144" t="n">
-        <v>292.3269650394689</v>
+        <v>358.2067876833306</v>
       </c>
       <c r="I144" t="n">
-        <v>78.59791010693893</v>
+        <v>197.8756303150149</v>
       </c>
       <c r="J144" t="n">
-        <v>146.4717730128704</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K144" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B145" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C145" t="n">
-        <v>89.62070182681427</v>
+        <v>233.8877881243662</v>
       </c>
       <c r="D145" t="n">
-        <v>152.86467803582</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E145" t="n">
-        <v>91.5873071905466</v>
+        <v>220.2097385023814</v>
       </c>
       <c r="F145" t="n">
-        <v>292.3269650394689</v>
+        <v>375.6247269598206</v>
       </c>
       <c r="G145" t="n">
-        <v>89.62070182681427</v>
+        <v>233.8877881243663</v>
       </c>
       <c r="H145" t="n">
-        <v>292.3269650394689</v>
+        <v>375.6247269598206</v>
       </c>
       <c r="I145" t="n">
-        <v>91.5873071905466</v>
+        <v>220.2097385023813</v>
       </c>
       <c r="J145" t="n">
-        <v>152.86467803582</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K145" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B146" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C146" t="n">
-        <v>84.44828512094161</v>
+        <v>231.9595446683977</v>
       </c>
       <c r="D146" t="n">
-        <v>156.8110592434665</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E146" t="n">
-        <v>87.12987160549112</v>
+        <v>217.419453096063</v>
       </c>
       <c r="F146" t="n">
-        <v>292.3269650394689</v>
+        <v>386.3769324110056</v>
       </c>
       <c r="G146" t="n">
-        <v>84.44828512094161</v>
+        <v>231.9595446683977</v>
       </c>
       <c r="H146" t="n">
-        <v>292.3269650394689</v>
+        <v>386.3769324110056</v>
       </c>
       <c r="I146" t="n">
-        <v>87.12987160549112</v>
+        <v>217.419453096063</v>
       </c>
       <c r="J146" t="n">
-        <v>156.8110592434665</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K146" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B147" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C147" t="n">
-        <v>0</v>
+        <v>14.77957846102029</v>
       </c>
       <c r="D147" t="n">
-        <v>253.5104218084386</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>9.130084724659298</v>
       </c>
       <c r="F147" t="n">
-        <v>755.5999710264347</v>
+        <v>108.0450732373359</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>14.7795784610203</v>
       </c>
       <c r="H147" t="n">
-        <v>755.5999710264347</v>
+        <v>108.0450732373359</v>
       </c>
       <c r="I147" t="n">
-        <v>0</v>
+        <v>9.130084724659321</v>
       </c>
       <c r="J147" t="n">
-        <v>253.5104218084386</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K147" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B148" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C148" t="n">
-        <v>0</v>
+        <v>37.43588896276142</v>
       </c>
       <c r="D148" t="n">
-        <v>325.9321163739264</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
+        <v>32.29989391033336</v>
       </c>
       <c r="F148" t="n">
-        <v>755.5999710264347</v>
+        <v>134.6260026807604</v>
       </c>
       <c r="G148" t="n">
-        <v>0</v>
+        <v>37.43588896276142</v>
       </c>
       <c r="H148" t="n">
-        <v>755.5999710264347</v>
+        <v>134.6260026807604</v>
       </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>32.29989391033336</v>
       </c>
       <c r="J148" t="n">
-        <v>325.9321163739264</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K148" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B149" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C149" t="n">
-        <v>0</v>
+        <v>76.00214041970763</v>
       </c>
       <c r="D149" t="n">
-        <v>358.2067876833306</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E149" t="n">
-        <v>0</v>
+        <v>71.96935325537588</v>
       </c>
       <c r="F149" t="n">
-        <v>755.5999710264347</v>
+        <v>146.4717730128704</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>76.00214041970764</v>
       </c>
       <c r="H149" t="n">
-        <v>755.5999710264347</v>
+        <v>146.4717730128704</v>
       </c>
       <c r="I149" t="n">
-        <v>0</v>
+        <v>71.96935325537589</v>
       </c>
       <c r="J149" t="n">
-        <v>358.2067876833306</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K149" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B150" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C150" t="n">
-        <v>0</v>
+        <v>91.84325396059577</v>
       </c>
       <c r="D150" t="n">
-        <v>375.6247269598206</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E150" t="n">
-        <v>0</v>
+        <v>88.04119026888159</v>
       </c>
       <c r="F150" t="n">
-        <v>755.5999710264347</v>
+        <v>152.86467803582</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>91.8432539605958</v>
       </c>
       <c r="H150" t="n">
-        <v>755.5999710264347</v>
+        <v>152.86467803582</v>
       </c>
       <c r="I150" t="n">
-        <v>0</v>
+        <v>88.04119026888161</v>
       </c>
       <c r="J150" t="n">
-        <v>375.6247269598206</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K150" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B151" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C151" t="n">
-        <v>0</v>
+        <v>86.47223640109658</v>
       </c>
       <c r="D151" t="n">
-        <v>386.3769324110056</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E151" t="n">
-        <v>0</v>
+        <v>82.78957993350964</v>
       </c>
       <c r="F151" t="n">
-        <v>755.5999710264347</v>
+        <v>156.8110592434665</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>86.47223640109655</v>
       </c>
       <c r="H151" t="n">
-        <v>755.5999710264347</v>
+        <v>156.8110592434665</v>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>82.7895799335096</v>
       </c>
       <c r="J151" t="n">
-        <v>386.3769324110056</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K151" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B152" s="2" t="n">
@@ -6052,34 +6052,34 @@
         <v>0</v>
       </c>
       <c r="D152" t="n">
-        <v>108.0450732373359</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E152" t="n">
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>292.3269650394689</v>
+        <v>253.5104218084386</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>292.3269650394689</v>
+        <v>253.5104218084386</v>
       </c>
       <c r="I152" t="n">
         <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>108.0450732373359</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K152" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B153" s="2" t="n">
@@ -6089,34 +6089,34 @@
         <v>0</v>
       </c>
       <c r="D153" t="n">
-        <v>134.6260026807604</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E153" t="n">
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>292.3269650394689</v>
+        <v>325.9321163739264</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>292.3269650394689</v>
+        <v>325.9321163739264</v>
       </c>
       <c r="I153" t="n">
         <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>134.6260026807604</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K153" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B154" s="2" t="n">
@@ -6126,34 +6126,34 @@
         <v>0</v>
       </c>
       <c r="D154" t="n">
-        <v>146.4717730128704</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E154" t="n">
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>292.3269650394689</v>
+        <v>358.2067876833306</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
       </c>
       <c r="H154" t="n">
-        <v>292.3269650394689</v>
+        <v>358.2067876833306</v>
       </c>
       <c r="I154" t="n">
         <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>146.4717730128704</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K154" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B155" s="2" t="n">
@@ -6163,34 +6163,34 @@
         <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>152.86467803582</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E155" t="n">
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>292.3269650394689</v>
+        <v>375.6247269598206</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>292.3269650394689</v>
+        <v>375.6247269598206</v>
       </c>
       <c r="I155" t="n">
         <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>152.86467803582</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K155" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B156" s="2" t="n">
@@ -6200,34 +6200,34 @@
         <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>156.8110592434665</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>292.3269650394689</v>
+        <v>386.3769324110056</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>292.3269650394689</v>
+        <v>386.3769324110056</v>
       </c>
       <c r="I156" t="n">
         <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>156.8110592434665</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K156" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B157" s="2" t="n">
@@ -6237,182 +6237,182 @@
         <v>0</v>
       </c>
       <c r="D157" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E157" t="n">
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>755.5999710264347</v>
+        <v>108.0450732373359</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>755.5999710264347</v>
+        <v>108.0450732373359</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K157" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B158" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C158" t="n">
-        <v>0.9479368870480998</v>
+        <v>0</v>
       </c>
       <c r="D158" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E158" t="n">
-        <v>0.3816178865997413</v>
+        <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>755.5999710264347</v>
+        <v>134.6260026807604</v>
       </c>
       <c r="G158" t="n">
-        <v>0.9479368870480998</v>
+        <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>755.5999710264347</v>
+        <v>134.6260026807604</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3816178865997413</v>
+        <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K158" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B159" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C159" t="n">
-        <v>143.9526841727568</v>
+        <v>0</v>
       </c>
       <c r="D159" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E159" t="n">
-        <v>115.3946325531683</v>
+        <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>755.5999710264347</v>
+        <v>146.4717730128704</v>
       </c>
       <c r="G159" t="n">
-        <v>143.9562315660591</v>
+        <v>0</v>
       </c>
       <c r="H159" t="n">
-        <v>755.5999710264347</v>
+        <v>146.4717730128704</v>
       </c>
       <c r="I159" t="n">
-        <v>117.506464132988</v>
+        <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K159" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B160" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C160" t="n">
-        <v>175.5020756782621</v>
+        <v>0</v>
       </c>
       <c r="D160" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E160" t="n">
-        <v>155.3213163420436</v>
+        <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>755.5999710264347</v>
+        <v>152.86467803582</v>
       </c>
       <c r="G160" t="n">
-        <v>175.179858208031</v>
+        <v>0</v>
       </c>
       <c r="H160" t="n">
-        <v>755.5999710264347</v>
+        <v>152.86467803582</v>
       </c>
       <c r="I160" t="n">
-        <v>155.3213163420436</v>
+        <v>0</v>
       </c>
       <c r="J160" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K160" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B161" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C161" t="n">
-        <v>223.8356393722509</v>
+        <v>0</v>
       </c>
       <c r="D161" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E161" t="n">
-        <v>204.4093979862431</v>
+        <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>755.5999710264347</v>
+        <v>156.8110592434665</v>
       </c>
       <c r="G161" t="n">
-        <v>222.8589756015262</v>
+        <v>0</v>
       </c>
       <c r="H161" t="n">
-        <v>755.5999710264347</v>
+        <v>156.8110592434665</v>
       </c>
       <c r="I161" t="n">
-        <v>204.4093979862431</v>
+        <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K161" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B162" s="2" t="n">
@@ -6422,34 +6422,34 @@
         <v>0</v>
       </c>
       <c r="D162" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E162" t="n">
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I162" t="n">
         <v>0</v>
       </c>
       <c r="J162" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K162" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B163" s="2" t="n">
@@ -6459,145 +6459,145 @@
         <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E163" t="n">
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I163" t="n">
         <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K163" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B164" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C164" t="n">
-        <v>39.26266514781521</v>
+        <v>28.23270125476637</v>
       </c>
       <c r="D164" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E164" t="n">
-        <v>36.86501081974302</v>
+        <v>46.27260348395755</v>
       </c>
       <c r="F164" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G164" t="n">
-        <v>38.54353442544863</v>
+        <v>28.23270125476641</v>
       </c>
       <c r="H164" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I164" t="n">
-        <v>36.85659398226964</v>
+        <v>46.27260348395758</v>
       </c>
       <c r="J164" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K164" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B165" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C165" t="n">
-        <v>59.64028466233725</v>
+        <v>68.97562743011315</v>
       </c>
       <c r="D165" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E165" t="n">
-        <v>57.71234434075127</v>
+        <v>79.91989578819884</v>
       </c>
       <c r="F165" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G165" t="n">
-        <v>59.64028466233724</v>
+        <v>68.97562743011311</v>
       </c>
       <c r="H165" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I165" t="n">
-        <v>57.71234434075127</v>
+        <v>79.91989578819887</v>
       </c>
       <c r="J165" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K165" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B166" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C166" t="n">
-        <v>68.84331447848078</v>
+        <v>71.03063877783477</v>
       </c>
       <c r="D166" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E166" t="n">
-        <v>66.20039303607763</v>
+        <v>85.57073035016957</v>
       </c>
       <c r="F166" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G166" t="n">
-        <v>68.84331447848078</v>
+        <v>71.03063877783475</v>
       </c>
       <c r="H166" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I166" t="n">
-        <v>66.20039303607763</v>
+        <v>85.57073035016953</v>
       </c>
       <c r="J166" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K166" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B167" s="2" t="n">
@@ -6607,34 +6607,34 @@
         <v>0</v>
       </c>
       <c r="D167" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E167" t="n">
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I167" t="n">
         <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K167" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B168" s="2" t="n">
@@ -6644,145 +6644,145 @@
         <v>0</v>
       </c>
       <c r="D168" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E168" t="n">
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I168" t="n">
         <v>0</v>
       </c>
       <c r="J168" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K168" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B169" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C169" t="n">
-        <v>0</v>
+        <v>4.643418362802003</v>
       </c>
       <c r="D169" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E169" t="n">
-        <v>0</v>
+        <v>4.66979833285318</v>
       </c>
       <c r="F169" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>4.643418362802001</v>
       </c>
       <c r="H169" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I169" t="n">
-        <v>0</v>
+        <v>4.669798332853135</v>
       </c>
       <c r="J169" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K169" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B170" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C170" t="n">
-        <v>0</v>
+        <v>21.13699142139052</v>
       </c>
       <c r="D170" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E170" t="n">
-        <v>0</v>
+        <v>25.57029051823661</v>
       </c>
       <c r="F170" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G170" t="n">
-        <v>0</v>
+        <v>21.13699142139049</v>
       </c>
       <c r="H170" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I170" t="n">
-        <v>0</v>
+        <v>25.5702905182366</v>
       </c>
       <c r="J170" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K170" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B171" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C171" t="n">
-        <v>0</v>
+        <v>26.50800898088972</v>
       </c>
       <c r="D171" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E171" t="n">
-        <v>0</v>
+        <v>30.82190085360856</v>
       </c>
       <c r="F171" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>26.50800898088976</v>
       </c>
       <c r="H171" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>30.82190085360861</v>
       </c>
       <c r="J171" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K171" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B172" s="2" t="n">
@@ -6792,34 +6792,34 @@
         <v>0</v>
       </c>
       <c r="D172" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E172" t="n">
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
       </c>
       <c r="H172" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I172" t="n">
         <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K172" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B173" s="2" t="n">
@@ -6829,34 +6829,34 @@
         <v>0</v>
       </c>
       <c r="D173" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E173" t="n">
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
       </c>
       <c r="H173" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I173" t="n">
         <v>0</v>
       </c>
       <c r="J173" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K173" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B174" s="2" t="n">
@@ -6866,34 +6866,34 @@
         <v>0</v>
       </c>
       <c r="D174" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E174" t="n">
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
       </c>
       <c r="H174" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I174" t="n">
         <v>0</v>
       </c>
       <c r="J174" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K174" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B175" s="2" t="n">
@@ -6903,34 +6903,34 @@
         <v>0</v>
       </c>
       <c r="D175" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E175" t="n">
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
       </c>
       <c r="H175" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I175" t="n">
         <v>0</v>
       </c>
       <c r="J175" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K175" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B176" s="2" t="n">
@@ -6940,34 +6940,34 @@
         <v>0</v>
       </c>
       <c r="D176" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E176" t="n">
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I176" t="n">
         <v>0</v>
       </c>
       <c r="J176" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K176" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B177" s="2" t="n">
@@ -6977,34 +6977,34 @@
         <v>0</v>
       </c>
       <c r="D177" t="n">
-        <v>46.59616059878885</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E177" t="n">
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I177" t="n">
         <v>0</v>
       </c>
       <c r="J177" t="n">
-        <v>46.59616059878885</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K177" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B178" s="2" t="n">
@@ -7014,34 +7014,34 @@
         <v>0</v>
       </c>
       <c r="D178" t="n">
-        <v>59.02198672273944</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E178" t="n">
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
       </c>
       <c r="H178" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I178" t="n">
         <v>0</v>
       </c>
       <c r="J178" t="n">
-        <v>59.02198672273944</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K178" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B179" s="2" t="n">
@@ -7051,34 +7051,34 @@
         <v>0</v>
       </c>
       <c r="D179" t="n">
-        <v>67.21391127239798</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E179" t="n">
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
       </c>
       <c r="H179" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I179" t="n">
         <v>0</v>
       </c>
       <c r="J179" t="n">
-        <v>67.21391127239798</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K179" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B180" s="2" t="n">
@@ -7088,34 +7088,34 @@
         <v>0</v>
       </c>
       <c r="D180" t="n">
-        <v>73.17911008830633</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
       </c>
       <c r="H180" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I180" t="n">
         <v>0</v>
       </c>
       <c r="J180" t="n">
-        <v>73.17911008830633</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K180" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B181" s="2" t="n">
@@ -7125,34 +7125,34 @@
         <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>77.79663527637209</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E181" t="n">
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I181" t="n">
         <v>0</v>
       </c>
       <c r="J181" t="n">
-        <v>77.79663527637209</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K181" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B182" s="2" t="n">
@@ -7162,34 +7162,34 @@
         <v>0</v>
       </c>
       <c r="D182" t="n">
-        <v>32.10134655363332</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E182" t="n">
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
       </c>
       <c r="H182" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I182" t="n">
         <v>0</v>
       </c>
       <c r="J182" t="n">
-        <v>32.10134655363332</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K182" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B183" s="2" t="n">
@@ -7199,34 +7199,34 @@
         <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>36.66199663864789</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E183" t="n">
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
       </c>
       <c r="H183" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I183" t="n">
         <v>0</v>
       </c>
       <c r="J183" t="n">
-        <v>36.66199663864789</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K183" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B184" s="2" t="n">
@@ -7236,34 +7236,34 @@
         <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>39.66867812776202</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E184" t="n">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
       </c>
       <c r="H184" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I184" t="n">
         <v>0</v>
       </c>
       <c r="J184" t="n">
-        <v>39.66867812776202</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K184" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B185" s="2" t="n">
@@ -7273,34 +7273,34 @@
         <v>0</v>
       </c>
       <c r="D185" t="n">
-        <v>41.8580846280239</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E185" t="n">
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
       </c>
       <c r="H185" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I185" t="n">
         <v>0</v>
       </c>
       <c r="J185" t="n">
-        <v>41.8580846280239</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K185" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B186" s="2" t="n">
@@ -7310,182 +7310,182 @@
         <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>43.552854571804</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E186" t="n">
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
       </c>
       <c r="H186" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I186" t="n">
         <v>0</v>
       </c>
       <c r="J186" t="n">
-        <v>43.552854571804</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K186" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B187" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C187" t="n">
-        <v>27.62587522183637</v>
+        <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>46.59616059878885</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E187" t="n">
-        <v>46.37932496873859</v>
+        <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G187" t="n">
-        <v>42.63985297213146</v>
+        <v>0</v>
       </c>
       <c r="H187" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I187" t="n">
-        <v>27.62587522183637</v>
+        <v>0</v>
       </c>
       <c r="J187" t="n">
-        <v>46.59616059878885</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K187" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B188" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C188" t="n">
-        <v>33.99771171912063</v>
+        <v>0</v>
       </c>
       <c r="D188" t="n">
-        <v>59.02198672273944</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E188" t="n">
-        <v>47.44801062004103</v>
+        <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G188" t="n">
-        <v>43.54594726893275</v>
+        <v>0</v>
       </c>
       <c r="H188" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I188" t="n">
-        <v>28.69456087313882</v>
+        <v>0</v>
       </c>
       <c r="J188" t="n">
-        <v>59.02198672273944</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K188" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B189" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C189" t="n">
-        <v>33.99771171912063</v>
+        <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>67.21391127239798</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E189" t="n">
-        <v>47.44801062004103</v>
+        <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G189" t="n">
-        <v>43.54594726893275</v>
+        <v>0</v>
       </c>
       <c r="H189" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I189" t="n">
-        <v>28.69456087313882</v>
+        <v>0</v>
       </c>
       <c r="J189" t="n">
-        <v>67.21391127239798</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K189" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B190" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C190" t="n">
-        <v>6.371836497284264</v>
+        <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>73.17911008830633</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E190" t="n">
-        <v>1.068685651302448</v>
+        <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G190" t="n">
-        <v>0.9060942968012863</v>
+        <v>0</v>
       </c>
       <c r="H190" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I190" t="n">
-        <v>1.068685651302448</v>
+        <v>0</v>
       </c>
       <c r="J190" t="n">
-        <v>73.17911008830633</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K190" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B191" s="2" t="n">
@@ -7495,182 +7495,182 @@
         <v>0</v>
       </c>
       <c r="D191" t="n">
-        <v>77.79663527637209</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E191" t="n">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
       </c>
       <c r="H191" t="n">
-        <v>755.5999710264347</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I191" t="n">
         <v>0</v>
       </c>
       <c r="J191" t="n">
-        <v>77.79663527637209</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="K191" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B192" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C192" t="n">
-        <v>9.418528307983514</v>
+        <v>28.80896534710155</v>
       </c>
       <c r="D192" t="n">
-        <v>32.10134655363332</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E192" t="n">
-        <v>11.51122923006349</v>
+        <v>16.80905605365735</v>
       </c>
       <c r="F192" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G192" t="n">
-        <v>12.78664203887503</v>
+        <v>28.80896534710155</v>
       </c>
       <c r="H192" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I192" t="n">
-        <v>9.418528307983514</v>
+        <v>16.80905605365735</v>
       </c>
       <c r="J192" t="n">
-        <v>32.10134655363332</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K192" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B193" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C193" t="n">
-        <v>9.418528307983514</v>
+        <v>28.93573323885464</v>
       </c>
       <c r="D193" t="n">
-        <v>36.66199663864789</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E193" t="n">
-        <v>11.51122923006349</v>
+        <v>19.66960520930962</v>
       </c>
       <c r="F193" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G193" t="n">
-        <v>12.78664203887503</v>
+        <v>28.93573323885464</v>
       </c>
       <c r="H193" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I193" t="n">
-        <v>9.418528307983514</v>
+        <v>19.66960520930959</v>
       </c>
       <c r="J193" t="n">
-        <v>36.66199663864789</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K193" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B194" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C194" t="n">
-        <v>9.418528307983514</v>
+        <v>28.93573323885464</v>
       </c>
       <c r="D194" t="n">
-        <v>39.66867812776202</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E194" t="n">
-        <v>11.51122923006349</v>
+        <v>19.66960520930962</v>
       </c>
       <c r="F194" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G194" t="n">
-        <v>12.78664203887503</v>
+        <v>28.93573323885464</v>
       </c>
       <c r="H194" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I194" t="n">
-        <v>9.418528307983514</v>
+        <v>19.66960520930959</v>
       </c>
       <c r="J194" t="n">
-        <v>39.66867812776202</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K194" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B195" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C195" t="n">
-        <v>0</v>
+        <v>0.1267678917530863</v>
       </c>
       <c r="D195" t="n">
-        <v>41.8580846280239</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E195" t="n">
-        <v>0</v>
+        <v>2.860549155652276</v>
       </c>
       <c r="F195" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G195" t="n">
-        <v>0</v>
+        <v>0.1267678917530865</v>
       </c>
       <c r="H195" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I195" t="n">
-        <v>0</v>
+        <v>2.860549155652244</v>
       </c>
       <c r="J195" t="n">
-        <v>41.8580846280239</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K195" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B196" s="2" t="n">
@@ -7680,139 +7680,145 @@
         <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>43.552854571804</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="E196" t="n">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
       </c>
       <c r="H196" t="n">
-        <v>292.3269650394689</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="I196" t="n">
         <v>0</v>
       </c>
       <c r="J196" t="n">
-        <v>43.552854571804</v>
+        <v>755.5999710264347</v>
       </c>
       <c r="K196" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B197" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C197" t="n">
-        <v>0</v>
+        <v>10.94915160875057</v>
       </c>
       <c r="D197" t="n">
-        <v>1.717300224897027</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E197" t="n">
-        <v>0</v>
+        <v>14.82863630512521</v>
       </c>
       <c r="F197" t="n">
-        <v>4</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G197" t="n">
-        <v>0</v>
+        <v>10.94915160875057</v>
       </c>
       <c r="H197" t="n">
-        <v>4</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I197" t="n">
-        <v>0</v>
+        <v>14.8286363051252</v>
       </c>
       <c r="J197" t="n">
-        <v>1.717300224897027</v>
-      </c>
-      <c r="K197" t="inlineStr"/>
+        <v>292.3269650394689</v>
+      </c>
+      <c r="K197" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B198" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C198" t="n">
-        <v>0</v>
+        <v>10.94915160875057</v>
       </c>
       <c r="D198" t="n">
-        <v>2.246209584507109</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E198" t="n">
-        <v>0</v>
+        <v>14.82863630512521</v>
       </c>
       <c r="F198" t="n">
-        <v>4</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G198" t="n">
-        <v>0</v>
+        <v>10.94915160875057</v>
       </c>
       <c r="H198" t="n">
-        <v>4</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I198" t="n">
-        <v>0</v>
+        <v>14.8286363051252</v>
       </c>
       <c r="J198" t="n">
-        <v>2.246209584507109</v>
-      </c>
-      <c r="K198" t="inlineStr"/>
+        <v>292.3269650394689</v>
+      </c>
+      <c r="K198" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B199" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C199" t="n">
-        <v>0</v>
+        <v>10.94915160875057</v>
       </c>
       <c r="D199" t="n">
-        <v>2.4982276762293</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E199" t="n">
-        <v>0</v>
+        <v>14.82863630512521</v>
       </c>
       <c r="F199" t="n">
-        <v>4</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G199" t="n">
-        <v>0</v>
+        <v>10.94915160875057</v>
       </c>
       <c r="H199" t="n">
-        <v>4</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I199" t="n">
-        <v>0</v>
+        <v>14.8286363051252</v>
       </c>
       <c r="J199" t="n">
-        <v>2.4982276762293</v>
-      </c>
-      <c r="K199" t="inlineStr"/>
+        <v>292.3269650394689</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B200" s="2" t="n">
@@ -7822,32 +7828,34 @@
         <v>0</v>
       </c>
       <c r="D200" t="n">
-        <v>2.648951845381237</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E200" t="n">
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>4</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
       </c>
       <c r="H200" t="n">
-        <v>4</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I200" t="n">
         <v>0</v>
       </c>
       <c r="J200" t="n">
-        <v>2.648951845381237</v>
-      </c>
-      <c r="K200" t="inlineStr"/>
+        <v>292.3269650394689</v>
+      </c>
+      <c r="K200" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B201" s="2" t="n">
@@ -7857,32 +7865,34 @@
         <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>2.752635411261187</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="E201" t="n">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>4</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
       </c>
       <c r="H201" t="n">
-        <v>4</v>
+        <v>292.3269650394689</v>
       </c>
       <c r="I201" t="n">
         <v>0</v>
       </c>
       <c r="J201" t="n">
-        <v>2.752635411261187</v>
-      </c>
-      <c r="K201" t="inlineStr"/>
+        <v>292.3269650394689</v>
+      </c>
+      <c r="K201" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B202" s="2" t="n">
@@ -7892,32 +7902,32 @@
         <v>0</v>
       </c>
       <c r="D202" t="n">
+        <v>4</v>
+      </c>
+      <c r="E202" t="n">
+        <v>0</v>
+      </c>
+      <c r="F202" t="n">
         <v>1.717300224897027</v>
       </c>
-      <c r="E202" t="n">
-        <v>0</v>
-      </c>
-      <c r="F202" t="n">
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" t="n">
+        <v>1.717300224897027</v>
+      </c>
+      <c r="I202" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" t="n">
         <v>4</v>
-      </c>
-      <c r="G202" t="n">
-        <v>0</v>
-      </c>
-      <c r="H202" t="n">
-        <v>4</v>
-      </c>
-      <c r="I202" t="n">
-        <v>0</v>
-      </c>
-      <c r="J202" t="n">
-        <v>1.717300224897027</v>
       </c>
       <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B203" s="2" t="n">
@@ -7927,32 +7937,32 @@
         <v>0</v>
       </c>
       <c r="D203" t="n">
+        <v>4</v>
+      </c>
+      <c r="E203" t="n">
+        <v>0</v>
+      </c>
+      <c r="F203" t="n">
         <v>2.246209584507109</v>
       </c>
-      <c r="E203" t="n">
-        <v>0</v>
-      </c>
-      <c r="F203" t="n">
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" t="n">
+        <v>2.246209584507109</v>
+      </c>
+      <c r="I203" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" t="n">
         <v>4</v>
-      </c>
-      <c r="G203" t="n">
-        <v>0</v>
-      </c>
-      <c r="H203" t="n">
-        <v>4</v>
-      </c>
-      <c r="I203" t="n">
-        <v>0</v>
-      </c>
-      <c r="J203" t="n">
-        <v>2.246209584507109</v>
       </c>
       <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B204" s="2" t="n">
@@ -7962,32 +7972,32 @@
         <v>0</v>
       </c>
       <c r="D204" t="n">
+        <v>4</v>
+      </c>
+      <c r="E204" t="n">
+        <v>0</v>
+      </c>
+      <c r="F204" t="n">
         <v>2.4982276762293</v>
       </c>
-      <c r="E204" t="n">
-        <v>0</v>
-      </c>
-      <c r="F204" t="n">
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" t="n">
+        <v>2.4982276762293</v>
+      </c>
+      <c r="I204" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" t="n">
         <v>4</v>
-      </c>
-      <c r="G204" t="n">
-        <v>0</v>
-      </c>
-      <c r="H204" t="n">
-        <v>4</v>
-      </c>
-      <c r="I204" t="n">
-        <v>0</v>
-      </c>
-      <c r="J204" t="n">
-        <v>2.4982276762293</v>
       </c>
       <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B205" s="2" t="n">
@@ -7997,32 +8007,32 @@
         <v>0</v>
       </c>
       <c r="D205" t="n">
+        <v>4</v>
+      </c>
+      <c r="E205" t="n">
+        <v>0</v>
+      </c>
+      <c r="F205" t="n">
         <v>2.648951845381237</v>
       </c>
-      <c r="E205" t="n">
-        <v>0</v>
-      </c>
-      <c r="F205" t="n">
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" t="n">
+        <v>2.648951845381237</v>
+      </c>
+      <c r="I205" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" t="n">
         <v>4</v>
-      </c>
-      <c r="G205" t="n">
-        <v>0</v>
-      </c>
-      <c r="H205" t="n">
-        <v>4</v>
-      </c>
-      <c r="I205" t="n">
-        <v>0</v>
-      </c>
-      <c r="J205" t="n">
-        <v>2.648951845381237</v>
       </c>
       <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B206" s="2" t="n">
@@ -8032,32 +8042,32 @@
         <v>0</v>
       </c>
       <c r="D206" t="n">
+        <v>4</v>
+      </c>
+      <c r="E206" t="n">
+        <v>0</v>
+      </c>
+      <c r="F206" t="n">
         <v>2.752635411261187</v>
       </c>
-      <c r="E206" t="n">
-        <v>0</v>
-      </c>
-      <c r="F206" t="n">
+      <c r="G206" t="n">
+        <v>0</v>
+      </c>
+      <c r="H206" t="n">
+        <v>2.752635411261187</v>
+      </c>
+      <c r="I206" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" t="n">
         <v>4</v>
-      </c>
-      <c r="G206" t="n">
-        <v>0</v>
-      </c>
-      <c r="H206" t="n">
-        <v>4</v>
-      </c>
-      <c r="I206" t="n">
-        <v>0</v>
-      </c>
-      <c r="J206" t="n">
-        <v>2.752635411261187</v>
       </c>
       <c r="K206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SH_window_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B207" s="2" t="n">
@@ -8067,32 +8077,32 @@
         <v>0</v>
       </c>
       <c r="D207" t="n">
+        <v>4</v>
+      </c>
+      <c r="E207" t="n">
+        <v>0</v>
+      </c>
+      <c r="F207" t="n">
         <v>1.717300224897027</v>
       </c>
-      <c r="E207" t="n">
-        <v>0</v>
-      </c>
-      <c r="F207" t="n">
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" t="n">
+        <v>1.717300224897027</v>
+      </c>
+      <c r="I207" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" t="n">
         <v>4</v>
-      </c>
-      <c r="G207" t="n">
-        <v>0</v>
-      </c>
-      <c r="H207" t="n">
-        <v>4</v>
-      </c>
-      <c r="I207" t="n">
-        <v>0</v>
-      </c>
-      <c r="J207" t="n">
-        <v>1.717300224897027</v>
       </c>
       <c r="K207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SH_window_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B208" s="2" t="n">
@@ -8102,32 +8112,32 @@
         <v>0</v>
       </c>
       <c r="D208" t="n">
+        <v>4</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" t="n">
         <v>2.246209584507109</v>
       </c>
-      <c r="E208" t="n">
-        <v>0</v>
-      </c>
-      <c r="F208" t="n">
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="n">
+        <v>2.246209584507109</v>
+      </c>
+      <c r="I208" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" t="n">
         <v>4</v>
-      </c>
-      <c r="G208" t="n">
-        <v>0</v>
-      </c>
-      <c r="H208" t="n">
-        <v>4</v>
-      </c>
-      <c r="I208" t="n">
-        <v>0</v>
-      </c>
-      <c r="J208" t="n">
-        <v>2.246209584507109</v>
       </c>
       <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SH_window_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B209" s="2" t="n">
@@ -8137,32 +8147,32 @@
         <v>0</v>
       </c>
       <c r="D209" t="n">
+        <v>4</v>
+      </c>
+      <c r="E209" t="n">
+        <v>0</v>
+      </c>
+      <c r="F209" t="n">
         <v>2.4982276762293</v>
       </c>
-      <c r="E209" t="n">
-        <v>0</v>
-      </c>
-      <c r="F209" t="n">
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" t="n">
+        <v>2.4982276762293</v>
+      </c>
+      <c r="I209" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" t="n">
         <v>4</v>
-      </c>
-      <c r="G209" t="n">
-        <v>0</v>
-      </c>
-      <c r="H209" t="n">
-        <v>4</v>
-      </c>
-      <c r="I209" t="n">
-        <v>0</v>
-      </c>
-      <c r="J209" t="n">
-        <v>2.4982276762293</v>
       </c>
       <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>SH_window_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B210" s="2" t="n">
@@ -8172,32 +8182,32 @@
         <v>0</v>
       </c>
       <c r="D210" t="n">
+        <v>4</v>
+      </c>
+      <c r="E210" t="n">
+        <v>0</v>
+      </c>
+      <c r="F210" t="n">
         <v>2.648951845381237</v>
       </c>
-      <c r="E210" t="n">
-        <v>0</v>
-      </c>
-      <c r="F210" t="n">
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" t="n">
+        <v>2.648951845381237</v>
+      </c>
+      <c r="I210" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" t="n">
         <v>4</v>
-      </c>
-      <c r="G210" t="n">
-        <v>0</v>
-      </c>
-      <c r="H210" t="n">
-        <v>4</v>
-      </c>
-      <c r="I210" t="n">
-        <v>0</v>
-      </c>
-      <c r="J210" t="n">
-        <v>2.648951845381237</v>
       </c>
       <c r="K210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>SH_window_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B211" s="2" t="n">
@@ -8207,27 +8217,202 @@
         <v>0</v>
       </c>
       <c r="D211" t="n">
+        <v>4</v>
+      </c>
+      <c r="E211" t="n">
+        <v>0</v>
+      </c>
+      <c r="F211" t="n">
         <v>2.752635411261187</v>
       </c>
-      <c r="E211" t="n">
-        <v>0</v>
-      </c>
-      <c r="F211" t="n">
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="n">
+        <v>2.752635411261187</v>
+      </c>
+      <c r="I211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" t="n">
         <v>4</v>
       </c>
-      <c r="G211" t="n">
-        <v>0</v>
-      </c>
-      <c r="H211" t="n">
+      <c r="K211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>SH_window_retrofit</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C212" t="n">
+        <v>0</v>
+      </c>
+      <c r="D212" t="n">
         <v>4</v>
       </c>
-      <c r="I211" t="n">
-        <v>0</v>
-      </c>
-      <c r="J211" t="n">
+      <c r="E212" t="n">
+        <v>0</v>
+      </c>
+      <c r="F212" t="n">
+        <v>1.717300224897027</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" t="n">
+        <v>1.717300224897027</v>
+      </c>
+      <c r="I212" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" t="n">
+        <v>4</v>
+      </c>
+      <c r="K212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>SH_window_retrofit</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="n">
+        <v>47849</v>
+      </c>
+      <c r="C213" t="n">
+        <v>0</v>
+      </c>
+      <c r="D213" t="n">
+        <v>4</v>
+      </c>
+      <c r="E213" t="n">
+        <v>0</v>
+      </c>
+      <c r="F213" t="n">
+        <v>2.246209584507109</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" t="n">
+        <v>2.246209584507109</v>
+      </c>
+      <c r="I213" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" t="n">
+        <v>4</v>
+      </c>
+      <c r="K213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>SH_window_retrofit</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="n">
+        <v>49675</v>
+      </c>
+      <c r="C214" t="n">
+        <v>0</v>
+      </c>
+      <c r="D214" t="n">
+        <v>4</v>
+      </c>
+      <c r="E214" t="n">
+        <v>0</v>
+      </c>
+      <c r="F214" t="n">
+        <v>2.4982276762293</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" t="n">
+        <v>2.4982276762293</v>
+      </c>
+      <c r="I214" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" t="n">
+        <v>4</v>
+      </c>
+      <c r="K214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>SH_window_retrofit</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="n">
+        <v>51502</v>
+      </c>
+      <c r="C215" t="n">
+        <v>0</v>
+      </c>
+      <c r="D215" t="n">
+        <v>4</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0</v>
+      </c>
+      <c r="F215" t="n">
+        <v>2.648951845381237</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="n">
+        <v>2.648951845381237</v>
+      </c>
+      <c r="I215" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" t="n">
+        <v>4</v>
+      </c>
+      <c r="K215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>SH_window_retrofit</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="n">
+        <v>53328</v>
+      </c>
+      <c r="C216" t="n">
+        <v>0</v>
+      </c>
+      <c r="D216" t="n">
+        <v>4</v>
+      </c>
+      <c r="E216" t="n">
+        <v>0</v>
+      </c>
+      <c r="F216" t="n">
         <v>2.752635411261187</v>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="n">
+        <v>2.752635411261187</v>
+      </c>
+      <c r="I216" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" t="n">
+        <v>4</v>
+      </c>
+      <c r="K216" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
